--- a/products/200-template-sosmed-premium-premium.xlsx
+++ b/products/200-template-sosmed-premium-premium.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Template Library" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Content Calendar" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Analytics Tracker" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Hashtag Bank" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Performance Log" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Platform Best Practices" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Quality Checklist" state="visible" r:id="rId10"/>
+    <sheet sheetId="1" name="Perpustakaan Templat" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Kalender Konten" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Pelacak Analitik" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Bank Hashtag" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Catatan Performa" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Praktik Terbaik Platform" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Checklist Kualitas" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -43,16 +43,16 @@
     <t>T-001</t>
   </si>
   <si>
-    <t>Bagian 1: Content Planning</t>
-  </si>
-  <si>
-    <t>Content Calendar Bulanan</t>
+    <t>Bagian 1: Perencanaan Konten</t>
+  </si>
+  <si>
+    <t>Kalender Konten Bulanan</t>
   </si>
   <si>
     <t>Membuat planning konten untuk 1 bulan penuh</t>
   </si>
   <si>
-    <t>Sebagai social media strategist, buatkan content calendar 30 hari untuk [BISNIS] di [PLATFORM]. Posting [FREKUENSI] kali per minggu dengan goal [GOAL]. Content pillar: [PILLAR]. Buat tabel dengan kolom: Tanggal, Hari, Content Pillar, Ide Konten, Format (image/video/carousel/story), Caption Hook, dan CTA. Variasikan format dan pastikan ada minimal 2 konten edukatif, 1 konten promosi, dan 1 konten engagement per minggu.</t>
+    <t>Sebagai perencana konten media sosial, buatkan kalender konten 30 hari untuk [BISNIS] di [PLATFORM]. Posting [FREKUENSI] kali per minggu dengan tujuan [GOAL]. Pilar konten: [PILLAR]. Buat tabel dengan kolom: Tanggal, Hari, Pilar Konten, Ide Konten, Format (gambar/video/carousel/story), Kalimat Pembuka Caption, dan CTA. Variasikan format dan pastikan ada minimal 2 konten edukatif, 1 konten promosi, dan 1 konten pemicu interaksi per minggu.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang digunakan (Instagram/Facebook/TikTok); [FREKUENSI]: berapa kali posting per minggu; [GOAL]: tujuan bulan ini (awareness/sales/engagement); [PILLAR]: 3-5 content pillar bisnis Anda</t>
@@ -64,7 +64,7 @@
     <t>T-002</t>
   </si>
   <si>
-    <t>Content Pillar Development</t>
+    <t>Pengembangan Pilar Konten</t>
   </si>
   <si>
     <t>Menentukan 3-5 topik utama untuk konten Anda</t>
@@ -82,7 +82,7 @@
     <t>T-003</t>
   </si>
   <si>
-    <t>Audience Research Summary</t>
+    <t>Ringkasan Riset Audiens</t>
   </si>
   <si>
     <t>Memahami karakteristik dan kebutuhan audience Anda</t>
@@ -100,7 +100,7 @@
     <t>T-004</t>
   </si>
   <si>
-    <t>Competitor Analysis</t>
+    <t>Analisis Kompetitor</t>
   </si>
   <si>
     <t>Menganalisis strategi social media kompetitor</t>
@@ -118,7 +118,7 @@
     <t>T-005</t>
   </si>
   <si>
-    <t>Weekly Content Batch</t>
+    <t>Batch Konten Mingguan</t>
   </si>
   <si>
     <t>Membuat 7 ide konten dalam sekali duduk</t>
@@ -136,7 +136,7 @@
     <t>T-006</t>
   </si>
   <si>
-    <t>Monthly Theme Planner</t>
+    <t>Perencana Tema Bulanan</t>
   </si>
   <si>
     <t>Menentukan tema besar untuk konten satu bulan penuh</t>
@@ -154,7 +154,7 @@
     <t>T-007</t>
   </si>
   <si>
-    <t>Content Mix Ratio Calculator</t>
+    <t>Kalkulator Rasio Campuran Konten</t>
   </si>
   <si>
     <t>Menentukan porsi konten edukasi, promosi, dan hiburan</t>
@@ -172,7 +172,7 @@
     <t>T-008</t>
   </si>
   <si>
-    <t>Evergreen Content Bank Builder</t>
+    <t>Penyusun Bank Konten Evergreen</t>
   </si>
   <si>
     <t>Membangun cadangan konten yang tidak kedaluwarsa</t>
@@ -190,7 +190,7 @@
     <t>T-009</t>
   </si>
   <si>
-    <t>Content Repurposing Planner</t>
+    <t>Perencana Daur Ulang Konten</t>
   </si>
   <si>
     <t>Mengubah 1 konten besar menjadi banyak konten kecil</t>
@@ -208,7 +208,7 @@
     <t>T-010</t>
   </si>
   <si>
-    <t>Campaign Calendar Builder</t>
+    <t>Penyusun Kalender Kampanye</t>
   </si>
   <si>
     <t>Merencanakan kampanye marketing dari awal sampai akhir</t>
@@ -226,7 +226,7 @@
     <t>T-011</t>
   </si>
   <si>
-    <t>Product Launch Content Calendar</t>
+    <t>Kalender Konten Peluncuran Produk</t>
   </si>
   <si>
     <t>Merencanakan konten untuk peluncuran produk baru</t>
@@ -244,7 +244,7 @@
     <t>T-012</t>
   </si>
   <si>
-    <t>Holiday Content Planner</t>
+    <t>Perencana Konten Hari Besar</t>
   </si>
   <si>
     <t>Menyiapkan konten untuk hari besar nasional dan internasional</t>
@@ -262,7 +262,7 @@
     <t>T-013</t>
   </si>
   <si>
-    <t>Content Production SOP Builder</t>
+    <t>Penyusun SOP Produksi Konten</t>
   </si>
   <si>
     <t>Menyusun prosedur produksi konten untuk tim</t>
@@ -280,7 +280,7 @@
     <t>T-014</t>
   </si>
   <si>
-    <t>Content Approval Workflow</t>
+    <t>Alur Kerja Persetujuan Konten</t>
   </si>
   <si>
     <t>Menyusun alur persetujuan konten sebelum tayang</t>
@@ -298,7 +298,7 @@
     <t>T-015</t>
   </si>
   <si>
-    <t>Content Brief Template Builder</t>
+    <t>Penyusun Templat Brief Konten</t>
   </si>
   <si>
     <t>Membuat brief yang jelas untuk konten kreatif</t>
@@ -316,7 +316,7 @@
     <t>T-016</t>
   </si>
   <si>
-    <t>Brand Voice Guide Generator</t>
+    <t>Generator Panduan Gaya Bahasa Merek</t>
   </si>
   <si>
     <t>Menyusun pedoman suara brand untuk konsistensi konten</t>
@@ -334,13 +334,13 @@
     <t>T-017</t>
   </si>
   <si>
-    <t>Hashtag Bank Builder</t>
+    <t>Penyusun Bank Hashtag</t>
   </si>
   <si>
     <t>Menyusun daftar hashtag yang terorganisir per topik</t>
   </si>
   <si>
-    <t>Sebagai hashtag researcher, bangun bank hashtag untuk [BISNIS] di industri [INDUSTRI], pasar utama [KOTA]. Kelompokkan menjadi 4 set: hashtag brand (3-5 buah), hashtag industri luas (10 buah, jutaan post), hashtag niche (15 buah, ribuan sampai ratusan ribu post), dan hashtag lokal (10 buah). Untuk setiap hashtag perkirakan tingkat persaingannya. Buat 3 kombinasi siap pakai untuk konten edukasi, promosi, dan engagement.</t>
+    <t>Sebagai peneliti hashtag, bangun bank hashtag untuk [BISNIS] di industri [INDUSTRI], pasar utama [KOTA]. Kelompokkan menjadi 4 set: hashtag brand (3-5 buah), hashtag industri luas (10 buah, jutaan post), hashtag niche (15 buah, ribuan sampai ratusan ribu post), dan hashtag lokal (10 buah). Untuk setiap hashtag perkirakan tingkat persaingannya. Buat 3 kombinasi siap pakai untuk konten edukasi, promosi, dan engagement.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [INDUSTRI]: industri Anda; [KOTA]: lokasi utama pasar Anda</t>
@@ -352,7 +352,7 @@
     <t>T-018</t>
   </si>
   <si>
-    <t>UGC Collection Plan</t>
+    <t>Rencana Pengumpulan UGC</t>
   </si>
   <si>
     <t>Merencanakan pengumpulan konten dari pelanggan</t>
@@ -370,7 +370,7 @@
     <t>T-019</t>
   </si>
   <si>
-    <t>Influencer Collaboration Planner</t>
+    <t>Perencana Kolaborasi Influencer</t>
   </si>
   <si>
     <t>Merencanakan kerja sama dengan kreator konten</t>
@@ -388,7 +388,7 @@
     <t>T-020</t>
   </si>
   <si>
-    <t>Cross-Platform Content Planner</t>
+    <t>Perencana Konten Lintas Platform</t>
   </si>
   <si>
     <t>Merencanakan konten yang sama untuk banyak platform</t>
@@ -406,7 +406,7 @@
     <t>T-021</t>
   </si>
   <si>
-    <t>Engagement Forecast Calculator</t>
+    <t>Kalkulator Perkiraan Engagement</t>
   </si>
   <si>
     <t>Memperkirakan hasil engagement dari rencana konten</t>
@@ -424,7 +424,7 @@
     <t>T-022</t>
   </si>
   <si>
-    <t>Content Audit Framework</t>
+    <t>Kerangka Audit Konten</t>
   </si>
   <si>
     <t>Menilai performa konten 3 bulan terakhir</t>
@@ -442,7 +442,7 @@
     <t>T-023</t>
   </si>
   <si>
-    <t>Competitor Content Gap Analysis</t>
+    <t>Analisis Kesenjangan Konten Kompetitor</t>
   </si>
   <si>
     <t>Menemukan peluang konten yang belum digarap kompetitor</t>
@@ -460,7 +460,7 @@
     <t>T-024</t>
   </si>
   <si>
-    <t>Trending Topic Scanner</t>
+    <t>Pemindai Topik Tren</t>
   </si>
   <si>
     <t>Menemukan topik sedang naik di industri Anda</t>
@@ -478,7 +478,7 @@
     <t>T-025</t>
   </si>
   <si>
-    <t>Audience Question Mining</t>
+    <t>Penggalian Pertanyaan Audiens</t>
   </si>
   <si>
     <t>Mengubah pertanyaan audiens menjadi ide konten</t>
@@ -496,7 +496,7 @@
     <t>T-026</t>
   </si>
   <si>
-    <t>Sales Funnel Content Mapping</t>
+    <t>Pemetaan Konten Sales Funnel</t>
   </si>
   <si>
     <t>Memetakan konten untuk setiap tahap perjalanan pembeli</t>
@@ -514,7 +514,7 @@
     <t>T-027</t>
   </si>
   <si>
-    <t>Retention Content Plan</t>
+    <t>Rencana Konten Retensi</t>
   </si>
   <si>
     <t>Merencanakan konten untuk pelanggan yang sudah beli</t>
@@ -532,7 +532,7 @@
     <t>T-028</t>
   </si>
   <si>
-    <t>Win-Back Campaign Planner</t>
+    <t>Perencana Kampanye Win-Back</t>
   </si>
   <si>
     <t>Merencanakan konten untuk mengaktifkan kembali pelanggan lama</t>
@@ -550,7 +550,7 @@
     <t>T-029</t>
   </si>
   <si>
-    <t>Event Content Plan</t>
+    <t>Rencana Konten Acara</t>
   </si>
   <si>
     <t>Merencanakan konten untuk event online atau offline</t>
@@ -568,7 +568,7 @@
     <t>T-030</t>
   </si>
   <si>
-    <t>Giveaway Campaign Planner</t>
+    <t>Perencana Kampanye Giveaway</t>
   </si>
   <si>
     <t>Merencanakan giveaway yang menghasilkan, bukan sekadar viral sesaat</t>
@@ -586,7 +586,7 @@
     <t>T-031</t>
   </si>
   <si>
-    <t>Announcement Content Sequence</t>
+    <t>Beruntun Konten Pengumuman</t>
   </si>
   <si>
     <t>Mengumumkan perubahan besar (harga, lokasi, produk baru)</t>
@@ -604,7 +604,7 @@
     <t>T-032</t>
   </si>
   <si>
-    <t>Crisis Content Plan</t>
+    <t>Rencana Konten Krisis</t>
   </si>
   <si>
     <t>Menyiapkan konten darurat sebelum masalah terjadi</t>
@@ -622,7 +622,7 @@
     <t>T-033</t>
   </si>
   <si>
-    <t>Content Backlog Builder</t>
+    <t>Penyusun Cadangan Ide Konten</t>
   </si>
   <si>
     <t>Menyusun cadangan ide konten untuk 3 bulan ke depan</t>
@@ -640,7 +640,7 @@
     <t>T-034</t>
   </si>
   <si>
-    <t>Idea Bank Generator per Pillar</t>
+    <t>Generator Bank Ide per Pilar</t>
   </si>
   <si>
     <t>Memperdalam satu pillar dengan banyak angle</t>
@@ -658,7 +658,7 @@
     <t>T-035</t>
   </si>
   <si>
-    <t>Weekly Content Review Template</t>
+    <t>Templat Telaah Konten Mingguan</t>
   </si>
   <si>
     <t>Menilai performa konten tiap akhir pekan</t>
@@ -676,7 +676,7 @@
     <t>T-036</t>
   </si>
   <si>
-    <t>Monthly Content Review Framework</t>
+    <t>Kerangka Telaah Konten Bulanan</t>
   </si>
   <si>
     <t>Evaluasi menyeluruh strategi konten bulanan</t>
@@ -694,7 +694,7 @@
     <t>T-037</t>
   </si>
   <si>
-    <t>Quarterly Strategy Refresh</t>
+    <t>Penyegaran Strategi Kuartalan</t>
   </si>
   <si>
     <t>Menyegarkan strategi konten setiap 3 bulan</t>
@@ -712,7 +712,7 @@
     <t>T-038</t>
   </si>
   <si>
-    <t>Annual Content Roadmap</t>
+    <t>Peta Jalan Konten Tahunan</t>
   </si>
   <si>
     <t>Menyusun peta jalan konten setahun penuh</t>
@@ -730,7 +730,7 @@
     <t>T-039</t>
   </si>
   <si>
-    <t>Team Task Assignment Matrix</t>
+    <t>Matriks Pembagian Tugas Tim</t>
   </si>
   <si>
     <t>Membagi tugas konten untuk tim kecil</t>
@@ -748,7 +748,7 @@
     <t>T-040</t>
   </si>
   <si>
-    <t>Seasonal Content Planner</t>
+    <t>Perencana Konten Musiman</t>
   </si>
   <si>
     <t>Merencanakan konten untuk momen spesial sepanjang tahun</t>
@@ -766,10 +766,10 @@
     <t>T-041</t>
   </si>
   <si>
-    <t>Bagian 2: Caption Writing</t>
-  </si>
-  <si>
-    <t>Instagram Caption yang Storytelling</t>
+    <t>Bagian 2: Penulisan Caption</t>
+  </si>
+  <si>
+    <t>Caption Instagram Bernuansa Storytelling</t>
   </si>
   <si>
     <t>Membuat caption Instagram yang menceritakan kisah brand</t>
@@ -787,25 +787,25 @@
     <t>T-042</t>
   </si>
   <si>
-    <t>Facebook Post yang Shareable</t>
+    <t>Post Facebook yang Mudah Dibagikan</t>
   </si>
   <si>
     <t>Membuat post Facebook yang mendorong sharing</t>
   </si>
   <si>
-    <t>Sebagai Facebook content strategist, tulis post 200 kata tentang [TOPIK] dengan insight [INSIGHT] untuk [AUDIENCE]. Goal: [GOAL]. Buat post yang: (1) relatable dengan masalah audience, (2) memberikan value nyata, (3) mudah dipahami, (4) mendorong sharing. Gunakan format: question di awal, story atau contoh di tengah, takeaway di akhir. Tambahkan 1 CTA yang tidak salesy.</t>
+    <t>Sebagai perencana konten Facebook, tulis post 200 kata tentang [TOPIK] dengan wawasan [INSIGHT] untuk [AUDIENCE]. Tujuan: [GOAL]. Buat post yang: (1) terasa dekat dengan masalah pembaca, (2) memberikan manfaat nyata, (3) mudah dipahami, (4) mendorong pembaca membagikannya. Gunakan format: pertanyaan di awal, cerita atau contoh di tengah, kesimpulan yang bisa dibawa pulang di akhir. Tambahkan 1 CTA yang tidak memaksa jualan.</t>
   </si>
   <si>
     <t>[TOPIK]: topik post; [INSIGHT]: insight atau tips yang dibagikan; [AUDIENCE]: target audience; [GOAL]: goal post (awareness/engagement/traffic)</t>
   </si>
   <si>
-    <t>Post Facebook yang engaging dan shareable</t>
+    <t>Post Facebook yang mengundang interaksi dan mudah dibagikan</t>
   </si>
   <si>
     <t>T-043</t>
   </si>
   <si>
-    <t>TikTok Script yang Viral</t>
+    <t>Naskah TikTok yang Berpotensi Viral</t>
   </si>
   <si>
     <t>Membuat script TikTok yang berpotensi viral</t>
@@ -823,7 +823,7 @@
     <t>T-044</t>
   </si>
   <si>
-    <t>Twitter/X Thread yang Informative</t>
+    <t>Thread Twitter/X yang Informatif</t>
   </si>
   <si>
     <t>Membuat thread Twitter/X yang educational</t>
@@ -841,7 +841,7 @@
     <t>T-045</t>
   </si>
   <si>
-    <t>LinkedIn Post yang Professional</t>
+    <t>Post LinkedIn yang Profesional</t>
   </si>
   <si>
     <t>Membuat post LinkedIn untuk personal branding</t>
@@ -853,13 +853,13 @@
     <t>[TOPIK]: topik post; [EXPERTISE]: bidang keahlian Anda; [LESSON]: pelajaran atau insight yang dibagikan; [AUDIENCE]: target reader (recruiter/client/peer)</t>
   </si>
   <si>
-    <t>Post LinkedIn yang professional dan engaging</t>
+    <t>Post LinkedIn yang profesional dan mengundang interaksi</t>
   </si>
   <si>
     <t>T-046</t>
   </si>
   <si>
-    <t>Product Launch Caption</t>
+    <t>Caption Peluncuran Produk</t>
   </si>
   <si>
     <t>Mengumumkan produk baru dengan caption yang membangun antusiasme</t>
@@ -877,7 +877,7 @@
     <t>T-047</t>
   </si>
   <si>
-    <t>Discount Promo Caption</t>
+    <t>Caption Promo Diskon</t>
   </si>
   <si>
     <t>Mengumumkan diskon tanpa terlihat murahan</t>
@@ -913,7 +913,7 @@
     <t>T-049</t>
   </si>
   <si>
-    <t>Testimonial Repost Caption</t>
+    <t>Caption Repost Testimoni</t>
   </si>
   <si>
     <t>Memposting ulang testimoni pelanggan dengan bingkai cerita</t>
@@ -931,7 +931,7 @@
     <t>T-050</t>
   </si>
   <si>
-    <t>How-To Educational Caption</t>
+    <t>Caption Edukasi Panduan Cara</t>
   </si>
   <si>
     <t>Mengajarkan sesuatu yang berguna dalam satu caption</t>
@@ -949,7 +949,7 @@
     <t>T-051</t>
   </si>
   <si>
-    <t>Myth vs Fact Caption</t>
+    <t>Caption Mitos vs Fakta</t>
   </si>
   <si>
     <t>Meluruskan miskonsepsi di industri Anda</t>
@@ -967,7 +967,7 @@
     <t>T-052</t>
   </si>
   <si>
-    <t>Before-After Transformation Caption</t>
+    <t>Caption Transformasi Before-After</t>
   </si>
   <si>
     <t>Menunjukkan perubahan hasil sebelum dan sesudah</t>
@@ -985,7 +985,7 @@
     <t>T-053</t>
   </si>
   <si>
-    <t>Behind the Scenes Caption</t>
+    <t>Caption Di Balik Layar</t>
   </si>
   <si>
     <t>Menunjukkan proses di balik produk atau jasa</t>
@@ -1003,7 +1003,7 @@
     <t>T-054</t>
   </si>
   <si>
-    <t>FAQ Answer Caption</t>
+    <t>Caption Jawaban FAQ</t>
   </si>
   <si>
     <t>Menjawab pertanyaan yang sering masuk dalam bentuk konten</t>
@@ -1021,7 +1021,7 @@
     <t>T-055</t>
   </si>
   <si>
-    <t>Question of the Day Caption</t>
+    <t>Caption Pertanyaan Hari Ini</t>
   </si>
   <si>
     <t>Memicu komentar dengan pertanyaan yang mudah dijawab</t>
@@ -1039,7 +1039,7 @@
     <t>T-056</t>
   </si>
   <si>
-    <t>Motivational Caption yang Tidak Klise</t>
+    <t>Caption Motivasi yang Tidak Klise</t>
   </si>
   <si>
     <t>Menghibau audiens tanpa kalimat motivasi kosong</t>
@@ -1057,7 +1057,7 @@
     <t>T-057</t>
   </si>
   <si>
-    <t>Weekend Sale Caption</t>
+    <t>Caption Diskon Akhir Pekan</t>
   </si>
   <si>
     <t>Promo akhir pekan dengan waktu terbatas</t>
@@ -1093,7 +1093,7 @@
     <t>T-059</t>
   </si>
   <si>
-    <t>Restock Announcement Caption</t>
+    <t>Caption Pengumuman Restock</t>
   </si>
   <si>
     <t>Mengumumkan ketersediaan kembali produk yang lama habis</t>
@@ -1111,7 +1111,7 @@
     <t>T-060</t>
   </si>
   <si>
-    <t>New Arrival Caption</t>
+    <t>Caption Produk Baru</t>
   </si>
   <si>
     <t>Memperkenalkan produk baru ke katalog</t>
@@ -1129,7 +1129,7 @@
     <t>T-061</t>
   </si>
   <si>
-    <t>Limited Edition Caption</t>
+    <t>Caption Edisi Terbatas</t>
   </si>
   <si>
     <t>Menjual produk edisi terbatas dengan kelangkaan jujur</t>
@@ -1147,7 +1147,7 @@
     <t>T-062</t>
   </si>
   <si>
-    <t>Bundle Offer Caption</t>
+    <t>Caption Penawaran Bundling</t>
   </si>
   <si>
     <t>Menjual paket beberapa produk dengan nilai lebih</t>
@@ -1165,7 +1165,7 @@
     <t>T-063</t>
   </si>
   <si>
-    <t>Holiday Greeting Caption</t>
+    <t>Caption Ucapan Hari Besar</t>
   </si>
   <si>
     <t>Mengucapkan hari besar tanpa terlihat ikut-ikutan</t>
@@ -1183,7 +1183,7 @@
     <t>T-064</t>
   </si>
   <si>
-    <t>National Day Tie-in Caption</t>
+    <t>Caption Kaitan Hari Nasional</t>
   </si>
   <si>
     <t>Menghubungkan hari nasional dengan bisnis secara wajar</t>
@@ -1201,7 +1201,7 @@
     <t>T-065</t>
   </si>
   <si>
-    <t>Trend Tie-in Caption</t>
+    <t>Caption Kaitan Tren</t>
   </si>
   <si>
     <t>Mengikuti tren yang sedang viral dengan cara yang tetap relevan</t>
@@ -1219,7 +1219,7 @@
     <t>T-066</t>
   </si>
   <si>
-    <t>Customer Story Feature Caption</t>
+    <t>Caption Sorotan Cerita Pelanggan</t>
   </si>
   <si>
     <t>Menampilkan perjalanan pelanggan sebagai konten utama</t>
@@ -1237,7 +1237,7 @@
     <t>T-067</t>
   </si>
   <si>
-    <t>Team Introduction Caption</t>
+    <t>Caption Perkenalan Tim</t>
   </si>
   <si>
     <t>Memperkenalkan anggota tim untuk membangun kepercayaan</t>
@@ -1255,7 +1255,7 @@
     <t>T-068</t>
   </si>
   <si>
-    <t>Problem-Solution Caption</t>
+    <t>Caption Masalah-Solusi</t>
   </si>
   <si>
     <t>Menyusun masalah dan solusi dalam struktur yang meyakinkan</t>
@@ -1273,7 +1273,7 @@
     <t>T-069</t>
   </si>
   <si>
-    <t>Listicle Caption</t>
+    <t>Caption Format Daftar</t>
   </si>
   <si>
     <t>Menyajikan daftar tips atau rekomendasi yang mudah dibaca</t>
@@ -1291,7 +1291,7 @@
     <t>T-070</t>
   </si>
   <si>
-    <t>Statistics Share Caption</t>
+    <t>Caption Berbagi Statistik</t>
   </si>
   <si>
     <t>Membagikan data atau statistik yang mengejutkan</t>
@@ -1309,7 +1309,7 @@
     <t>T-071</t>
   </si>
   <si>
-    <t>Quote Reflection Caption</t>
+    <t>Caption Renungan Kutipan</t>
   </si>
   <si>
     <t>Mengutip kalimat dan menambahkan refleksi personal</t>
@@ -1327,7 +1327,7 @@
     <t>T-072</t>
   </si>
   <si>
-    <t>Humor Caption yang Tetap On-Brand</t>
+    <t>Caption Humor yang Tetap Sesuai Merek</t>
   </si>
   <si>
     <t>Membuat audiens tersenyum tanpa keluar dari karakter brand</t>
@@ -1363,7 +1363,7 @@
     <t>T-074</t>
   </si>
   <si>
-    <t>Take a Stand Caption</t>
+    <t>Caption yang Bersikap</t>
   </si>
   <si>
     <t>Menyatakan pendapat tentang isu industri dengan cara yang terukur</t>
@@ -1381,7 +1381,7 @@
     <t>T-075</t>
   </si>
   <si>
-    <t>Comparison Caption</t>
+    <t>Caption Perbandingan</t>
   </si>
   <si>
     <t>Membandingkan pilihan secara jujur termasuk kelemahan</t>
@@ -1435,7 +1435,7 @@
     <t>T-078</t>
   </si>
   <si>
-    <t>Countdown Caption</t>
+    <t>Caption Hitung Mundur</t>
   </si>
   <si>
     <t>Menghitung mundur menuju momen penting</t>
@@ -1453,7 +1453,7 @@
     <t>T-079</t>
   </si>
   <si>
-    <t>User Content Shoutout Caption</t>
+    <t>Caption Sorotan Konten Pelanggan</t>
   </si>
   <si>
     <t>Mengapresiasi konten pelanggan yang menggunakan produk Anda</t>
@@ -1471,13 +1471,13 @@
     <t>T-080</t>
   </si>
   <si>
-    <t>Multi-Platform Caption Adapter</t>
+    <t>Adaptor Caption Lintas Platform</t>
   </si>
   <si>
     <t>Mengadaptasi 1 konten untuk berbagai platform</t>
   </si>
   <si>
-    <t>Sebagai multi-platform content strategist, adaptasi konten inti [KONTEN_INTI] untuk [PLATFORMS]. Brand voice: [BRAND_VOICE]. Untuk setiap platform, berikan: (1) panjang optimal caption, (2) format yang sesuai, (3) hashtag strategy, (4) CTA yang platform-specific, (5) best posting time. Pastikan pesan konsisten tapi format disesuaikan dengan karakter setiap platform.</t>
+    <t>Sebagai perencana konten multi-platform, adaptasi konten inti [KONTEN_INTI] untuk [PLATFORMS]. Gaya bahasa merek: [BRAND_VOICE]. Untuk setiap platform, berikan: (1) panjang caption yang optimal, (2) format yang sesuai, (3) strategi hashtag, (4) CTA yang khas platform tersebut, (5) waktu posting terbaik. Pastikan pesan konsisten tapi format disesuaikan dengan karakter setiap platform.</t>
   </si>
   <si>
     <t>[KONTEN_INTI]: pesan utama yang ingin disampaikan; [PLATFORMS]: platform target (Instagram, Facebook, Twitter, LinkedIn, TikTok); [BRAND_VOICE]: tone dan style brand Anda</t>
@@ -1489,19 +1489,19 @@
     <t>T-081</t>
   </si>
   <si>
-    <t>Bagian 3: Visual Content</t>
-  </si>
-  <si>
-    <t>Instagram Carousel Structure</t>
-  </si>
-  <si>
-    <t>Membuat struktur carousel yang engaging</t>
+    <t>Bagian 3: Konten Visual</t>
+  </si>
+  <si>
+    <t>Struktur Carousel Instagram</t>
+  </si>
+  <si>
+    <t>Membuat struktur carousel yang mengundang interaksi</t>
   </si>
   <si>
     <t>Sebagai visual content designer, buatkan struktur carousel Instagram [SLIDES] slide tentang [TOPIK]. Goal: [GOAL]. Akhiri dengan [CTA]. Untuk setiap slide, berikan: (1) headline/title, (2) 2-3 bullet points atau visual element, (3) design suggestion (warna, layout, imagery). Slide 1 harus hook yang stop scroll. Slide terakhir harus CTA yang clear. Buat flow yang logical dan visually appealing.</t>
   </si>
   <si>
-    <t>[TOPIK]: topik carousel; [SLIDES]: jumlah slide (5-10); [GOAL]: tujuan (educate/entertain/promote); [CTA]: call-to-action di slide terakhir</t>
+    <t>[TOPIK]: topik carousel; [SLIDES]: jumlah slide (5-10); [GOAL]: tujuan (edukasi/hiburan/promosi); [CTA]: ajakan bertindak (CTA) di slide terakhir</t>
   </si>
   <si>
     <t>Struktur carousel lengkap dengan design directions</t>
@@ -1510,10 +1510,10 @@
     <t>T-082</t>
   </si>
   <si>
-    <t>Reel Concept Generator</t>
-  </si>
-  <si>
-    <t>Membuat konsep Reels yang engaging</t>
+    <t>Generator Konsep Reel</t>
+  </si>
+  <si>
+    <t>Membuat konsep Reels yang mengundang interaksi</t>
   </si>
   <si>
     <t>Sebagai Reels creator, buatkan 5 konsep video [DURASI] detik tentang [TOPIK] dengan style [STYLE]. Jika ada produk [PRODUCT], integrate secara natural. Untuk setiap konsep, berikan: (1) hook 3 detik pertama, (2) main content flow, (3) transition ideas, (4) music/sound recommendation, (5) text overlay suggestions, (6) CTA. Pastikan konsep sesuai dengan trend Reels saat ini.</t>
@@ -1528,7 +1528,7 @@
     <t>T-083</t>
   </si>
   <si>
-    <t>Story Series Planner</t>
+    <t>Perencana Seri Story</t>
   </si>
   <si>
     <t>Merencanakan series Instagram Stories</t>
@@ -1546,7 +1546,7 @@
     <t>T-084</t>
   </si>
   <si>
-    <t>Infographic Content Structure</t>
+    <t>Struktur Konten Infografis</t>
   </si>
   <si>
     <t>Membuat struktur infographic yang informative</t>
@@ -1564,10 +1564,10 @@
     <t>T-085</t>
   </si>
   <si>
-    <t>Meme Concept Generator</t>
-  </si>
-  <si>
-    <t>Membuat konsep meme yang relatable dan shareable</t>
+    <t>Generator Konsep Meme</t>
+  </si>
+  <si>
+    <t>Membuat konsep meme yang terasa dekat dan mudah dibagikan</t>
   </si>
   <si>
     <t>Sebagai meme creator, buatkan 5 konsep meme tentang [SITUASI] di industri [INDUSTRI]. Tone: [TONE]. Jika ada produk [PRODUCT], integrate secara subtle tidak hard-sell. Untuk setiap konsep, berikan: (1) meme format (Drake/Distracted Boyfriend/Two Buttons/etc), (2) top text, (3) bottom text, (4) why it's relatable, (5) caption untuk post. Pastikan meme appropriate dan tidak offensive.</t>
@@ -1582,7 +1582,7 @@
     <t>T-086</t>
   </si>
   <si>
-    <t>Before-After Photo Concept</t>
+    <t>Konsep Foto Before-After</t>
   </si>
   <si>
     <t>Merencanakan foto perbandingan sebelum dan sesudah yang jujur</t>
@@ -1600,7 +1600,7 @@
     <t>T-087</t>
   </si>
   <si>
-    <t>Flat Lay Layout Guide</t>
+    <t>Panduan Tata Letak Flat Lay</t>
   </si>
   <si>
     <t>Menyusun foto produk dari atas dengan properti pendukung</t>
@@ -1618,7 +1618,7 @@
     <t>T-088</t>
   </si>
   <si>
-    <t>Tutorial Carousel Structure</t>
+    <t>Struktur Carousel Tutorial</t>
   </si>
   <si>
     <t>Menyusun carousel yang mengajarkan langkah demi langkah</t>
@@ -1636,7 +1636,7 @@
     <t>T-089</t>
   </si>
   <si>
-    <t>Quote Graphics Series</t>
+    <t>Seri Grafis Kutipan</t>
   </si>
   <si>
     <t>Membuat rangkaian grafik kutipan yang konsisten</t>
@@ -1654,7 +1654,7 @@
     <t>T-090</t>
   </si>
   <si>
-    <t>Data Visualization Concept</t>
+    <t>Konsep Visualisasi Data</t>
   </si>
   <si>
     <t>Mengubah data menjadi visual yang mudah dipahami</t>
@@ -1672,7 +1672,7 @@
     <t>T-091</t>
   </si>
   <si>
-    <t>Product in Use Photo Concept</t>
+    <t>Konsep Foto Produk Sedang Dipakai</t>
   </si>
   <si>
     <t>Menunjukkan produk dipakai dalam situasi nyata</t>
@@ -1690,7 +1690,7 @@
     <t>T-092</t>
   </si>
   <si>
-    <t>Packaging Showcase Plan</t>
+    <t>Rencana Pameran Kemasan</t>
   </si>
   <si>
     <t>Memperlihatkan kemasan produk sebagai bagian dari pengalaman</t>
@@ -1708,7 +1708,7 @@
     <t>T-093</t>
   </si>
   <si>
-    <t>Day in the Life Video Outline</t>
+    <t>Kerangka Video Sehari Bersama Kami</t>
   </si>
   <si>
     <t>Mendokumentasikan sehari dalam bisnis Anda</t>
@@ -1720,13 +1720,13 @@
     <t>[BISNIS]: jenis bisnis Anda; [MOMEN_MENARIK]: momen dalam sehari yang paling menarik; [PESAN]: pesan yang ingin tersampaikan</t>
   </si>
   <si>
-    <t>Outline video day in the life dengan momen jujur</t>
+    <t>Kerangka video sehari bersama pemilik usaha dengan momen jujur</t>
   </si>
   <si>
     <t>T-094</t>
   </si>
   <si>
-    <t>Process Video Script</t>
+    <t>Naskah Video Proses</t>
   </si>
   <si>
     <t>Merekam proses produksi sebagai konten yang memuaskan ditonton</t>
@@ -1744,7 +1744,7 @@
     <t>T-095</t>
   </si>
   <si>
-    <t>Transformation Video Concept</t>
+    <t>Konsep Video Transformasi</t>
   </si>
   <si>
     <t>Video perubahan dari kondisi awal ke akhir</t>
@@ -1762,7 +1762,7 @@
     <t>T-096</t>
   </si>
   <si>
-    <t>Duet and Collab Video Idea</t>
+    <t>Ide Video Duet dan Kolaborasi</t>
   </si>
   <si>
     <t>Merespons atau berkolaborasi dengan konten kreator lain</t>
@@ -1780,7 +1780,7 @@
     <t>T-097</t>
   </si>
   <si>
-    <t>Green Screen Video Script</t>
+    <t>Naskah Video Green Screen</t>
   </si>
   <si>
     <t>Video dengan latar digital untuk penjelasan atau reaksi</t>
@@ -1798,7 +1798,7 @@
     <t>T-098</t>
   </si>
   <si>
-    <t>Stop Motion Concept</t>
+    <t>Konsep Stop Motion</t>
   </si>
   <si>
     <t>Video frame-by-frame yang menghibur dan unik</t>
@@ -1816,7 +1816,7 @@
     <t>T-099</t>
   </si>
   <si>
-    <t>Time Lapse Planning</t>
+    <t>Perencanaan Time Lapse</t>
   </si>
   <si>
     <t>Mempercepat proses panjang menjadi video singkat</t>
@@ -1834,7 +1834,7 @@
     <t>T-100</t>
   </si>
   <si>
-    <t>ASMR Content Concept</t>
+    <t>Konsep Konten ASMR</t>
   </si>
   <si>
     <t>Konten dengan suara yang memuaskan untuk produk tertentu</t>
@@ -1852,7 +1852,7 @@
     <t>T-101</t>
   </si>
   <si>
-    <t>Behind Counter Series</t>
+    <t>Seri Di Balik Meja Kasir</t>
   </si>
   <si>
     <t>Serial konten dari sudut pandang pelaksana (barista, kasir, kurir)</t>
@@ -1870,7 +1870,7 @@
     <t>T-102</t>
   </si>
   <si>
-    <t>Office or Store Tour Video</t>
+    <t>Video Tur Toko atau Kantor</t>
   </si>
   <si>
     <t>Mengajak penonton melihat tempat kerja Anda</t>
@@ -1888,7 +1888,7 @@
     <t>T-103</t>
   </si>
   <si>
-    <t>Team Photo Concept Guide</t>
+    <t>Panduan Konsep Foto Tim</t>
   </si>
   <si>
     <t>Foto tim yang terlihat profesional dan hangat</t>
@@ -1906,7 +1906,7 @@
     <t>T-104</t>
   </si>
   <si>
-    <t>Customer Photo Feature Plan</t>
+    <t>Rencana Sorotan Foto Pelanggan</t>
   </si>
   <si>
     <t>Menampilkan foto pelanggan dengan izin dan apresiasi</t>
@@ -1924,7 +1924,7 @@
     <t>T-105</t>
   </si>
   <si>
-    <t>Unboxing Video Script</t>
+    <t>Naskah Video Unboxing</t>
   </si>
   <si>
     <t>Video membuka paket yang membangun antusiasme</t>
@@ -1942,7 +1942,7 @@
     <t>T-106</t>
   </si>
   <si>
-    <t>Haul Video Concept</t>
+    <t>Konsep Video Haul</t>
   </si>
   <si>
     <t>Menampilkan beberapa produk sekaligus dalam satu video</t>
@@ -1960,7 +1960,7 @@
     <t>T-107</t>
   </si>
   <si>
-    <t>Side-by-Side Comparison Visual</t>
+    <t>Visual Perbandingan Berdampingan</t>
   </si>
   <si>
     <t>Visual perbandingan dua produk atau pilihan</t>
@@ -1978,7 +1978,7 @@
     <t>T-108</t>
   </si>
   <si>
-    <t>Myth-Busting Visual Series</t>
+    <t>Seri Visual Pembongkar Mitos</t>
   </si>
   <si>
     <t>Serial visual yang meluruskan mitos di industri Anda</t>
@@ -1996,7 +1996,7 @@
     <t>T-109</t>
   </si>
   <si>
-    <t>Checklist Graphic Template</t>
+    <t>Templat Grafis Checklist</t>
   </si>
   <si>
     <t>Grafik daftar periksa yang bisa disimpan pembaca</t>
@@ -2014,7 +2014,7 @@
     <t>T-110</t>
   </si>
   <si>
-    <t>Calendar Graphic Design</t>
+    <t>Desain Grafis Kalender</t>
   </si>
   <si>
     <t>Grafik kalender konten atau event untuk pembaca</t>
@@ -2032,7 +2032,7 @@
     <t>T-111</t>
   </si>
   <si>
-    <t>Quiz Visual Concept</t>
+    <t>Konsep Visual Kuis</t>
   </si>
   <si>
     <t>Visual kuis interaktif untuk engagement</t>
@@ -2050,7 +2050,7 @@
     <t>T-112</t>
   </si>
   <si>
-    <t>Challenge Visual Kit</t>
+    <t>Kit Visual Challenge</t>
   </si>
   <si>
     <t>Materi visual untuk challenge yang diikuti audiens</t>
@@ -2068,7 +2068,7 @@
     <t>T-113</t>
   </si>
   <si>
-    <t>Cover Design System untuk Feed</t>
+    <t>Sistem Desain Sampul Feed</t>
   </si>
   <si>
     <t>Menyusun sistem sampul agar feed terlihat rapi dan konsisten</t>
@@ -2086,7 +2086,7 @@
     <t>T-114</t>
   </si>
   <si>
-    <t>Thumbnail Formula untuk Video</t>
+    <t>Formula Thumbnail untuk Video</t>
   </si>
   <si>
     <t>Rumus thumbnail video yang meningkatkan klik</t>
@@ -2104,7 +2104,7 @@
     <t>T-115</t>
   </si>
   <si>
-    <t>B-Roll Shot List Builder</t>
+    <t>Penyusun Daftar Shot B-Roll</t>
   </si>
   <si>
     <t>Daftar shot pendukung yang perlu direkam</t>
@@ -2122,7 +2122,7 @@
     <t>T-116</t>
   </si>
   <si>
-    <t>Video Storyboard Template</t>
+    <t>Templat Storyboard Video</t>
   </si>
   <si>
     <t>Menggambar alur video sebelum merekam</t>
@@ -2140,7 +2140,7 @@
     <t>T-117</t>
   </si>
   <si>
-    <t>Lighting Setup Guide untuk Konten Sederhana</t>
+    <t>Panduan Pencahayaan untuk Konten Sederhana</t>
   </si>
   <si>
     <t>Menyiapkan pencahayaan dengan alat terbatas</t>
@@ -2158,7 +2158,7 @@
     <t>T-118</t>
   </si>
   <si>
-    <t>Prop and Background Checklist</t>
+    <t>Checklist Properti dan Latar</t>
   </si>
   <si>
     <t>Menyiapkan properti dan latar sebelum merekam</t>
@@ -2176,7 +2176,7 @@
     <t>T-119</t>
   </si>
   <si>
-    <t>Content Styling Consistency Guide</t>
+    <t>Panduan Konsistensi Gaya Visual Konten</t>
   </si>
   <si>
     <t>Menjaga konsistensi gaya visual antar konten</t>
@@ -2194,7 +2194,7 @@
     <t>T-120</t>
   </si>
   <si>
-    <t>User-Generated Content Campaign</t>
+    <t>Kampanye UGC</t>
   </si>
   <si>
     <t>Merencanakan campaign yang mendorong UGC</t>
@@ -2212,10 +2212,10 @@
     <t>T-121</t>
   </si>
   <si>
-    <t>Bagian 4: Engagement</t>
-  </si>
-  <si>
-    <t>Comment Response Templates</t>
+    <t>Bagian 4: Interaksi dan Komunitas</t>
+  </si>
+  <si>
+    <t>Templat Balasan Komentar</t>
   </si>
   <si>
     <t>Membalas komentar followers dengan konsisten</t>
@@ -2233,7 +2233,7 @@
     <t>T-122</t>
   </si>
   <si>
-    <t>DM Response Templates</t>
+    <t>Templat Balasan DM</t>
   </si>
   <si>
     <t>Membalas direct message dengan professional</t>
@@ -2251,7 +2251,7 @@
     <t>T-123</t>
   </si>
   <si>
-    <t>Poll dan Question Ideas</t>
+    <t>Ide Polling dan Pertanyaan</t>
   </si>
   <si>
     <t>Membuat interactive content untuk Stories</t>
@@ -2263,13 +2263,13 @@
     <t>[TOPIK]: topik yang ingin didiskusikan; [AUDIENCE]: target audience; [GOAL]: tujuan (engagement/research/feedback); [FUNNEL]: tahap funnel (awareness/consideration/decision)</t>
   </si>
   <si>
-    <t>10 ide interactive content yang engaging</t>
+    <t>10 ide konten interaktif yang mengundang interaksi</t>
   </si>
   <si>
     <t>T-124</t>
   </si>
   <si>
-    <t>Contest dan Giveaway Mechanics</t>
+    <t>Mekanisme Kontes dan Giveaway</t>
   </si>
   <si>
     <t>Merencanakan contest atau giveaway</t>
@@ -2287,25 +2287,25 @@
     <t>T-125</t>
   </si>
   <si>
-    <t>Community Building Strategy</t>
+    <t>Strategi Membangun Komunitas</t>
   </si>
   <si>
     <t>Membangun komunitas yang engaged dan loyal</t>
   </si>
   <si>
-    <t>Sebagai community builder, buatkan strategy untuk membangun komunitas [BRAND] di niche [NICHE] menggunakan [PLATFORM]. Goal: [GOAL]. Include: (1) nama komunitas yang memorable, (2) value proposition untuk member, (3) onboarding process untuk member baru, (4) weekly activities dan rituals, (5) moderation guidelines, (6) engagement triggers, (7) growth tactics, (8) metrics untuk track success. Fokus pada building genuine connections, bukan hanya numbers.</t>
+    <t>Sebagai pembangun komunitas, buatkan strategi untuk membangun komunitas [BRAND] di bidang [NICHE] menggunakan [PLATFORM]. Tujuan: [GOAL]. Sertakan: (1) nama komunitas yang mudah diingat, (2) manfaat nyata untuk anggota, (3) proses penyambutan anggota baru, (4) kegiatan rutin mingguan dan tradisi komunitas, (5) pedoman moderasi, (6) pemicu interaksi antaranggota, (7) taktik pertumbuhan, (8) metrik untuk mengukur keberhasilan. Fokus pada koneksi yang tulus, bukan sekadar jumlah anggota.</t>
   </si>
   <si>
     <t>[BRAND]: nama brand Anda; [NICHE]: niche atau industri; [PLATFORM]: platform utama (Instagram Group/Facebook Group/Discord/Telegram); [GOAL]: tujuan komunitas (support/feedback/advocacy)</t>
   </si>
   <si>
-    <t>Strategy komunitas lengkap dengan implementation plan</t>
+    <t>Strategi komunitas lengkap dengan rencana implementasi</t>
   </si>
   <si>
     <t>T-126</t>
   </si>
   <si>
-    <t>Question Sticker Strategy</t>
+    <t>Strategi Stiker Pertanyaan</t>
   </si>
   <si>
     <t>Mengisi Instagram Story dengan pertanyaan interaktif yang mengundang jawaban</t>
@@ -2323,7 +2323,7 @@
     <t>T-127</t>
   </si>
   <si>
-    <t>This or That Content Series</t>
+    <t>Seri Konten This or That</t>
   </si>
   <si>
     <t>Membuat konten pilihan ganda yang gampang dijawab follower</t>
@@ -2341,7 +2341,7 @@
     <t>T-128</t>
   </si>
   <si>
-    <t>Fill in the Blank Post</t>
+    <t>Post Isi Titik-Titik</t>
   </si>
   <si>
     <t>Membuat kalimat rumpang yang mengundang komentar kreatif</t>
@@ -2359,7 +2359,7 @@
     <t>T-129</t>
   </si>
   <si>
-    <t>Caption This Challenge</t>
+    <t>Challenge Tebak Caption</t>
   </si>
   <si>
     <t>Mengubah foto lucu produk jadi konten yang memancing komentar</t>
@@ -2395,7 +2395,7 @@
     <t>T-131</t>
   </si>
   <si>
-    <t>Challenge Campaign Launcher</t>
+    <t>Peluncur Kampanye Challenge</t>
   </si>
   <si>
     <t>Meluncurkan tantangan multi hari yang membuat audiens ikut berpartisipasi</t>
@@ -2413,7 +2413,7 @@
     <t>T-132</t>
   </si>
   <si>
-    <t>Live Session Planner</t>
+    <t>Perencana Sesi Live</t>
   </si>
   <si>
     <t>Menyusun alur siaran langsung tanya jawab yang tidak melantur</t>
@@ -2431,7 +2431,7 @@
     <t>T-133</t>
   </si>
   <si>
-    <t>Live Shopping Script</t>
+    <t>Naskah Live Shopping</t>
   </si>
   <si>
     <t>Menjalankan live shopping yang menjual produk secara terstruktur</t>
@@ -2449,7 +2449,7 @@
     <t>T-134</t>
   </si>
   <si>
-    <t>Feedback Request Campaign</t>
+    <t>Kampanye Permintaan Masukan</t>
   </si>
   <si>
     <t>Meminta masukan pelanggan dengan cara yang menghasilkan jawaban jujur</t>
@@ -2467,7 +2467,7 @@
     <t>T-135</t>
   </si>
   <si>
-    <t>Customer Survey Design</t>
+    <t>Desain Survei Pelanggan</t>
   </si>
   <si>
     <t>Menyusun survei pelanggan yang dijawab banyak orang</t>
@@ -2485,7 +2485,7 @@
     <t>T-136</t>
   </si>
   <si>
-    <t>Beta Tester Invitation</t>
+    <t>Undangan Penguji Beta</t>
   </si>
   <si>
     <t>Mengundang pelanggan setia mencoba produk baru sebelum diluncurkan</t>
@@ -2503,7 +2503,7 @@
     <t>T-137</t>
   </si>
   <si>
-    <t>Ambassador Program Blueprint</t>
+    <t>Cetak Biru Program Ambassador</t>
   </si>
   <si>
     <t>Membangun program duta merek dari pelanggan yang paling antusias</t>
@@ -2521,7 +2521,7 @@
     <t>T-138</t>
   </si>
   <si>
-    <t>Loyalty Program Announcement</t>
+    <t>Pengumuman Program Loyalitas</t>
   </si>
   <si>
     <t>Mengumumkan program loyalitas yang membuat pelanggan kembali lagi</t>
@@ -2539,7 +2539,7 @@
     <t>T-139</t>
   </si>
   <si>
-    <t>Referral Program Design</t>
+    <t>Desain Program Referral</t>
   </si>
   <si>
     <t>Membuat program ajak teman yang saling menguntungkan</t>
@@ -2557,7 +2557,7 @@
     <t>T-140</t>
   </si>
   <si>
-    <t>Birthday dan Anniversary Greeting System</t>
+    <t>Sistem Ucapan Ulang Tahun dan Hari Jadi</t>
   </si>
   <si>
     <t>Menyapa pelanggan di hari spesial mereka agar merasa dikenal</t>
@@ -2575,7 +2575,7 @@
     <t>T-141</t>
   </si>
   <si>
-    <t>Re-engagement DM Campaign</t>
+    <t>Kampanye DM Reaktivasi Pelanggan</t>
   </si>
   <si>
     <t>Menghubungi kembali pelanggan yang sudah lama tidak berinteraksi</t>
@@ -2593,7 +2593,7 @@
     <t>T-142</t>
   </si>
   <si>
-    <t>Complaint Handling Response</t>
+    <t>Balasan Penanganan Komplain</t>
   </si>
   <si>
     <t>Merespons komplain pelanggan dengan cepat dan menjaga reputasi</t>
@@ -2611,7 +2611,7 @@
     <t>T-143</t>
   </si>
   <si>
-    <t>Negative Review Response</t>
+    <t>Balasan Ulasan Negatif</t>
   </si>
   <si>
     <t>Menjawab ulasan negatif di marketplace atau Google dengan elegan</t>
@@ -2629,7 +2629,7 @@
     <t>T-144</t>
   </si>
   <si>
-    <t>Testimonial Request Message</t>
+    <t>Pesan Permintaan Testimoni</t>
   </si>
   <si>
     <t>Meminta testimoni dari pelanggan puas tanpa terasa memaksa</t>
@@ -2647,7 +2647,7 @@
     <t>T-145</t>
   </si>
   <si>
-    <t>User Spotlight Series</t>
+    <t>Seri Sorotan Pengguna</t>
   </si>
   <si>
     <t>Menampilkan cerita pelanggan sebagai konten rutin yang membangun kepercayaan</t>
@@ -2665,7 +2665,7 @@
     <t>T-146</t>
   </si>
   <si>
-    <t>Community Guidelines Document</t>
+    <t>Dokumen Pedoman Komunitas</t>
   </si>
   <si>
     <t>Menyusun aturan grup atau komunitas agar tetap sehat dan ramah</t>
@@ -2683,7 +2683,7 @@
     <t>T-147</t>
   </si>
   <si>
-    <t>Moderator Handbook</t>
+    <t>Buku Panduan Moderator</t>
   </si>
   <si>
     <t>Menyiapkan panduan moderator agar pengelolaan komunitas konsisten</t>
@@ -2701,7 +2701,7 @@
     <t>T-148</t>
   </si>
   <si>
-    <t>Welcome Message Series</t>
+    <t>Seri Pesan Sambutan</t>
   </si>
   <si>
     <t>Menyambut follower atau anggota baru agar segera merasa diterima</t>
@@ -2719,7 +2719,7 @@
     <t>T-149</t>
   </si>
   <si>
-    <t>Ethical Engagement Hooks</t>
+    <t>Hook Interaksi yang Etis</t>
   </si>
   <si>
     <t>Membuka konten dengan kalimat yang mengundang interaksi tanpa manipulasi</t>
@@ -2737,7 +2737,7 @@
     <t>T-150</t>
   </si>
   <si>
-    <t>Collab Post Strategy</t>
+    <t>Strategi Post Kolaborasi</t>
   </si>
   <si>
     <t>Memakai fitur kolaborasi Instagram agar konten menjangkau audiens mitra</t>
@@ -2755,7 +2755,7 @@
     <t>T-151</t>
   </si>
   <si>
-    <t>Cross Community Partnership</t>
+    <t>Kemitraan Antar Komunitas</t>
   </si>
   <si>
     <t>Menjalin kerja sama dengan komunitas lain yang audiensnya cocok</t>
@@ -2773,7 +2773,7 @@
     <t>T-152</t>
   </si>
   <si>
-    <t>Influencer Engagement Outreach</t>
+    <t>Pendekatan Kolaborasi Influencer</t>
   </si>
   <si>
     <t>Menghubungi kreator konten untuk kerja sama promosi dengan cara yang dibalas</t>
@@ -2791,7 +2791,7 @@
     <t>T-153</t>
   </si>
   <si>
-    <t>Comment Thread Starter</t>
+    <t>Pemicu Utas Komentar</t>
   </si>
   <si>
     <t>Menulis komentar pembuka di akun besar untuk menarik perhatian audiens baru</t>
@@ -2809,7 +2809,7 @@
     <t>T-154</t>
   </si>
   <si>
-    <t>Story Reply Triage System</t>
+    <t>Sistem Triage Balasan Story</t>
   </si>
   <si>
     <t>Mengelola balasan story yang masuk banyak agar tidak ada yang terlewat</t>
@@ -2827,7 +2827,7 @@
     <t>T-155</t>
   </si>
   <si>
-    <t>Save dan Share Optimization</t>
+    <t>Optimasi Simpan dan Bagikan</t>
   </si>
   <si>
     <t>Merancang konten yang memang sengaja disimpan atau dibagikan audiens</t>
@@ -2845,7 +2845,7 @@
     <t>T-156</t>
   </si>
   <si>
-    <t>Response Time SLA Planner</t>
+    <t>Perencana SLA Waktu Respons</t>
   </si>
   <si>
     <t>Menetapkan standar waktu balas pesan agar pelanggan tidak kabur</t>
@@ -2863,7 +2863,7 @@
     <t>T-157</t>
   </si>
   <si>
-    <t>Engagement Rate Booster Plan</t>
+    <t>Rencana Peningkatan Engagement Rate</t>
   </si>
   <si>
     <t>Menaikkan engagement rate yang sedang stagnan dalam 30 hari</t>
@@ -2881,7 +2881,7 @@
     <t>T-158</t>
   </si>
   <si>
-    <t>Silent Follower Reactivation</t>
+    <t>Reaktivasi Pengikut Pasif</t>
   </si>
   <si>
     <t>Membangunkan follower yang tidak pernah berinteraksi sama sekali</t>
@@ -2899,7 +2899,7 @@
     <t>T-159</t>
   </si>
   <si>
-    <t>Post Purchase Follow Up</t>
+    <t>Tindak Lanjut Setelah Pembelian</t>
   </si>
   <si>
     <t>Menjaga hubungan dengan pembeli setelah transaksi agar repeat order</t>
@@ -2917,7 +2917,7 @@
     <t>T-160</t>
   </si>
   <si>
-    <t>Crisis Communication Templates</t>
+    <t>Templat Komunikasi Krisis</t>
   </si>
   <si>
     <t>Menangani situasi krisis atau komplain viral</t>
@@ -2935,16 +2935,16 @@
     <t>T-161</t>
   </si>
   <si>
-    <t>Bagian 5: Analytics and Optimization</t>
-  </si>
-  <si>
-    <t>Monthly Performance Report</t>
+    <t>Bagian 5: Analitik dan Optimasi</t>
+  </si>
+  <si>
+    <t>Laporan Performa Bulanan</t>
   </si>
   <si>
     <t>Membuat laporan performa social media bulanan</t>
   </si>
   <si>
-    <t>Sebagai social media analyst, buatkan template laporan performa [PLATFORM] untuk periode [PERIODE]. Metrics: [METRICS]. Goal: [GOAL]. Include: (1) executive summary (3-5 kalimat), (2) key metrics overview dengan comparison vs bulan lalu, (3) top performing content analysis (5 posts terbaik), (4) underperforming content analysis (3 posts terburuk), (5) audience insights, (6) competitor benchmarking, (7) recommendations untuk bulan depan (5 action items), (8) next month goals. Format dalam bahasa yang mudah dipahami non-technical stakeholders.</t>
+    <t>Sebagai analis media sosial, buatkan template laporan performa [PLATFORM] untuk periode [PERIODE]. Metrik: [METRICS]. Tujuan: [GOAL]. Sertakan: (1) ringkasan eksekutif (3-5 kalimat), (2) gambaran umum metrik utama dibanding bulan lalu, (3) analisis konten berperforma terbaik (5 posting teratas), (4) analisis konten berperforma terendah (3 posting terbawah), (5) wawasan tentang audiens, (6) perbandingan dengan kompetitor, (7) rekomendasi untuk bulan depan (5 tindakan), (8) target bulan berikutnya. Gunakan bahasa yang mudah dipahami orang non-teknis.</t>
   </si>
   <si>
     <t>[PERIODE]: bulan yang dilaporkan; [PLATFORM]: platform yang dianalisis; [METRICS]: metrics yang di-track (followers/engagement/reach/conversions); [GOAL]: goal bulanan</t>
@@ -2956,7 +2956,7 @@
     <t>T-162</t>
   </si>
   <si>
-    <t>A/B Testing Ideas Generator</t>
+    <t>Generator Ide Pengujian A/B</t>
   </si>
   <si>
     <t>Merencanakan eksperimen untuk optimasi konten</t>
@@ -2968,67 +2968,67 @@
     <t>[ELEMENT]: element yang ingin di-test (caption/image/timing/hashtag/format); [HYPOTHESIS]: hipotesis yang ingin dibuktikan; [METRIC]: metric sukses (engagement rate/click-through/conversion); [DURASI]: lama test (1-4 minggu)</t>
   </si>
   <si>
-    <t>5 A/B testing ideas lengkap dengan implementation plan</t>
+    <t>5 ide pengujian A/B lengkap dengan rencana implementasi</t>
   </si>
   <si>
     <t>T-163</t>
   </si>
   <si>
-    <t>Growth Strategy Planner</t>
+    <t>Perencana Strategi Pertumbuhan</t>
   </si>
   <si>
     <t>Merencanakan strategi pertumbuhan followers</t>
   </si>
   <si>
-    <t>Sebagai growth strategist, buatkan 90-day growth plan untuk [PLATFORM] dari [CURRENT_FOLLOWERS] ke [TARGET_FOLLOWERS]. Resources: [RESOURCES]. Include: (1) current state analysis (strengths/weaknesses/opportunities), (2) growth levers (organic/paid/partnerships), (3) monthly milestones, (4) weekly action items, (5) content strategy adjustments, (6) engagement tactics, (7) collaboration opportunities, (8) budget allocation (jika ada), (9) KPIs untuk track progress, (10) risk mitigation plan. Fokus pada sustainable growth, bukan vanity metrics.</t>
+    <t>Sebagai ahli strategi pertumbuhan, buatkan rencana pertumbuhan 90 hari untuk [PLATFORM] dari [CURRENT_FOLLOWERS] ke [TARGET_FOLLOWERS]. Sumber daya: [RESOURCES]. Sertakan: (1) analisis kondisi saat ini (kekuatan/kelemahan/peluang), (2) tuas pertumbuhan (organik/berbayar/kolaborasi), (3) tonggak capaian bulanan, (4) daftar tindakan mingguan, (5) penyesuaian strategi konten, (6) taktik meningkatkan interaksi, (7) peluang kolaborasi, (8) alokasi anggaran (jika ada), (9) KPI untuk memantau kemajuan, (10) rencana mengatasi risiko. Fokus pada pertumbuhan yang berkelanjutan, bukan sekadar angka kosong.</t>
   </si>
   <si>
     <t>[PLATFORM]: platform yang ingin ditumbuhkan; [CURRENT_FOLLOWERS]: jumlah followers saat ini; [TARGET_FOLLOWERS]: target followers dalam 3-6 bulan; [RESOURCES]: resources yang tersedia (time/budget/team)</t>
   </si>
   <si>
-    <t>90-day growth plan lengkap dengan action items</t>
+    <t>Rencana pertumbuhan 90 hari lengkap dengan daftar tindakan</t>
   </si>
   <si>
     <t>T-164</t>
   </si>
   <si>
-    <t>Content Performance Analysis</t>
+    <t>Analisis Performa Konten</t>
   </si>
   <si>
     <t>Menganalisis kenapa konten tertentu perform baik/buruk</t>
   </si>
   <si>
-    <t>Sebagai content strategist, analisis performa konten [PERIODE]. Top content: [TOP_CONTENT]. Bottom content: [BOTTOM_CONTENT]. Metrics: [METRICS]. Berikan: (1) pattern analysis (apa persamaan top content), (2) anti-pattern analysis (apa persamaan bottom content), (3) audience behavior insights, (4) content format preferences, (5) optimal posting times, (6) hashtag effectiveness, (7) caption length correlation, (8) 5 actionable recommendations untuk improve future content. Gunakan data-driven approach.</t>
+    <t>Sebagai perencana konten, analisis performa konten [PERIODE]. Konten terbaik: [TOP_CONTENT]. Konten terlemah: [BOTTOM_CONTENT]. Metrik: [METRICS]. Berikan: (1) analisis pola (apa persamaan konten terbaik), (2) analisis anti-pola (apa persamaan konten terlemah), (3) wawasan perilaku audiens, (4) preferensi format konten, (5) waktu posting paling optimal, (6) efektivitas hashtag, (7) korelasi panjang caption dengan hasil, (8) 5 rekomendasi yang bisa langsung diterapkan untuk konten ke depan. Gunakan pendekatan berbasis data.</t>
   </si>
   <si>
     <t>[TOP_CONTENT]: 3-5 konten top performing; [BOTTOM_CONTENT]: 3-5 konten bottom performing; [METRICS]: metrics yang dianalisis (reach/engagement/saves/shares); [PERIODE]: periode analisis</t>
   </si>
   <si>
-    <t>Analisis mendalam dengan actionable insights</t>
+    <t>Analisis mendalam dengan wawasan yang bisa langsung ditindaklanjuti</t>
   </si>
   <si>
     <t>T-165</t>
   </si>
   <si>
-    <t>ROI Calculation Template</t>
+    <t>Templat Perhitungan ROI</t>
   </si>
   <si>
     <t>Menghitung return on investment dari social media efforts</t>
   </si>
   <si>
-    <t>Sebagai marketing analyst, buatkan ROI calculation untuk social media efforts [PERIODE]. Costs: [COSTS]. Revenue: [REVENUE]. Goals: [GOALS]. Include: (1) direct ROI calculation (revenue - costs) / costs x 100%, (2) cost per acquisition (CPA), (3) customer lifetime value (CLV) dari social media, (4) brand value metrics (reach/impressions/mentions), (5) engagement value estimation, (6) comparison vs industry benchmarks, (7) recommendations untuk optimize ROI, (8) projection untuk next period. Present dalam format yang mudah dipahami stakeholders.</t>
+    <t>Sebagai analis pemasaran, buatkan perhitungan ROI untuk aktivitas media sosial [PERIODE]. Biaya: [COSTS]. Pendapatan: [REVENUE]. Target: [GOALS]. Sertakan: (1) perhitungan ROI langsung (pendapatan - biaya) / biaya x 100%, (2) biaya per pembelian (CPA), (3) nilai seumur hidup pelanggan (CLV) dari media sosial, (4) metrik nilai merek (jangkauan/tayangan/penyebutan), (5) perkiraan nilai interaksi, (6) perbandingan dengan tolok ukur industri, (7) rekomendasi mengoptimalkan ROI, (8) proyeksi periode berikutnya. Sajikan dalam format yang mudah dipahami pemangku kepentingan.</t>
   </si>
   <si>
     <t>[PERIODE]: periode perhitungan (bulanan/kuartalan/tahunan); [COSTS]: biaya yang dikeluarkan (ads/tools/time); [REVENUE]: revenue yang di-generate (sales/leads/valuasi brand); [GOALS]: goal bisnis utama</t>
   </si>
   <si>
-    <t>ROI report lengkap dengan financial metrics dan recommendations</t>
+    <t>Laporan ROI lengkap dengan metrik keuangan dan rekomendasi</t>
   </si>
   <si>
     <t>T-166</t>
   </si>
   <si>
-    <t>Weekly Metrics Tracker</t>
+    <t>Pelacak Metrik Mingguan</t>
   </si>
   <si>
     <t>Mencatat metrik mingguan agar tren terlihat sejak dini</t>
@@ -3046,7 +3046,7 @@
     <t>T-167</t>
   </si>
   <si>
-    <t>Engagement Rate Calculator</t>
+    <t>Kalkulator Engagement Rate</t>
   </si>
   <si>
     <t>Menghitung engagement rate dengan benar agar tidak salah banding</t>
@@ -3064,7 +3064,7 @@
     <t>T-168</t>
   </si>
   <si>
-    <t>Follower Growth Analysis</t>
+    <t>Analisis Pertumbuhan Pengikut</t>
   </si>
   <si>
     <t>Memahami mengapa followers naik atau turun dalam periode tertentu</t>
@@ -3082,7 +3082,7 @@
     <t>T-169</t>
   </si>
   <si>
-    <t>Best Posting Time Analysis</t>
+    <t>Analisis Waktu Posting Terbaik</t>
   </si>
   <si>
     <t>Menemukan jam posting terbaik dari data sendiri, bukan asumsi umum</t>
@@ -3100,13 +3100,13 @@
     <t>T-170</t>
   </si>
   <si>
-    <t>Hashtag Performance Audit</t>
+    <t>Audit Performa Hashtag</t>
   </si>
   <si>
     <t>Membersihkan dan mengganti hashtag yang tidak lagi membawa reach</t>
   </si>
   <si>
-    <t>Sebagai hashtag strategist, audit daftar hashtag berikut: [HASHTAG_AKTIF] untuk [BISNIS] di [PLATFORM]. Data hasil: [DATA]. Sertakan: klasifikasi setiap hashtag ke 4 lapis (besar jutaan posting, menengah ratusan ribu, kecil puluhan ribu, sangat kecil atau niche), peran tiap lapis dalam strategi reach, mana yang perlu diganti dan mengapa, 20 usulan hashtag baru yang relevan dengan produk dan target saya, dan aturan pemakaian per posting (berapa hashtag, campuran lapis apa). Ingatkan aturan penggunaan hashtag yang aman dari penalti platform.</t>
+    <t>Sebagai ahli strategi hashtag, audit daftar hashtag berikut: [HASHTAG_AKTIF] untuk [BISNIS] di [PLATFORM]. Data hasil: [DATA]. Sertakan: klasifikasi setiap hashtag ke 4 lapis (besar jutaan posting, menengah ratusan ribu, kecil puluhan ribu, sangat kecil atau niche), peran tiap lapis dalam strategi reach, mana yang perlu diganti dan mengapa, 20 usulan hashtag baru yang relevan dengan produk dan target saya, dan aturan pemakaian per posting (berapa hashtag, campuran lapis apa). Ingatkan aturan penggunaan hashtag yang aman dari penalti platform.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang diaudit; [HASHTAG_AKTIF]: daftar hashtag yang sedang dipakai; [DATA]: hasil reach posting dengan hashtag tersebut jika ada</t>
@@ -3118,7 +3118,7 @@
     <t>T-171</t>
   </si>
   <si>
-    <t>Story Analytics Review</t>
+    <t>Telaah Analitik Story</t>
   </si>
   <si>
     <t>Mengevaluasi performa story dan memperbaiki urutan konten story</t>
@@ -3136,7 +3136,7 @@
     <t>T-172</t>
   </si>
   <si>
-    <t>Reel dan Video Performance Analysis</t>
+    <t>Analisis Performa Reel dan Video</t>
   </si>
   <si>
     <t>Mengetahui pola video yang berhasil agar bisa direplikasi</t>
@@ -3154,7 +3154,7 @@
     <t>T-173</t>
   </si>
   <si>
-    <t>Competitor Benchmark Report</t>
+    <t>Laporan Tolok Ukur Kompetitor</t>
   </si>
   <si>
     <t>Membandingkan posisi Anda dengan pesaing secara jujur</t>
@@ -3172,7 +3172,7 @@
     <t>T-174</t>
   </si>
   <si>
-    <t>Sales Funnel Mapping</t>
+    <t>Pemetaan Sales Funnel</t>
   </si>
   <si>
     <t>Memetakan perjalanan audiens dari melihat konten sampai membeli</t>
@@ -3190,7 +3190,7 @@
     <t>T-175</t>
   </si>
   <si>
-    <t>CTR Optimization Analysis</t>
+    <t>Analisis Optimasi CTR</t>
   </si>
   <si>
     <t>Menaikkan jumlah klik dari konten atau iklan dengan memperbaiki elemen pemicu</t>
@@ -3208,7 +3208,7 @@
     <t>T-176</t>
   </si>
   <si>
-    <t>Conversion Tracking Setup</t>
+    <t>Penyiapan Pelacakan Konversi</t>
   </si>
   <si>
     <t>Menyiapkan pencatatan konversi sederhana tanpa alat mahal</t>
@@ -3226,7 +3226,7 @@
     <t>T-177</t>
   </si>
   <si>
-    <t>UTM Builder dan Tracking Guide</t>
+    <t>Panduan Pembuat dan Pelacak UTM</t>
   </si>
   <si>
     <t>Memberi tanda pada setiap tautan agar tahu sumber trafik yang benar</t>
@@ -3244,7 +3244,7 @@
     <t>T-178</t>
   </si>
   <si>
-    <t>Customer Acquisition Cost Calculator</t>
+    <t>Kalkulator Biaya Akuisisi Pelanggan</t>
   </si>
   <si>
     <t>Menghitung biaya mendapatkan satu pembeli agar tidak jual rugi</t>
@@ -3262,7 +3262,7 @@
     <t>T-179</t>
   </si>
   <si>
-    <t>Customer Lifetime Value Estimator</t>
+    <t>Perkiraan Nilai Seumur Hidup Pelanggan</t>
   </si>
   <si>
     <t>Mengestimasi nilai jangka panjang satu pelanggan untuk keputusan promosi</t>
@@ -3280,7 +3280,7 @@
     <t>T-180</t>
   </si>
   <si>
-    <t>Ads Budget Allocation Planner</t>
+    <t>Perencana Alokasi Anggaran Iklan</t>
   </si>
   <si>
     <t>Membagi anggaran iklan ke kanal dan tujuan yang tepat</t>
@@ -3298,7 +3298,7 @@
     <t>T-181</t>
   </si>
   <si>
-    <t>Growth Forecast Model</t>
+    <t>Model Proyeksi Pertumbuhan</t>
   </si>
   <si>
     <t>Membuat proyeksi pertumbuhan yang realistis untuk 3 bulan ke depan</t>
@@ -3316,7 +3316,7 @@
     <t>T-182</t>
   </si>
   <si>
-    <t>KPI Dashboard Setup</t>
+    <t>Penyiapan Dasbor KPI</t>
   </si>
   <si>
     <t>Menyusun satu halaman pantauan berisi angka yang paling menentukan</t>
@@ -3334,7 +3334,7 @@
     <t>T-183</t>
   </si>
   <si>
-    <t>Sentiment Analysis Report</t>
+    <t>Laporan Analisis Sentimen</t>
   </si>
   <si>
     <t>Mengetahui kesan publik terhadap merek dari komentar dan pesan</t>
@@ -3352,7 +3352,7 @@
     <t>T-184</t>
   </si>
   <si>
-    <t>Experiment Log System</t>
+    <t>Sistem Catatan Eksperimen</t>
   </si>
   <si>
     <t>Mencatat uji coba konten agar pembelajaran tidak hilang</t>
@@ -3370,25 +3370,25 @@
     <t>T-185</t>
   </si>
   <si>
-    <t>Quarterly Review Framework</t>
+    <t>Kerangka Telaah Kuartalan</t>
   </si>
   <si>
     <t>Menilai capaian tiga bulan dan menyusun arah kuartal berikutnya</t>
   </si>
   <si>
-    <t>Sebagai strategy review facilitator, fasilitasi review kuartalan [KUARTAL] untuk [BISNIS]. Goal awal: [GOAL]. Capaian: [CAPAIAN]. Sertakan: skor capaian per goal dengan bukti angka, analisis kenapa tiap goal tercapai atau tidak (faktor internal dan eksternal), pembelajaran yang harus dibawa ke kuartal berikutnya, keputusan berhenti, lanjut, atau ubah untuk tiap inisiatif, draf 3 goal kuartal berikutnya dengan metrik pengukuran, dan daftar pertanyaan hard untuk evaluasi diri yang tidak membolehkan jawaban mengambang.</t>
+    <t>Sebagai fasilitator telaah strategi, fasilitasi telaah kuartalan [KUARTAL] untuk [BISNIS]. Goal awal: [GOAL]. Capaian: [CAPAIAN]. Sertakan: skor capaian per goal dengan bukti angka, analisis kenapa tiap goal tercapai atau tidak (faktor internal dan eksternal), pembelajaran yang harus dibawa ke kuartal berikutnya, keputusan berhenti, lanjut, atau ubah untuk tiap inisiatif, draf 3 goal kuartal berikutnya dengan metrik pengukuran, dan daftar pertanyaan berat untuk evaluasi diri yang tidak membolehkan jawaban mengambang.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [KUARTAL]: kuartal yang direview; [CAPAIAN]: data pencapaian kuartal; [GOAL]: goal yang ditetapkan di awal kuartal</t>
   </si>
   <si>
-    <t>Kerangka review kuartalan dengan keputusan per inisiatif dan draf goal baru</t>
+    <t>Kerangka telaah kuartalan dengan keputusan per inisiatif dan draf target baru</t>
   </si>
   <si>
     <t>T-186</t>
   </si>
   <si>
-    <t>Content Gap Analysis</t>
+    <t>Analisis Kesenjangan Konten</t>
   </si>
   <si>
     <t>Menemukan topik yang dicari audiens tetapi belum Anda buat</t>
@@ -3406,7 +3406,7 @@
     <t>T-187</t>
   </si>
   <si>
-    <t>Audience Insights Deep Dive</t>
+    <t>Bedah Mendalam Wawasan Audiens</t>
   </si>
   <si>
     <t>Memahami siapa yang benar benar mengikuti dan membeli dari Anda</t>
@@ -3424,7 +3424,7 @@
     <t>T-188</t>
   </si>
   <si>
-    <t>Reach Decline Diagnosis</t>
+    <t>Diagnosis Penurunan Jangkauan</t>
   </si>
   <si>
     <t>Mendiagnosis mengapa reach turun drastis dan cara pulihkannya</t>
@@ -3442,7 +3442,7 @@
     <t>T-189</t>
   </si>
   <si>
-    <t>Baseline Benchmark Builder</t>
+    <t>Penyusun Tolok Ukur Dasar</t>
   </si>
   <si>
     <t>Menetapkan angka dasar untuk mengukur kemajuan ke depan</t>
@@ -3460,7 +3460,7 @@
     <t>T-190</t>
   </si>
   <si>
-    <t>Traffic Attribution Report</t>
+    <t>Laporan Atribusi Trafik</t>
   </si>
   <si>
     <t>Mengetahui konten atau kanal mana yang benar benar mendatangkan pembeli</t>
@@ -3478,7 +3478,7 @@
     <t>T-191</t>
   </si>
   <si>
-    <t>Cohort Analysis Guide</t>
+    <t>Panduan Analisis Kohort</t>
   </si>
   <si>
     <t>Mengelompokkan pelanggan per bulan masuk untuk melihat siapa yang bertahan</t>
@@ -3496,7 +3496,7 @@
     <t>T-192</t>
   </si>
   <si>
-    <t>Conversion Rate Optimization Checklist</t>
+    <t>Checklist Optimasi Tingkat Konversi</t>
   </si>
   <si>
     <t>Memeriksa titik titik yang menghambat pengunjung menjadi pembeli</t>
@@ -3514,7 +3514,7 @@
     <t>T-193</t>
   </si>
   <si>
-    <t>Monthly Ads Performance Report</t>
+    <t>Laporan Performa Iklan Bulanan</t>
   </si>
   <si>
     <t>Melaporkan hasil iklan bulanan dengan bahasa yang bisa dipahami pemilik usaha</t>
@@ -3532,7 +3532,7 @@
     <t>T-194</t>
   </si>
   <si>
-    <t>Content ROI Ranking</t>
+    <t>Peringkat ROI Konten</t>
   </si>
   <si>
     <t>Mengurutkan konten dari yang paling menghasilkan agar bisa direplikasi</t>
@@ -3550,7 +3550,7 @@
     <t>T-195</t>
   </si>
   <si>
-    <t>Dashboard Review Meeting Agenda</t>
+    <t>Agenda Rapat Telaah Dasbor</t>
   </si>
   <si>
     <t>Menjalankan rapat pantauan angka mingguan yang tidak buang waktu</t>
@@ -3568,7 +3568,7 @@
     <t>T-196</t>
   </si>
   <si>
-    <t>Insights to Action Translator</t>
+    <t>Penerjemah Wawasan ke Tindakan</t>
   </si>
   <si>
     <t>Mengubah data yang sudah dikumpulkan menjadi keputusan konkret</t>
@@ -3586,7 +3586,7 @@
     <t>T-197</t>
   </si>
   <si>
-    <t>Platform Comparison Report</t>
+    <t>Laporan Perbandingan Platform</t>
   </si>
   <si>
     <t>Memutuskan platform mana yang layak difokuskan dan mana yang dilepas</t>
@@ -3604,7 +3604,7 @@
     <t>T-198</t>
   </si>
   <si>
-    <t>Data Collection Checklist</t>
+    <t>Checklist Pengumpulan Data</t>
   </si>
   <si>
     <t>Menyiapkan daftar data yang harus dicatat sejak sekarang agar analisis bisa jalan</t>
@@ -3622,7 +3622,7 @@
     <t>T-199</t>
   </si>
   <si>
-    <t>Annual Metrics Summary</t>
+    <t>Rekap Metrik Tahunan</t>
   </si>
   <si>
     <t>Merangkum capaian setahun menjadi dokumen ringkas untuk refleksi</t>
@@ -3646,13 +3646,13 @@
     <t>Melakukan review strategi tahunan dan planning tahun depan</t>
   </si>
   <si>
-    <t>Sebagai marketing director, buatkan annual strategy review untuk social media [TAHUN_INI] dan planning [TAHUN_DEPAN]. Achievements: [ACHIEVEMENTS]. Challenges: [CHALLENGES]. Goals: [GOALS_DEPAN]. Include: (1) year in review (key metrics dan milestones), (2) what worked well (5 success factors), (3) what didn't work (5 lessons learned), (4) competitive landscape changes, (5) industry trends untuk tahun depan, (6) strategic priorities (3-5 focus areas), (7) quarterly goals dan initiatives, (8) resource requirements (budget/team/tools), (9) risk assessment dan mitigation, (10) success metrics dan tracking plan. Make it comprehensive yet actionable.</t>
+    <t>Sebagai direktur pemasaran, buatkan telaah strategi tahunan media sosial untuk [TAHUN_INI] dan perencanaan [TAHUN_DEPAN]. Pencapaian: [ACHIEVEMENTS]. Tantangan: [CHALLENGES]. Target: [GOALS_DEPAN]. Sertakan: (1) rekap setahun (metrik utama dan momen penting), (2) apa yang berhasil (5 faktor keberhasilan), (3) apa yang tidak berhasil (5 pelajaran), (4) perubahan lanskap kompetisi, (5) tren industri untuk tahun depan, (6) prioritas strategis (3-5 fokus utama), (7) target per kuartal dan inisiatifnya, (8) kebutuhan sumber daya (anggaran/tim/peralatan), (9) penilaian risiko dan cara menguranginya, (10) metrik keberhasilan dan rencana pemantauan. Buat lengkap tapi tetap bisa langsung dieksekusi.</t>
   </si>
   <si>
     <t>[TAHUN_INI]: tahun yang di-review; [TAHUN_DEPAN]: tahun yang direncanakan; [ACHIEVEMENTS]: pencapaian tahun ini; [CHALLENGES]: tantangan yang dihadapi; [GOALS_DEPAN]: goal tahun depan</t>
   </si>
   <si>
-    <t>Annual review dan strategic plan lengkap</t>
+    <t>Telaah tahunan dan rencana strategis lengkap</t>
   </si>
   <si>
     <t>Minggu</t>

--- a/products/200-template-sosmed-premium-premium.xlsx
+++ b/products/200-template-sosmed-premium-premium.xlsx
@@ -11,13 +11,14 @@
     <sheet sheetId="5" name="Catatan Performa" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Praktik Terbaik Platform" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="Checklist Kualitas" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Daftar Variabel" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="1406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2190" uniqueCount="1512">
   <si>
     <t>Kode</t>
   </si>
@@ -49,16 +50,16 @@
     <t>Kalender Konten Bulanan</t>
   </si>
   <si>
-    <t>Membuat planning konten untuk 1 bulan penuh</t>
-  </si>
-  <si>
-    <t>Sebagai perencana konten media sosial, buatkan kalender konten 30 hari untuk [BISNIS] di [PLATFORM]. Posting [FREKUENSI] kali per minggu dengan tujuan [GOAL]. Pilar konten: [PILLAR]. Buat tabel dengan kolom: Tanggal, Hari, Pilar Konten, Ide Konten, Format (gambar/video/carousel/story), Kalimat Pembuka Caption, dan CTA. Variasikan format dan pastikan ada minimal 2 konten edukatif, 1 konten promosi, dan 1 konten pemicu interaksi per minggu.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang digunakan (Instagram/Facebook/TikTok); [FREKUENSI]: berapa kali posting per minggu; [GOAL]: tujuan bulan ini (awareness/sales/engagement); [PILLAR]: 3-5 content pillar bisnis Anda</t>
-  </si>
-  <si>
-    <t>Tabel content calendar 30 hari lengkap dengan detail setiap posting</t>
+    <t>Membuat perencanaan konten untuk 1 bulan penuh</t>
+  </si>
+  <si>
+    <t>Sebagai perencana konten media sosial, buatkan kalender konten 30 hari untuk [BISNIS] di [PLATFORM]. Posting [FREKUENSI] kali per minggu dengan tujuan [TUJUAN]. Pilar konten: [PILLAR]. Buat tabel dengan kolom: Tanggal, Hari, Pilar Konten, Ide Konten, Format (gambar/video/carousel/story), Kalimat Pembuka Caption, dan CTA. Variasikan format dan pastikan ada minimal 2 konten edukatif, 1 konten promosi, dan 1 konten pemicu interaksi per minggu.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang digunakan (Instagram/Facebook/TikTok); [FREKUENSI]: berapa kali posting per minggu; [TUJUAN]: tujuan bulan ini (awareness/penjualan/engagement); [PILLAR]: 3-5 pilar konten bisnis Anda</t>
+  </si>
+  <si>
+    <t>Tabel kalender konten 30 hari lengkap dengan detail setiap posting</t>
   </si>
   <si>
     <t>T-002</t>
@@ -70,10 +71,10 @@
     <t>Menentukan 3-5 topik utama untuk konten Anda</t>
   </si>
   <si>
-    <t>Sebagai brand strategist, tentukan 5 content pillar untuk [BISNIS] yang menjual [PRODUK] kepada [TARGET]. Keahlian kami adalah [KEAHLIAN]. Setiap pillar harus: (1) relevan dengan audience, (2) menunjukkan expertise, (3) mendukung goal bisnis, (4) bisa diproduksi konsisten. Untuk setiap pillar, berikan: nama pillar, deskripsi, contoh 5 ide konten, dan persentase alokasi dari total konten bulanan.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk/jasa yang dijual; [TARGET]: target audience; [KEAHLIAN]: keahlian atau unique selling point</t>
+    <t>Sebagai brand strategist, tentukan 5 content pillar untuk [BISNIS] yang menjual [PRODUK] kepada [AUDIENS]. Keahlian kami adalah [KEAHLIAN]. Setiap pillar harus: (1) relevan dengan audience, (2) menunjukkan expertise, (3) mendukung goal bisnis, (4) bisa diproduksi konsisten. Untuk setiap pillar, berikan: nama pillar, deskripsi, contoh 5 ide konten, dan persentase alokasi dari total konten bulanan.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk/jasa yang dijual; [AUDIENS]: pembeli atau pengikut yang dituju; [KEAHLIAN]: keahlian atau unique selling point</t>
   </si>
   <si>
     <t>5 content pillar lengkap dengan contoh ide dan alokasi persentase</t>
@@ -88,10 +89,10 @@
     <t>Memahami karakteristik dan kebutuhan audience Anda</t>
   </si>
   <si>
-    <t>Sebagai market researcher, buatkan profil audience untuk [BISNIS] yang menjual [PRODUK] kepada usia [USIA] di [LOKASI]. Include: (1) demographic profile, (2) psychographic traits, (3) pain points dan challenges, (4) goals dan aspirations, (5) social media behavior (platform favorit, waktu aktif, jenis konten yang disukai), (6) buying triggers dan objections, (7) 5 persona berbeda dengan nama dan cerita singkat.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk/jasa yang dijual; [USIA]: range usia target audience; [LOKASI]: lokasi geografis target</t>
+    <t>Sebagai market researcher, buatkan profil audience untuk [BISNIS] yang menjual [PRODUK] kepada usia [USIA] di [LOKASI]. Sertakan: (1) demographic profile, (2) psychographic traits, (3) pain points dan challenges, (4) goals dan aspirations, (5) media sosial behavior (platform favorit, waktu aktif, jenis konten yang disukai), (6) buying triggers dan objections, (7) 5 persona berbeda dengan nama dan cerita singkat.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk/jasa yang dijual; [USIA]: rentang usia audiens yang dituju; [LOKASI]: lokasi geografis target</t>
   </si>
   <si>
     <t>Profil audience lengkap dengan 5 persona berbeda</t>
@@ -103,10 +104,10 @@
     <t>Analisis Kompetitor</t>
   </si>
   <si>
-    <t>Menganalisis strategi social media kompetitor</t>
-  </si>
-  <si>
-    <t>Sebagai competitive intelligence analyst, analisis strategi social media [KOMPETITOR_1], [KOMPETITOR_2], dan [KOMPETITOR_3] di [PLATFORM] untuk bisnis [BISNIS]. Buat tabel perbandingan dengan kolom: Nama Kompetitor, Followers, Engagement Rate, Frekuensi Posting, Jenis Konten Dominan, Tone of Voice, Hashtag Strategy, Kekuatan, Kelemahan, dan Peluang untuk [BISNIS]. Berikan 5 rekomendasi strategi yang bisa kita adopsi atau diferensiasi.</t>
+    <t>Menganalisis strategi media sosial kompetitor</t>
+  </si>
+  <si>
+    <t>Sebagai competitive intelligence analyst, analisis strategi media sosial [KOMPETITOR_1], [KOMPETITOR_2], dan [KOMPETITOR_3] di [PLATFORM] untuk bisnis [BISNIS]. Buat tabel perbandingan dengan kolom: Nama Kompetitor, Followers, Engagement Rate, Frekuensi Posting, Jenis Konten Dominan, Tone of Voice, Hashtag Strategy, Kekuatan, Kelemahan, dan Peluang untuk [BISNIS]. Berikan 5 rekomendasi strategi yang bisa kita adopsi atau diferensiasi.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [KOMPETITOR_1]: nama kompetitor pertama; [KOMPETITOR_2]: nama kompetitor kedua; [KOMPETITOR_3]: nama kompetitor ketiga; [PLATFORM]: platform yang dianalisis</t>
@@ -124,10 +125,10 @@
     <t>Membuat 7 ide konten dalam sekali duduk</t>
   </si>
   <si>
-    <t>Sebagai content creator, buatkan 7 ide konten untuk [BISNIS] minggu ini. Content pillar: [PILLAR]. Goal: [GOAL]. Event: [EVENT]. Untuk setiap ide, berikan: (1) judul/hook, (2) format (image/video/carousel/story), (3) angle unik, (4) CTA yang sesuai, (5) estimasi waktu produksi. Variasikan antara konten edukatif, inspiratif, entertaining, dan promotif.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [PILLAR]: content pillar minggu ini; [GOAL]: tujuan minggu ini; [EVENT]: event atau momen spesial (jika ada)</t>
+    <t>Sebagai content creator, buatkan 7 ide konten untuk [BISNIS] minggu ini. Content pillar: [PILLAR]. Goal: [TUJUAN]. Event: [EVENT]. Untuk setiap ide, berikan: (1) judul/hook, (2) format (image/video/carousel/story), (3) angle unik, (4) CTA yang sesuai, (5) estimasi waktu produksi. Variasikan antara konten edukatif, inspiratif, entertaining, dan promotif.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [PILLAR]: content pillar minggu ini; [TUJUAN]: tujuan minggu ini; [EVENT]: event atau momen spesial (jika ada)</t>
   </si>
   <si>
     <t>7 ide konten lengkap dengan detail produksi</t>
@@ -142,10 +143,10 @@
     <t>Menentukan tema besar untuk konten satu bulan penuh</t>
   </si>
   <si>
-    <t>Sebagai social media strategist, tentukan tema konten untuk [BISNIS] sepanjang [BULAN]. Goal bulan ini: [GOAL]. Momen penting: [MOMEN]. Buat 4 tema mingguan yang saling terhubung, untuk setiap tema berikan: nama tema, alasan pemilihan, 5 ide konten, format yang disarankan, dan cara mengukur keberhasilannya. Pastikan tema minggu terakhir mengarah ke konversi penjualan.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [BULAN]: bulan yang direncanakan; [GOAL]: target bisnis bulan itu; [MOMEN]: momen penting dalam bulan tersebut</t>
+    <t>Sebagai media sosial strategist, tentukan tema konten untuk [BISNIS] sepanjang [BULAN]. Goal bulan ini: [TUJUAN]. Momen penting: [MOMEN]. Buat 4 tema mingguan yang saling terhubung, untuk setiap tema berikan: nama tema, alasan pemilihan, 5 ide konten, format yang disarankan, dan cara mengukur keberhasilannya. Pastikan tema minggu terakhir mengarah ke konversi penjualan.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [BULAN]: bulan yang direncanakan; [TUJUAN]: target bisnis bulan itu; [MOMEN]: momen penting dalam bulan tersebut</t>
   </si>
   <si>
     <t>4 tema mingguan dengan ide konten dan metrik keberhasilan</t>
@@ -160,10 +161,10 @@
     <t>Menentukan porsi konten edukasi, promosi, dan hiburan</t>
   </si>
   <si>
-    <t>Sebagai social media planner, hitung rasio konten ideal untuk [BISNIS] di [PLATFORM] dengan goal [GOAL]. Bagi konten menjadi 4 kategori: edukasi, inspirasi, hiburan, dan promosi. Berikan persentase ideal untuk setiap kategori beserta alasannya, contoh topik untuk masing-masing kategori, dan jadwal seminggu yang menerapkan rasio tersebut. Jelaskan juga tanda-tanda rasio perlu diubah.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform utama; [GOAL]: goal utama (awareness/sales/community)</t>
+    <t>Sebagai media sosial planner, hitung rasio konten ideal untuk [BISNIS] di [PLATFORM] dengan goal [TUJUAN]. Bagi konten menjadi 4 kategori: edukasi, inspirasi, hiburan, dan promosi. Berikan persentase ideal untuk setiap kategori beserta alasannya, contoh topik untuk masing-masing kategori, dan jadwal seminggu yang menerapkan rasio tersebut. Jelaskan juga tanda-tanda rasio perlu diubah.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform utama; [TUJUAN]: goal utama (awareness/sales/community)</t>
   </si>
   <si>
     <t>Rasio konten per kategori dengan jadwal contoh seminggu</t>
@@ -232,10 +233,10 @@
     <t>Merencanakan konten untuk peluncuran produk baru</t>
   </si>
   <si>
-    <t>Sebagai launch strategist, buat konten calendar peluncuran [PRODUK] pada [TANGGAL_LAUNCH]. Target: [AUDIENCE], harga: [PRICE_POINT]. Susun konten dari H-14 sampai H+7: fase intrik (H-14 sampai H-8), fase mengungkap (H-7 sampai H-1), fase peluncuran (H-0 sampai H+3), fase testimoni (H+4 sampai H+7). Untuk setiap hari berikan: jenis konten, hook, channel, dan tujuan. Fokuskan konten H-7 ke atas untuk mengumpulkan waitlist.</t>
-  </si>
-  <si>
-    <t>[PRODUK]: produk baru yang akan diluncurkan; [TANGGAL_LAUNCH]: tanggal peluncuran; [AUDIENCE]: target pembeli; [PRICE_POINT]: kisaran harga</t>
+    <t>Sebagai launch strategist, buat konten calendar peluncuran [PRODUK] pada [TANGGAL_LAUNCH]. Target: [AUDIENS], harga: [PRICE_POINT]. Susun konten dari H-14 sampai H+7: fase intrik (H-14 sampai H-8), fase mengungkap (H-7 sampai H-1), fase peluncuran (H-0 sampai H+3), fase testimoni (H+4 sampai H+7). Untuk setiap hari berikan: jenis konten, hook, channel, dan tujuan. Fokuskan konten H-7 ke atas untuk mengumpulkan waitlist.</t>
+  </si>
+  <si>
+    <t>[PRODUK]: produk baru yang akan diluncurkan; [TANGGAL_LAUNCH]: tanggal peluncuran; [AUDIENS]: pembeli atau pengikut yang dituju; [PRICE_POINT]: kisaran harga</t>
   </si>
   <si>
     <t>Kalender 22 hari konten peluncuran lengkap dengan tujuan per hari</t>
@@ -250,7 +251,7 @@
     <t>Menyiapkan konten untuk hari besar nasional dan internasional</t>
   </si>
   <si>
-    <t>Sebagai social media planner, susun konten untuk hari besar berikut: [HARI_BESAR] untuk bisnis [BISNIS]. Untuk setiap hari besar berikan: angle yang menghubungkan hari besar dengan produk (bukan sekadar ucapan), ide konten utama dan pendukung, timing posting, dan apakah perlu promo. Promo yang tersedia: [PROMO]. Hindari konten yang terlihat ikut-ikutan tanpa kaitan nyata dengan bisnis.</t>
+    <t>Sebagai media sosial planner, susun konten untuk hari besar berikut: [HARI_BESAR] untuk bisnis [BISNIS]. Untuk setiap hari besar berikan: angle yang menghubungkan hari besar dengan produk (bukan sekadar ucapan), ide konten utama dan pendukung, timing posting, dan apakah perlu promo. Promo yang tersedia: [PROMO]. Hindari konten yang terlihat ikut-ikutan tanpa kaitan nyata dengan bisnis.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [HARI_BESAR]: daftar hari besar yang relevan; [PROMO]: jenis promo yang tersedia</t>
@@ -304,10 +305,10 @@
     <t>Membuat brief yang jelas untuk konten kreatif</t>
   </si>
   <si>
-    <t>Sebagai creative director, buat template brief konten untuk proyek [PROYEK]. Tujuan: [OBJECTIVE]. Audiens: [AUDIENCE]. Template harus mencakup: satu kalimat pesan inti, apa yang audiens harus lakukan setelah melihat konten, do dan don't, referensi visual, deadline, dan definisi berhasil. Buat versi satu halaman yang bisa diisi dalam 10 menit.</t>
-  </si>
-  <si>
-    <t>[PROYEK]: nama proyek konten; [OBJECTIVE]: tujuan konten; [AUDIENCE]: penerima pesan</t>
+    <t>Sebagai creative director, buat template brief konten untuk proyek [PROYEK]. Tujuan: [OBJECTIVE]. Audiens: [AUDIENS]. Template harus mencakup: satu kalimat pesan inti, apa yang audiens harus lakukan setelah melihat konten, do dan don't, referensi visual, deadline, dan definisi berhasil. Buat versi satu halaman yang bisa diisi dalam 10 menit.</t>
+  </si>
+  <si>
+    <t>[PROYEK]: nama proyek konten; [OBJECTIVE]: tujuan konten; [AUDIENS]: penerima pesan</t>
   </si>
   <si>
     <t>Template brief satu halaman siap pakai</t>
@@ -322,10 +323,10 @@
     <t>Menyusun pedoman suara brand untuk konsistensi konten</t>
   </si>
   <si>
-    <t>Sebagai brand consultant, buat pedoman suara brand untuk [BISNIS] dengan kepribadian [KEPRIBADIAN] dan audiens [AUDIENCE]. Isi pedoman: 3 kata kepribadian beserta artinya dalam praktik menulis, contoh kalimat yang sesuai dan yang tidak sesuai, cara menyapa audiens, kata yang harus selalu dipakai dan yang dihindari, serta cara menyesuaikan tone di platform berbeda tanpa kehilangan identitas.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [KEPRIBADIAN]: 3 kata yang menggambarkan brand; [AUDIENCE]: target audiens</t>
+    <t>Sebagai brand consultant, buat pedoman suara brand untuk [BISNIS] dengan kepribadian [KEPRIBADIAN] dan audiens [AUDIENS]. Isi pedoman: 3 kata kepribadian beserta artinya dalam praktik menulis, contoh kalimat yang sesuai dan yang tidak sesuai, cara menyapa audiens, kata yang harus selalu dipakai dan yang dihindari, serta cara menyesuaikan tone di platform berbeda tanpa kehilangan identitas.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [KEPRIBADIAN]: 3 kata yang menggambarkan brand; [AUDIENS]: target audiens</t>
   </si>
   <si>
     <t>Pedoman suara brand dengan contoh konkret</t>
@@ -358,10 +359,10 @@
     <t>Merencanakan pengumpulan konten dari pelanggan</t>
   </si>
   <si>
-    <t>Sebagai UGC strategist, buat rencana pengumpulan konten pelanggan untuk [PRODUK]. Channel yang dipakai: [CHANNEL]. Insentif yang tersedia: [INSENTIF]. Susun: momen yang tepat meminta konten (setelah pembelian, setelah penggunaan 7 hari, dan seterusnya), kalimat permintaan yang tidak memaksa, cara meminta izin pemakaian, dan sistem pencatatan konten yang masuk. Sertakan 3 template pesan permintaan untuk channel berbeda.</t>
-  </si>
-  <si>
-    <t>[PRODUK]: produk yang dipakai pelanggan; [INSENTIF]: insentif yang bisa ditawarkan; [CHANNEL]: channel komunikasi dengan pelanggan</t>
+    <t>Sebagai UGC strategist, buat rencana pengumpulan konten pelanggan untuk [PRODUK]. Channel yang dipakai: [KANAL]. Insentif yang tersedia: [INSENTIF]. Susun: momen yang tepat meminta konten (setelah pembelian, setelah penggunaan 7 hari, dan seterusnya), kalimat permintaan yang tidak memaksa, cara meminta izin pemakaian, dan sistem pencatatan konten yang masuk. Sertakan 3 template pesan permintaan untuk channel berbeda.</t>
+  </si>
+  <si>
+    <t>[PRODUK]: produk yang dipakai pelanggan; [INSENTIF]: insentif yang bisa ditawarkan; [KANAL]: kanal komunikasi dengan pelanggan</t>
   </si>
   <si>
     <t>Rencana pengumpulan UGC dengan template pesan</t>
@@ -412,7 +413,7 @@
     <t>Memperkirakan hasil engagement dari rencana konten</t>
   </si>
   <si>
-    <t>Sebagai social media analyst, perkirakan hasil engagement dari rencana berikut untuk akun dengan [FOLLOWERS] follower dan engagement rate [ENGAGEMENT_RATA]: [RENCANA]. Hitung perkiraan likes, comments, shares, dan saves untuk setiap konten berdasarkan data historis tersebut. Tunjukkan konten mana yang berpotensi perform terbaik dan mengapa. Berikan satu perubahan pada rencana yang bisa menaikkan total engagement 20 persen.</t>
+    <t>Sebagai media sosial analyst, perkirakan hasil engagement dari rencana berikut untuk akun dengan [FOLLOWERS] follower dan engagement rate [ENGAGEMENT_RATA]: [RENCANA]. Hitung perkiraan likes, comments, shares, dan saves untuk setiap konten berdasarkan data historis tersebut. Tunjukkan konten mana yang berpotensi perform terbaik dan mengapa. Berikan satu perubahan pada rencana yang bisa menaikkan total engagement 20 persen.</t>
   </si>
   <si>
     <t>[FOLLOWERS]: jumlah follower saat ini; [ENGAGEMENT_RATA]: engagement rate rata-rata saat ini; [RENCANA]: rencana konten seminggu</t>
@@ -430,10 +431,10 @@
     <t>Menilai performa konten 3 bulan terakhir</t>
   </si>
   <si>
-    <t>Sebagai content auditor, analisis performa konten periode [PERIODE] dengan data berikut: [DATA]. Goal akun: [GOAL]. Kelompokkan konten menjadi 4 kuadran: performa tinggi dan mudah dibuat (perbanyak), performa tinggi tapi berat produksi (optimalkan proses), performa rendah tapi mudah (perbaiki angle), performa rendah dan berat (hentikan). Untuk setiap kuadran berikan contoh konten dari data dan rekomendasi tindakan spesifik.</t>
-  </si>
-  <si>
-    <t>[PERIODE]: periode audit; [DATA]: ringkasan data performa konten; [GOAL]: goal akun saat ini</t>
+    <t>Sebagai content auditor, analisis performa konten periode [PERIODE] dengan data berikut: [DATA]. Goal akun: [TUJUAN]. Kelompokkan konten menjadi 4 kuadran: performa tinggi dan mudah dibuat (perbanyak), performa tinggi tapi berat produksi (optimalkan proses), performa rendah tapi mudah (perbaiki angle), performa rendah dan berat (hentikan). Untuk setiap kuadran berikan contoh konten dari data dan rekomendasi tindakan spesifik.</t>
+  </si>
+  <si>
+    <t>[PERIODE]: periode audit; [DATA]: ringkasan data performa konten; [TUJUAN]: goal akun saat ini</t>
   </si>
   <si>
     <t>Analisis 4 kuadran dengan rekomendasi tindakan</t>
@@ -538,10 +539,10 @@
     <t>Merencanakan konten untuk mengaktifkan kembali pelanggan lama</t>
   </si>
   <si>
-    <t>Sebagai win-back strategist, rancang kampanye untuk mengaktifkan kembali [SEGMENT]. Penawaran tersedia: [PENAWARAN]. Channel: [CHANNEL]. Susun 3 tahap: mengingatkan nilai (kenapa dulu mereka beli), meminta kabar (apakah ada yang berubah di kebutuhan mereka), dan penawaran spesifik dengan batas waktu. Untuk setiap tahap berikan salinan pesan, timing kirim, dan tanda kapan harus berhenti mengirim agar tidak jadi spam.</t>
-  </si>
-  <si>
-    <t>[SEGMENT]: pelanggan yang tidak aktif (berapa lama tidak beli); [PENAWARAN]: penawaran khusus yang tersedia; [CHANNEL]: channel untuk menjangkau mereka</t>
+    <t>Sebagai win-back strategist, rancang kampanye untuk mengaktifkan kembali [SEGMENT]. Penawaran tersedia: [PENAWARAN]. Channel: [KANAL]. Susun 3 tahap: mengingatkan nilai (kenapa dulu mereka beli), meminta kabar (apakah ada yang berubah di kebutuhan mereka), dan penawaran spesifik dengan batas waktu. Untuk setiap tahap berikan salinan pesan, timing kirim, dan tanda kapan harus berhenti mengirim agar tidak jadi spam.</t>
+  </si>
+  <si>
+    <t>[SEGMENT]: pelanggan yang tidak aktif (berapa lama tidak beli); [PENAWARAN]: penawaran khusus yang tersedia; [KANAL]: channel untuk menjangkau mereka</t>
   </si>
   <si>
     <t>Kampanye win-back 3 tahap dengan batas pengiriman</t>
@@ -559,7 +560,7 @@
     <t>Sebagai event content planner, susun konten untuk [EVENT] pada [TANGGAL] dengan tujuan [TUJUAN]. Buat konten 3 fase: sebelum (pembukaan pendaftaran, pengenalan pembicara, countdown), saat (live update, kutipan pembicara, interaksi peserta), dan sesudah (rekapan, materi gratis, testimonial peserta). Untuk setiap konten berikan format, timing, dan CTA. Sertakan rencana darurat jika pendaftaran lambat di tengah fase sebelum.</t>
   </si>
   <si>
-    <t>[EVENT]: nama dan jenis event; [TANGGAL]: tanggal penyelenggaraan; [TUJUAN]: tujuan event (leads, penjualan, brand)</t>
+    <t>[EVENT]: nama dan jenis event; [TANGGAL]: tanggal penyelenggaraan; [TUJUAN]: tujuan acara (calon pembeli, penjualan, mengenalkan merek)</t>
   </si>
   <si>
     <t>Rencana konten event 3 fase dengan rencana darurat</t>
@@ -574,10 +575,10 @@
     <t>Merencanakan giveaway yang menghasilkan, bukan sekadar viral sesaat</t>
   </si>
   <si>
-    <t>Sebagai giveaway strategist, rancang kampanye giveaway dengan hadiah [HADIAH] untuk tujuan [GOAL]. Budget promosi: [BUDGET_PROMO]. Tentukan: syarat partisipasi yang sejalan dengan goal (jangan minta tag 10 teman jika goal-nya leads), durasi ideal, konten pengumuman dan pengingat, cara memilih pemenang yang transparan, dan konten pasca giveaway untuk mengonversi peserta baru menjadi pengikut yang benar-benar tertarik. Sertakan perhitungan biaya per hasil.</t>
-  </si>
-  <si>
-    <t>[HADIAH]: hadiah yang tersedia; [GOAL]: tujuan giveaway (follower, leads, awareness); [BUDGET_PROMO]: anggaran promosi giveaway</t>
+    <t>Sebagai giveaway strategist, rancang kampanye giveaway dengan hadiah [HADIAH] untuk tujuan [TUJUAN]. Budget promosi: [BUDGET_PROMO]. Tentukan: syarat partisipasi yang sejalan dengan goal (jangan minta tag 10 teman jika goal-nya leads), durasi ideal, konten pengumuman dan pengingat, cara memilih pemenang yang transparan, dan konten pasca giveaway untuk mengonversi peserta baru menjadi pengikut yang benar-benar tertarik. Sertakan perhitungan biaya per hasil.</t>
+  </si>
+  <si>
+    <t>[HADIAH]: hadiah yang tersedia; [TUJUAN]: tujuan giveaway (follower, leads, awareness); [BUDGET_PROMO]: anggaran promosi giveaway</t>
   </si>
   <si>
     <t>Rencana giveaway lengkap dengan perhitungan biaya per hasil</t>
@@ -610,10 +611,10 @@
     <t>Menyiapkan konten darurat sebelum masalah terjadi</t>
   </si>
   <si>
-    <t>Sebagai crisis communication planner, siapkan rencana konten darurat untuk risiko berikut: [RISIKO]. Tim penanggung jawab: [TIM]. Channel resmi: [CHANNEL]. Buat untuk setiap risiko: template pernyataan awal (mengakui masalah tanpa menyalahkan pihak lain), template update kedua (langkah yang diambil), dan template penutup (pemulihan dan pencegahan). Sertakan aturan timing: seberapa cepat harus merespons dan kapan diam lebih baik.</t>
-  </si>
-  <si>
-    <t>[RISIKO]: risiko yang mungkin terjadi di bisnis Anda; [TIM]: siapa yang bertugas saat darurat; [CHANNEL]: channel resmi untuk komunikasi</t>
+    <t>Sebagai crisis communication planner, siapkan rencana konten darurat untuk risiko berikut: [RISIKO]. Tim penanggung jawab: [TIM]. Channel resmi: [KANAL]. Buat untuk setiap risiko: template pernyataan awal (mengakui masalah tanpa menyalahkan pihak lain), template update kedua (langkah yang diambil), dan template penutup (pemulihan dan pencegahan). Sertakan aturan timing: seberapa cepat harus merespons dan kapan diam lebih baik.</t>
+  </si>
+  <si>
+    <t>[RISIKO]: risiko yang mungkin terjadi di bisnis Anda; [TIM]: siapa yang bertugas saat darurat; [KANAL]: channel resmi untuk komunikasi</t>
   </si>
   <si>
     <t>Template konten darurat per risiko dengan aturan timing</t>
@@ -646,10 +647,10 @@
     <t>Memperdalam satu pillar dengan banyak angle</t>
   </si>
   <si>
-    <t>Sebagai ideation specialist, hasulkan 20 angle berbeda untuk pillar [PILLAR] yang ditujukan ke [AUDIENCE] dan berkaitan dengan [PRODUK]. Variasikan angle ke dalam 5 jenis: kesalahan umum, rahasia praktisi, perbandingan pilihan, cerita nyata, dan jawaban skeptis. Untuk setiap angle tulis satu kalimat hook. Tandai 5 angle yang paling jarang dipakai kompetitor, itu yang berpotensi menonjol.</t>
-  </si>
-  <si>
-    <t>[PILLAR]: satu content pillar yang ingin diperdalam; [AUDIENCE]: audiens pillar ini; [PRODUK]: produk yang berkaitan</t>
+    <t>Sebagai ideation specialist, hasulkan 20 angle berbeda untuk pillar [PILLAR] yang ditujukan ke [AUDIENS] dan berkaitan dengan [PRODUK]. Variasikan angle ke dalam 5 jenis: kesalahan umum, rahasia praktisi, perbandingan pilihan, cerita nyata, dan jawaban skeptis. Untuk setiap angle tulis satu kalimat hook. Tandai 5 angle yang paling jarang dipakai kompetitor, itu yang berpotensi menonjol.</t>
+  </si>
+  <si>
+    <t>[PILLAR]: satu content pillar yang ingin diperdalam; [AUDIENS]: audiens pillar ini; [PRODUK]: produk yang berkaitan</t>
   </si>
   <si>
     <t>20 angle terklasifikasi dengan hook dan penanda peluang</t>
@@ -664,10 +665,10 @@
     <t>Menilai performa konten tiap akhir pekan</t>
   </si>
   <si>
-    <t>Sebagai social media coach, bantu saya review konten minggu ini dengan data: [DATA_MINGGU_INI] dan target [TARGET]. Jawab 4 pertanyaan: konten mana yang paling berhasil dan kenapa (pola yang bisa diulang), konten mana yang gagal dan kenapa (pola yang harus dihentikan), apakah ritme posting terjaga, dan satu perubahan spesifik untuk minggu depan. Buat jawaban singkat dan bisa dieksekusi, bukan analisis panjang.</t>
-  </si>
-  <si>
-    <t>[DATA_MINGGU_INI]: statistik konten minggu ini; [TARGET]: target mingguan yang ditetapkan</t>
+    <t>Sebagai media sosial coach, bantu saya review konten minggu ini dengan data: [DATA_MINGGU_INI] dan target [AUDIENS]. Jawab 4 pertanyaan: konten mana yang paling berhasil dan kenapa (pola yang bisa diulang), konten mana yang gagal dan kenapa (pola yang harus dihentikan), apakah ritme posting terjaga, dan satu perubahan spesifik untuk minggu depan. Buat jawaban singkat dan bisa dieksekusi, bukan analisis panjang.</t>
+  </si>
+  <si>
+    <t>[DATA_MINGGU_INI]: statistik konten minggu ini; [AUDIENS]: target mingguan yang ditetapkan</t>
   </si>
   <si>
     <t>Review 4 pertanyaan dengan satu tindakan minggu depan</t>
@@ -682,7 +683,7 @@
     <t>Evaluasi menyeluruh strategi konten bulanan</t>
   </si>
   <si>
-    <t>Sebagai social media strategist, evaluasi bulan ini dengan data [DATA_BULAN] terhadap goal [GOAL_BULAN]. Jawab: apakah goal tercapai dan seberapa jauh, kontribusi tiap jenis konten terhadap goal, keputusan bulan ini yang terbukti tepat dan yang keliru. Lalu tinjau draft rencana bulan depan: [RENCANA_BULAN_DEPAN]. Sarankan perubahan konkret berdasarkan temuan, jangan ubah yang sudah terbukti bekerja.</t>
+    <t>Sebagai media sosial strategist, evaluasi bulan ini dengan data [DATA_BULAN] terhadap goal [GOAL_BULAN]. Jawab: apakah goal tercapai dan seberapa jauh, kontribusi tiap jenis konten terhadap goal, keputusan bulan ini yang terbukti tepat dan yang keliru. Lalu tinjau draft rencana bulan depan: [RENCANA_BULAN_DEPAN]. Sarankan perubahan konkret berdasarkan temuan, jangan ubah yang sudah terbukti bekerja.</t>
   </si>
   <si>
     <t>[DATA_BULAN]: data performa sebulan penuh; [GOAL_BULAN]: goal yang ditetapkan awal bulan; [RENCANA_BULAN_DEPAN]: draft rencana bulan depan</t>
@@ -700,10 +701,10 @@
     <t>Menyegarkan strategi konten setiap 3 bulan</t>
   </si>
   <si>
-    <t>Sebagai strategy consultant, lakukan refresh strategi kuartalan. Hasil kuartal lalu: [HASIL_KUARTAL]. Perubahan pasar: [PERUBAHAN_PASAR]. Goal kuartal depan: [GOAL_KUARTAL_DEPAN]. Tentukan: apa yang dipertahankan (yang sudah terbukti), apa yang dihentikan (yang tidak menyumbang goal), dan apa yang dicoba baru (maksimal 2 eksperimen). Untuk setiap eksperimen tentukan ukuran keberhasilan dan tanggal evaluasi.</t>
-  </si>
-  <si>
-    <t>[HASIL_KUARTAL]: hasil 3 bulan terakhir; [PERUBAHAN_PASAR]: perubahan di pasar atau platform; [GOAL_KUARTAL_DEPAN]: goal 3 bulan ke depan</t>
+    <t>Sebagai konsultan strategi, lakukan penyegaran strategi kuartalan. Hasil kuartal lalu: [HASIL_KUARTAL]. Perubahan pasar: [PERUBAHAN_PASAR]. Goal kuartal depan: [TUJUAN_KUARTAL_DEPAN]. Tentukan: apa yang dipertahankan (yang sudah terbukti), apa yang dihentikan (yang tidak menyumbang tujuan), dan apa yang dicoba baru (maksimal 2 eksperimen). Untuk setiap eksperimen tentukan ukuran keberhasilan dan tanggal evaluasi.</t>
+  </si>
+  <si>
+    <t>[HASIL_KUARTAL]: hasil 3 bulan terakhir; [PERUBAHAN_PASAR]: perubahan di pasar atau platform; [TUJUAN_KUARTAL_DEPAN]: goal 3 bulan ke depan</t>
   </si>
   <si>
     <t>Keputusan pertahankan-hentikan-coba dengan kriteria evaluasi</t>
@@ -754,7 +755,7 @@
     <t>Merencanakan konten untuk momen spesial sepanjang tahun</t>
   </si>
   <si>
-    <t>Sebagai marketing strategist, buatkan seasonal content calendar untuk [BISNIS] di industri [INDUSTRI] tahun [TAHUN]. Include: (1) hari besar nasional dan internasional, (2) momen industri spesifik, (3) season belanja (Ramadhan, Lebaran, Natal, Tahun Baru, dll), (4) event olahraga atau entertainment besar. Untuk setiap momen, berikan: tanggal, nama event, ide konten 7 hari sebelum-sesudah, rekomendasi format, dan estimated engagement boost.</t>
+    <t>Sebagai perancang strategi pemasaran, buatkan kalender konten musiman untuk [BISNIS] di industri [INDUSTRI] tahun [TAHUN]. Sertakan: (1) hari besar nasional dan internasional, (2) momen industri spesifik, (3) season belanja (Ramadhan, Lebaran, Natal, Tahun Baru, dll), (4) acara olahraga atau hiburan besar. Untuk setiap momen, berikan: tanggal, nama event, ide konten 7 hari sebelum-sesudah, rekomendasi format, dan perkiraan tambahan engagement.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [INDUSTRI]: industri bisnis Anda; [TAHUN]: tahun yang direncanakan</t>
@@ -793,10 +794,10 @@
     <t>Membuat post Facebook yang mendorong sharing</t>
   </si>
   <si>
-    <t>Sebagai perencana konten Facebook, tulis post 200 kata tentang [TOPIK] dengan wawasan [INSIGHT] untuk [AUDIENCE]. Tujuan: [GOAL]. Buat post yang: (1) terasa dekat dengan masalah pembaca, (2) memberikan manfaat nyata, (3) mudah dipahami, (4) mendorong pembaca membagikannya. Gunakan format: pertanyaan di awal, cerita atau contoh di tengah, kesimpulan yang bisa dibawa pulang di akhir. Tambahkan 1 CTA yang tidak memaksa jualan.</t>
-  </si>
-  <si>
-    <t>[TOPIK]: topik post; [INSIGHT]: insight atau tips yang dibagikan; [AUDIENCE]: target audience; [GOAL]: goal post (awareness/engagement/traffic)</t>
+    <t>Sebagai perencana konten Facebook, tulis post 200 kata tentang [TOPIK] dengan wawasan [INSIGHT] untuk [AUDIENS]. Tujuan: [TUJUAN]. Buat post yang: (1) terasa dekat dengan masalah pembaca, (2) memberikan manfaat nyata, (3) mudah dipahami, (4) mendorong pembaca membagikannya. Gunakan format: pertanyaan di awal, cerita atau contoh di tengah, kesimpulan yang bisa dibawa pulang di akhir. Tambahkan 1 CTA yang tidak memaksa jualan.</t>
+  </si>
+  <si>
+    <t>[TOPIK]: topik post; [INSIGHT]: insight atau tips yang dibagikan; [AUDIENS]: pembeli atau pengikut yang dituju; [TUJUAN]: goal post (awareness/engagement/traffic)</t>
   </si>
   <si>
     <t>Post Facebook yang mengundang interaksi dan mudah dibagikan</t>
@@ -808,16 +809,16 @@
     <t>Naskah TikTok yang Berpotensi Viral</t>
   </si>
   <si>
-    <t>Membuat script TikTok yang berpotensi viral</t>
-  </si>
-  <si>
-    <t>Sebagai TikTok content creator, buatkan script video [DURASI] detik tentang [TOPIK] yang incorporate trend [TREND]. Jika ada produk [PRODUCT], integrate secara natural. Struktur: (1) hook 3 detik pertama yang stop scroll, (2) setup 5 detik, (3) main content, (4) plot twist atau surprise, (5) CTA. Sertakan: text overlay untuk setiap scene, rekomendasi music/sound, camera angles, dan transition ideas.</t>
-  </si>
-  <si>
-    <t>[TOPIK]: topik video; [DURASI]: durasi video (15/30/60 detik); [TREND]: trend yang sedang viral; [PRODUCT]: produk yang ingin dipromosikan (opsional)</t>
-  </si>
-  <si>
-    <t>Script TikTok lengkap dengan visual directions</t>
+    <t>Membuat naskah TikTok yang berpotensi viral</t>
+  </si>
+  <si>
+    <t>Sebagai TikTok content creator, buatkan naskah video [DURASI] detik tentang [TOPIK] yang incorporate trend [TREND]. Jika ada produk [PRODUK], integrate secara natural. Struktur: (1) hook 3 detik pertama yang stop scroll, (2) setup 5 detik, (3) main content, (4) plot twist atau surprise, (5) CTA. Sertakan: text overlay untuk setiap scene, rekomendasi music/sound, camera angles, dan transition ideas.</t>
+  </si>
+  <si>
+    <t>[TOPIK]: topik video; [DURASI]: durasi video (15/30/60 detik); [TREND]: trend yang sedang viral; [PRODUK]: produk yang ingin dipromosikan (jika ada)</t>
+  </si>
+  <si>
+    <t>Naskah TikTok lengkap dengan petunjuk visual</t>
   </si>
   <si>
     <t>T-044</t>
@@ -829,10 +830,10 @@
     <t>Membuat thread Twitter/X yang educational</t>
   </si>
   <si>
-    <t>Sebagai Twitter/X strategist, buatkan thread 7 tweets tentang [TOPIK]. Poin utama: [POINTS]. Target: [AUDIENCE]. Akhiri dengan [CTA]. Setiap tweet harus: (1) standalone yang bisa dipahami, (2) max 280 karakter, (3) hook di tweet pertama, (4) numbering (1/7, 2/7, dst), (5) 1-2 hashtag relevan per tweet. Buat flow yang logical dan engaging.</t>
-  </si>
-  <si>
-    <t>[TOPIK]: topik thread; [POINTS]: 5-7 poin utama yang ingin disampaikan; [AUDIENCE]: target reader; [CTA]: call-to-action di akhir</t>
+    <t>Sebagai Twitter/X strategist, buatkan thread 7 tweets tentang [TOPIK]. Poin utama: [POINTS]. Target: [AUDIENS]. Akhiri dengan [CTA]. Setiap tweet harus: (1) standalone yang bisa dipahami, (2) max 280 karakter, (3) hook di tweet pertama, (4) numbering (1/7, 2/7, dst), (5) 1-2 hashtag relevan per tweet. Buat flow yang logical dan engaging.</t>
+  </si>
+  <si>
+    <t>[TOPIK]: topik thread; [POINTS]: 5-7 poin utama yang ingin disampaikan; [AUDIENS]: target reader; [CTA]: call-to-action di akhir</t>
   </si>
   <si>
     <t>Thread 7 tweets yang cohesive dan informative</t>
@@ -847,10 +848,10 @@
     <t>Membuat post LinkedIn untuk personal branding</t>
   </si>
   <si>
-    <t>Sebagai LinkedIn ghostwriter, tulis post 300 kata tentang [TOPIK] dari perspektif [EXPERTISE]. Lesson: [LESSON]. Target: [AUDIENCE]. Tone: professional namun conversational. Struktur: (1) hook yang provocative atau surprising, (2) personal story atau case study, (3) 3-5 key takeaways dalam bullet points, (4) reflection atau forward-looking statement, (5) question untuk mendorong engagement. Hindari jargon berlebihan.</t>
-  </si>
-  <si>
-    <t>[TOPIK]: topik post; [EXPERTISE]: bidang keahlian Anda; [LESSON]: pelajaran atau insight yang dibagikan; [AUDIENCE]: target reader (recruiter/client/peer)</t>
+    <t>Sebagai LinkedIn ghostwriter, tulis post 300 kata tentang [TOPIK] dari perspektif [EXPERTISE]. Lesson: [LESSON]. Target: [AUDIENS]. Tone: professional namun conversational. Struktur: (1) hook yang provocative atau surprising, (2) personal story atau case study, (3) 3-5 key takeaways dalam bullet points, (4) reflection atau forward-looking statement, (5) question untuk mendorong engagement. Hindari jargon berlebihan.</t>
+  </si>
+  <si>
+    <t>[TOPIK]: topik post; [EXPERTISE]: bidang keahlian Anda; [LESSON]: pelajaran atau insight yang dibagikan; [AUDIENS]: target reader (recruiter/client/peer)</t>
   </si>
   <si>
     <t>Post LinkedIn yang profesional dan mengundang interaksi</t>
@@ -1027,10 +1028,10 @@
     <t>Memicu komentar dengan pertanyaan yang mudah dijawab</t>
   </si>
   <si>
-    <t>Sebagai engagement writer, buat pertanyaan hari ini tentang [TOPIK] untuk [AUDIENCE] dengan tujuan [GOAL]. Buat 3 opsi pertanyaan dengan tingkat keterbukaan berbeda: pertanyaan fakta yang mudah dijawab, pertanyaan opini yang memicu perbedaan pendapat sehat, dan pertanyaan cerita yang mengundang berbagi pengalaman. Untuk masing-masing tulis hook singkat dan cara Anda akan merespons jawaban yang masuk agar percakapan berlanjut.</t>
-  </si>
-  <si>
-    <t>[TOPIK]: topik pertanyaan; [AUDIENCE]: siapa audiens Anda; [GOAL]: tujuan (memahami audiens, membangun komunitas)</t>
+    <t>Sebagai engagement writer, buat pertanyaan hari ini tentang [TOPIK] untuk [AUDIENS] dengan tujuan [TUJUAN]. Buat 3 opsi pertanyaan dengan tingkat keterbukaan berbeda: pertanyaan fakta yang mudah dijawab, pertanyaan opini yang memicu perbedaan pendapat sehat, dan pertanyaan cerita yang mengundang berbagi pengalaman. Untuk masing-masing tulis hook singkat dan cara Anda akan merespons jawaban yang masuk agar percakapan berlanjut.</t>
+  </si>
+  <si>
+    <t>[TOPIK]: topik pertanyaan; [AUDIENS]: siapa audiens Anda; [TUJUAN]: tujuan (memahami audiens, membangun komunitas)</t>
   </si>
   <si>
     <t>3 opsi pertanyaan dengan rencana respons</t>
@@ -1480,7 +1481,7 @@
     <t>Sebagai perencana konten multi-platform, adaptasi konten inti [KONTEN_INTI] untuk [PLATFORMS]. Gaya bahasa merek: [BRAND_VOICE]. Untuk setiap platform, berikan: (1) panjang caption yang optimal, (2) format yang sesuai, (3) strategi hashtag, (4) CTA yang khas platform tersebut, (5) waktu posting terbaik. Pastikan pesan konsisten tapi format disesuaikan dengan karakter setiap platform.</t>
   </si>
   <si>
-    <t>[KONTEN_INTI]: pesan utama yang ingin disampaikan; [PLATFORMS]: platform target (Instagram, Facebook, Twitter, LinkedIn, TikTok); [BRAND_VOICE]: tone dan style brand Anda</t>
+    <t>[KONTEN_INTI]: pesan utama yang ingin disampaikan; [PLATFORMS]: platform target (Instagram, Facebook, Twitter, LinkedIn, TikTok); [BRAND_VOICE]: gaya bahasa merek Anda</t>
   </si>
   <si>
     <t>5 variasi caption untuk platform berbeda dengan pesan konsisten</t>
@@ -1498,10 +1499,10 @@
     <t>Membuat struktur carousel yang mengundang interaksi</t>
   </si>
   <si>
-    <t>Sebagai visual content designer, buatkan struktur carousel Instagram [SLIDES] slide tentang [TOPIK]. Goal: [GOAL]. Akhiri dengan [CTA]. Untuk setiap slide, berikan: (1) headline/title, (2) 2-3 bullet points atau visual element, (3) design suggestion (warna, layout, imagery). Slide 1 harus hook yang stop scroll. Slide terakhir harus CTA yang clear. Buat flow yang logical dan visually appealing.</t>
-  </si>
-  <si>
-    <t>[TOPIK]: topik carousel; [SLIDES]: jumlah slide (5-10); [GOAL]: tujuan (edukasi/hiburan/promosi); [CTA]: ajakan bertindak (CTA) di slide terakhir</t>
+    <t>Sebagai visual content designer, buatkan struktur carousel Instagram [SLIDES] slide tentang [TOPIK]. Goal: [TUJUAN]. Akhiri dengan [CTA]. Untuk setiap slide, berikan: (1) headline/title, (2) 2-3 bullet points atau visual element, (3) design suggestion (warna, layout, imagery). Slide 1 harus hook yang stop scroll. Slide terakhir harus CTA yang clear. Buat flow yang logical dan visually appealing.</t>
+  </si>
+  <si>
+    <t>[TOPIK]: topik carousel; [SLIDES]: jumlah slide (5-10); [TUJUAN]: tujuan (edukasi/hiburan/promosi); [CTA]: ajakan bertindak (CTA) di slide terakhir</t>
   </si>
   <si>
     <t>Struktur carousel lengkap dengan design directions</t>
@@ -1516,10 +1517,10 @@
     <t>Membuat konsep Reels yang mengundang interaksi</t>
   </si>
   <si>
-    <t>Sebagai Reels creator, buatkan 5 konsep video [DURASI] detik tentang [TOPIK] dengan style [STYLE]. Jika ada produk [PRODUCT], integrate secara natural. Untuk setiap konsep, berikan: (1) hook 3 detik pertama, (2) main content flow, (3) transition ideas, (4) music/sound recommendation, (5) text overlay suggestions, (6) CTA. Pastikan konsep sesuai dengan trend Reels saat ini.</t>
-  </si>
-  <si>
-    <t>[TOPIK]: topik Reels; [DURASI]: durasi (15/30/60 detik); [STYLE]: gaya (tutorial/entertaining/inspirational); [PRODUCT]: produk yang ingin ditampilkan (opsional)</t>
+    <t>Sebagai Reels creator, buatkan 5 konsep video [DURASI] detik tentang [TOPIK] dengan style [STYLE]. Jika ada produk [PRODUK], integrate secara natural. Untuk setiap konsep, berikan: (1) hook 3 detik pertama, (2) main content flow, (3) transition ideas, (4) music/sound recommendation, (5) text overlay suggestions, (6) CTA. Pastikan konsep sesuai dengan trend Reels saat ini.</t>
+  </si>
+  <si>
+    <t>[TOPIK]: topik Reels; [DURASI]: durasi (15/30/60 detik); [STYLE]: gaya (tutorial/entertaining/inspirational); [PRODUK]: produk yang ingin ditampilkan (opsional)</t>
   </si>
   <si>
     <t>5 konsep Reels lengkap dengan production details</t>
@@ -1534,10 +1535,10 @@
     <t>Merencanakan series Instagram Stories</t>
   </si>
   <si>
-    <t>Sebagai Instagram strategist, buatkan [DURASI] hari Instagram Story series tentang [TOPIK]. Goal: [GOAL]. Include interactive elements: [INTERACTIVE]. Untuk setiap hari, berikan: (1) theme hari itu, (2) 3-5 story slides dengan konten, (3) interactive element (poll/quiz/question slider), (4) CTA untuk ke hari berikutnya atau ke link. Buat narrative arc yang membuat orang follow terus.</t>
-  </si>
-  <si>
-    <t>[TOPIK]: topik series; [DURASI]: berapa hari (3-7 hari); [GOAL]: tujuan (engagement/sales/awareness); [INTERACTIVE]: elemen interaktif yang ingin digunakan</t>
+    <t>Sebagai Instagram strategist, buatkan [DURASI] hari Instagram Story series tentang [TOPIK]. Goal: [TUJUAN]. Include interactive elements: [INTERACTIVE]. Untuk setiap hari, berikan: (1) theme hari itu, (2) 3-5 story slides dengan konten, (3) interactive element (poll/quiz/question slider), (4) CTA untuk ke hari berikutnya atau ke link. Buat narrative arc yang membuat orang follow terus.</t>
+  </si>
+  <si>
+    <t>[TOPIK]: topik series; [DURASI]: berapa hari (3-7 hari); [TUJUAN]: tujuan (engagement/sales/awareness); [INTERACTIVE]: elemen interaktif yang ingin digunakan</t>
   </si>
   <si>
     <t>Plan series Stories lengkap dengan interactive elements</t>
@@ -1552,10 +1553,10 @@
     <t>Membuat struktur infographic yang informative</t>
   </si>
   <si>
-    <t>Sebagai infographic designer, buatkan struktur infographic tentang [DATA] untuk [AUDIENCE]. Key message: [KEY_MESSAGE]. Format: [FORMAT]. Include: (1) headline yang catchy, (2) 5-7 section dengan data points, (3) visual hierarchy suggestions, (4) color palette recommendation, (5) icon/imagery ideas. Pastikan informasi mudah dipahami dalam 30 detik.</t>
-  </si>
-  <si>
-    <t>[DATA]: data atau informasi yang ingin divisualkan; [AUDIENCE]: target audience; [KEY_MESSAGE]: pesan utama yang ingin disampaikan; [FORMAT]: format (list/comparison/timeline/process)</t>
+    <t>Sebagai infographic designer, buatkan struktur infographic tentang [DATA] untuk [AUDIENS]. Key message: [KEY_MESSAGE]. Format: [FORMAT]. Sertakan: (1) headline yang catchy, (2) 5-7 section dengan data points, (3) visual hierarchy suggestions, (4) color palette recommendation, (5) icon/imagery ideas. Pastikan informasi mudah dipahami dalam 30 detik.</t>
+  </si>
+  <si>
+    <t>[DATA]: data atau informasi yang ingin divisualkan; [AUDIENS]: pembeli atau pengikut yang dituju; [KEY_MESSAGE]: pesan utama yang ingin disampaikan; [FORMAT]: bentuk penyajian (daftar/perbandingan/garis waktu/langkah)</t>
   </si>
   <si>
     <t>Struktur infographic lengkap dengan design guidelines</t>
@@ -1570,10 +1571,10 @@
     <t>Membuat konsep meme yang terasa dekat dan mudah dibagikan</t>
   </si>
   <si>
-    <t>Sebagai meme creator, buatkan 5 konsep meme tentang [SITUASI] di industri [INDUSTRI]. Tone: [TONE]. Jika ada produk [PRODUCT], integrate secara subtle tidak hard-sell. Untuk setiap konsep, berikan: (1) meme format (Drake/Distracted Boyfriend/Two Buttons/etc), (2) top text, (3) bottom text, (4) why it's relatable, (5) caption untuk post. Pastikan meme appropriate dan tidak offensive.</t>
-  </si>
-  <si>
-    <t>[SITUASI]: situasi atau masalah yang dihadapi audience; [INDUSTRI]: industri bisnis Anda; [TONE]: tone humor (sarcastic/wholesome/self-deprecating); [PRODUCT]: produk yang ingin dipromosikan secara subtle</t>
+    <t>Sebagai meme creator, buatkan 5 konsep meme tentang [SITUASI] di industri [INDUSTRI]. Tone: [TONE]. Jika ada produk [PRODUK], integrate secara subtle tidak hard-sell. Untuk setiap konsep, berikan: (1) meme format (Drake/Distracted Boyfriend/Two Buttons/etc), (2) top text, (3) bottom text, (4) why it's relatable, (5) caption untuk post. Pastikan meme appropriate dan tidak offensive.</t>
+  </si>
+  <si>
+    <t>[SITUASI]: situasi atau masalah yang dihadapi audience; [INDUSTRI]: industri bisnis Anda; [TONE]: gaya humor (sarkastik/hangat/menggertak diri sendiri); [PRODUK]: produk yang ingin dipromosikan secara subtle</t>
   </si>
   <si>
     <t>5 konsep meme lengkap dengan caption</t>
@@ -1732,13 +1733,13 @@
     <t>Merekam proses produksi sebagai konten yang memuaskan ditonton</t>
   </si>
   <si>
-    <t>Sebagai process video planner, susun script video proses [PROSES] durasi [DURASI]. Momen paling memuaskan: [SAAT_MEMUASKAN]. Struktur: tampilkan bahan atau alat awal dengan cepat, kerjakan proses dengan cut yang menjaga ritme, letakkan momen paling memuaskan di 70 persen durasi, tutup dengan hasil akhir. Tentukan: sudut kamera per bagian, kecepatan (real time atau time lapse) per bagian, dan teks penjelas singkat jika perlu. Ritme penting: tidak ada bagian yang berlarut.</t>
+    <t>Sebagai process video planner, susun naskah video proses [PROSES] durasi [DURASI]. Momen paling memuaskan: [SAAT_MEMUASKAN]. Struktur: tampilkan bahan atau alat awal dengan cepat, kerjakan proses dengan cut yang menjaga ritme, letakkan momen paling memuaskan di 70 persen durasi, tutup dengan hasil akhir. Tentukan: sudut kamera per bagian, kecepatan (real time atau time lapse) per bagian, dan teks penjelas singkat jika perlu. Ritme penting: tidak ada bagian yang berlarut.</t>
   </si>
   <si>
     <t>[PROSES]: proses yang direkam; [DURASI]: durasi video; [SAAT_MEMUASKAN]: momen paling memuaskan dalam proses</t>
   </si>
   <si>
-    <t>Script proses video dengan ritme dan momen memuaskan</t>
+    <t>Naskah proses video dengan ritme dan momen memuaskan</t>
   </si>
   <si>
     <t>T-095</t>
@@ -1786,13 +1787,13 @@
     <t>Video dengan latar digital untuk penjelasan atau reaksi</t>
   </si>
   <si>
-    <t>Sebagai green screen script writer, tulis script video tentang [TOPIK] dengan latar [VISUAL_LATAR]. Poin: [POIN]. Struktur: hook 3 detik dengan Anda di frame dan satu visual pendukung, untuk tiap poin tentukan visual latar yang muncul dan kapan, teks besar di layar untuk poin kunci, penutup dengan CTA. Tulis instruksi per segmen: apa yang Anda katakan, apa yang muncul di latar, kapan transisi terjadi.</t>
+    <t>Sebagai green screen naskah writer, tulis naskah video tentang [TOPIK] dengan latar [VISUAL_LATAR]. Poin: [POIN]. Struktur: hook 3 detik dengan Anda di frame dan satu visual pendukung, untuk tiap poin tentukan visual latar yang muncul dan kapan, teks besar di layar untuk poin kunci, penutup dengan CTA. Tulis instruksi per segmen: apa yang Anda katakan, apa yang muncul di latar, kapan transisi terjadi.</t>
   </si>
   <si>
     <t>[TOPIK]: topik yang dibahas; [VISUAL_LATAR]: visual latar yang dibutuhkan; [POIN]: poin-poin yang disampaikan</t>
   </si>
   <si>
-    <t>Script green screen dengan instruksi visual per segmen</t>
+    <t>Naskah green screen dengan instruksi visual per segmen</t>
   </si>
   <si>
     <t>T-098</t>
@@ -1930,13 +1931,13 @@
     <t>Video membuka paket yang membangun antusiasme</t>
   </si>
   <si>
-    <t>Sebagai unboxing script writer, susun script unboxing [PRODUK] dengan detail kemasan [DETIL_KEMASAN]. Reaksi harus jujur: [REAKSI]. Struktur: tampilkan paket luar sebelum dibuka, proses membuka tanpa dipotong agar jujur, reaksi pertama saat melihat produk, sorot detail satu per satu, uji coba singkat, kesimpulan jujur termasuk kekurangan jika ada. Unboxing yang hanya memuji terasa iklan; yang jujur lebih dipercaya.</t>
+    <t>Sebagai unboxing naskah writer, susun naskah unboxing [PRODUK] dengan detail kemasan [DETIL_KEMASAN]. Reaksi harus jujur: [REAKSI]. Struktur: tampilkan paket luar sebelum dibuka, proses membuka tanpa dipotong agar jujur, reaksi pertama saat melihat produk, sorot detail satu per satu, uji coba singkat, kesimpulan jujur termasuk kekurangan jika ada. Unboxing yang hanya memuji terasa iklan; yang jujur lebih dipercaya.</t>
   </si>
   <si>
     <t>[PRODUK]: produk yang dibuka; [DETIL_KEMASAN]: detail kemasan yang layak disorot; [REAKSI]: reaksi jujur yang diharapkan</t>
   </si>
   <si>
-    <t>Script unboxing dengan alur dan reaksi jujur</t>
+    <t>Naskah unboxing dengan alur dan reaksi jujur</t>
   </si>
   <si>
     <t>T-106</t>
@@ -2200,10 +2201,10 @@
     <t>Merencanakan campaign yang mendorong UGC</t>
   </si>
   <si>
-    <t>Sebagai campaign strategist, buatkan UGC campaign untuk [BRAND] yang mempromosikan [PRODUCT]. Goal: [GOAL]. Insentif: [INCENTIVE]. Include: (1) nama campaign yang catchy, (2) hashtag campaign, (3) mekanisme partisipasi, (4) kriteria konten yang diharapkan, (5) timeline campaign (2-4 minggu), (6) cara seleksi pemenang, (7) strategi amplifikasi, (8) template announcement post. Pastikan campaign mudah diikuti dan motivating.</t>
-  </si>
-  <si>
-    <t>[BRAND]: nama brand Anda; [PRODUCT]: produk yang ingin dipromosikan; [GOAL]: tujuan campaign (awareness/sales/engagement); [INCENTIVE]: insentif untuk partisipan</t>
+    <t>Sebagai campaign strategist, buatkan UGC campaign untuk [BRAND] yang mempromosikan [PRODUK]. Goal: [TUJUAN]. Insentif: [INCENTIVE]. Sertakan: (1) nama campaign yang catchy, (2) hashtag campaign, (3) mekanisme partisipasi, (4) kriteria konten yang diharapkan, (5) timeline campaign (2-4 minggu), (6) cara seleksi pemenang, (7) strategi amplifikasi, (8) template announcement post. Pastikan campaign mudah diikuti dan motivating.</t>
+  </si>
+  <si>
+    <t>[BRAND]: nama brand Anda; [PRODUK]: produk yang ingin dipromosikan; [TUJUAN]: tujuan campaign (awareness/sales/engagement); [INCENTIVE]: insentif untuk partisipan</t>
   </si>
   <si>
     <t>Plan UGC campaign lengkap dengan mekanisme dan timeline</t>
@@ -2221,10 +2222,10 @@
     <t>Membalas komentar followers dengan konsisten</t>
   </si>
   <si>
-    <t>Sebagai community manager, buatkan 5 template balasan untuk komentar [JENIS_KOMENTAR] di social media [BRAND_VOICE]. Jika terkait [PRODUCT], mention secara natural. Akhiri dengan [CTA] jika appropriate. Setiap template harus: (1) personal dan authentic, (2) max 50 kata, (3) sesuai brand voice, (4) mendorong conversation lanjut. Include variasi untuk situasi berbeda.</t>
-  </si>
-  <si>
-    <t>[JENIS_KOMENTAR]: jenis komentar (positive/question/complaint/compliment); [BRAND_VOICE]: tone dan style brand Anda; [PRODUCT]: produk yang terkait (jika ada); [CTA]: call-to-action yang ingin disampaikan</t>
+    <t>Sebagai community manager, buatkan 5 template balasan untuk komentar [JENIS_KOMENTAR] di media sosial [BRAND_VOICE]. Jika terkait [PRODUK], mention secara natural. Akhiri dengan [CTA] jika appropriate. Setiap template harus: (1) personal dan authentic, (2) max 50 kata, (3) sesuai brand voice, (4) mendorong conversation lanjut. Include variasi untuk situasi berbeda.</t>
+  </si>
+  <si>
+    <t>[JENIS_KOMENTAR]: jenis komentar (positif/pertanyaan/keluhan/pujian); [BRAND_VOICE]: gaya bahasa merek Anda; [PRODUK]: produk yang terkait (jika ada); [CTA]: call-to-action yang ingin disampaikan</t>
   </si>
   <si>
     <t>5 template balasan komentar yang versatile</t>
@@ -2239,10 +2240,10 @@
     <t>Membalas direct message dengan professional</t>
   </si>
   <si>
-    <t>Sebagai customer service specialist, buatkan 3 template balasan DM [JENIS_DM] untuk [BRAND]. Goal: [GOAL]. Tone: [TONE]. Setiap template harus: (1) acknowledge pesan dengan nama customer, (2) jawab pertanyaan atau address concern, (3) berikan next step yang jelas, (4) akhiri dengan question atau CTA yang mendorong response. Include bagian yang bisa dipersonalisasi.</t>
-  </si>
-  <si>
-    <t>[JENIS_DM]: jenis DM (inquiry/complaint/collaboration/general); [BRAND]: nama brand Anda; [GOAL]: tujuan balasan (convert/retain/inform); [TONE]: tone komunikasi (friendly/professional/casual)</t>
+    <t>Sebagai customer service specialist, buatkan 3 template balasan DM [JENIS_DM] untuk [BRAND]. Goal: [TUJUAN]. Tone: [TONE]. Setiap template harus: (1) acknowledge pesan dengan nama customer, (2) jawab pertanyaan atau address concern, (3) berikan next step yang jelas, (4) akhiri dengan question atau CTA yang mendorong response. Include bagian yang bisa dipersonalisasi.</t>
+  </si>
+  <si>
+    <t>[JENIS_DM]: jenis DM (inquiry/complaint/collaboration/general); [BRAND]: nama brand Anda; [TUJUAN]: tujuan balasan (convert/retain/inform); [TONE]: tone komunikasi (friendly/professional/casual)</t>
   </si>
   <si>
     <t>3 template DM yang professional dan personal</t>
@@ -2257,10 +2258,10 @@
     <t>Membuat interactive content untuk Stories</t>
   </si>
   <si>
-    <t>Sebagai engagement strategist, buatkan 10 ide poll dan question untuk Stories tentang [TOPIK] untuk [AUDIENCE]. Goal: [GOAL]. Funnel stage: [FUNNEL]. Untuk setiap ide, berikan: (1) type (poll/quiz/question slider/emoji slider), (2) question text, (3) options (untuk poll/quiz), (4) follow-up action berdasarkan jawaban. Variasikan antara fun, insightful, dan actionable questions.</t>
-  </si>
-  <si>
-    <t>[TOPIK]: topik yang ingin didiskusikan; [AUDIENCE]: target audience; [GOAL]: tujuan (engagement/research/feedback); [FUNNEL]: tahap funnel (awareness/consideration/decision)</t>
+    <t>Sebagai engagement strategist, buatkan 10 ide poll dan question untuk Stories tentang [TOPIK] untuk [AUDIENS]. Goal: [TUJUAN]. Funnel stage: [FUNNEL]. Untuk setiap ide, berikan: (1) type (poll/quiz/question slider/emoji slider), (2) question text, (3) options (untuk poll/quiz), (4) follow-up action berdasarkan jawaban. Variasikan antara fun, insightful, dan actionable questions.</t>
+  </si>
+  <si>
+    <t>[TOPIK]: topik yang ingin didiskusikan; [AUDIENS]: pembeli atau pengikut yang dituju; [TUJUAN]: tujuan (engagement/research/feedback); [FUNNEL]: tahap funnel (awareness/consideration/decision)</t>
   </si>
   <si>
     <t>10 ide konten interaktif yang mengundang interaksi</t>
@@ -2275,10 +2276,10 @@
     <t>Merencanakan contest atau giveaway</t>
   </si>
   <si>
-    <t>Sebagai campaign manager, buatkan mechanics untuk contest [PRIZE] dengan goal [GOAL]. Durasi: [DURASI]. Mechanics: [MECHANICS]. Include: (1) nama contest yang catchy, (2) rules dan syarat partisipasi (5-7 poin), (3) step-by-step cara ikut, (4) kriteria pemenang, (5) timeline announcement, (6) disclaimer dan legal notes, (7) caption announcement post, (8) reminder posts (3 variasi), (9) winner announcement template. Pastikan mechanics mudah dipahami dan motivating.</t>
-  </si>
-  <si>
-    <t>[PRIZE]: hadiah yang diberikan; [GOAL]: tujuan (followers/engagement/UGC/sales); [DURASI]: lama contest (3-14 hari); [MECHANICS]: mekanisme yang diinginkan (like+comment/share/UGC)</t>
+    <t>Sebagai campaign manager, buatkan mechanics untuk contest [PRIZE] dengan goal [TUJUAN]. Durasi: [DURASI]. Mechanics: [MECHANICS]. Sertakan: (1) nama contest yang catchy, (2) rules dan syarat partisipasi (5-7 poin), (3) step-by-step cara ikut, (4) kriteria pemenang, (5) timeline announcement, (6) disclaimer dan legal notes, (7) caption announcement post, (8) reminder posts (3 variasi), (9) winner announcement template. Pastikan mechanics mudah dipahami dan motivating.</t>
+  </si>
+  <si>
+    <t>[PRIZE]: hadiah yang diberikan; [TUJUAN]: tujuan (followers/engagement/UGC/sales); [DURASI]: lama contest (3-14 hari); [MECHANICS]: mekanisme yang diinginkan (like+comment/share/UGC)</t>
   </si>
   <si>
     <t>Plan contest lengkap dengan semua template komunikasi</t>
@@ -2293,10 +2294,10 @@
     <t>Membangun komunitas yang engaged dan loyal</t>
   </si>
   <si>
-    <t>Sebagai pembangun komunitas, buatkan strategi untuk membangun komunitas [BRAND] di bidang [NICHE] menggunakan [PLATFORM]. Tujuan: [GOAL]. Sertakan: (1) nama komunitas yang mudah diingat, (2) manfaat nyata untuk anggota, (3) proses penyambutan anggota baru, (4) kegiatan rutin mingguan dan tradisi komunitas, (5) pedoman moderasi, (6) pemicu interaksi antaranggota, (7) taktik pertumbuhan, (8) metrik untuk mengukur keberhasilan. Fokus pada koneksi yang tulus, bukan sekadar jumlah anggota.</t>
-  </si>
-  <si>
-    <t>[BRAND]: nama brand Anda; [NICHE]: niche atau industri; [PLATFORM]: platform utama (Instagram Group/Facebook Group/Discord/Telegram); [GOAL]: tujuan komunitas (support/feedback/advocacy)</t>
+    <t>Sebagai pembangun komunitas, buatkan strategi untuk membangun komunitas [BRAND] di bidang [NICHE] menggunakan [PLATFORM]. Tujuan: [TUJUAN]. Sertakan: (1) nama komunitas yang mudah diingat, (2) manfaat nyata untuk anggota, (3) proses penyambutan anggota baru, (4) kegiatan rutin mingguan dan tradisi komunitas, (5) pedoman moderasi, (6) pemicu interaksi antaranggota, (7) taktik pertumbuhan, (8) metrik untuk mengukur keberhasilan. Fokus pada koneksi yang tulus, bukan sekadar jumlah anggota.</t>
+  </si>
+  <si>
+    <t>[BRAND]: nama brand Anda; [NICHE]: niche atau industri; [PLATFORM]: platform utama (Instagram Group/Facebook Group/Discord/Telegram); [TUJUAN]: tujuan komunitas (support/feedback/advocacy)</t>
   </si>
   <si>
     <t>Strategi komunitas lengkap dengan rencana implementasi</t>
@@ -2311,10 +2312,10 @@
     <t>Mengisi Instagram Story dengan pertanyaan interaktif yang mengundang jawaban</t>
   </si>
   <si>
-    <t>Sebagai social media strategist, buatkan 10 pertanyaan untuk question sticker Instagram Story [BISNIS] yang menjual [PRODUK]. Konteks kampanye: [MOMEN]. Tujuan: [GOAL]. Untuk setiap pertanyaan berikan: teks pertayaannya, alasan mengapa itu mengundang jawaban, cara memanfaatkan jawaban yang masuk (share ke story, jadi konten baru, atau jadi leads), dan perkiraan tingkat respons (tinggi/sedang/rendah). Campur pertanyaan ringan yang mudah dijawab dengan pertanyaan dalam yang menghasilkan riset pasar.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk atau jasa utama; [MOMEN]: momen atau kampanye yang sedang berjalan; [GOAL]: tujuan sesi tanya jawab (riset/engagement/konversi)</t>
+    <t>Sebagai media sosial strategist, buatkan 10 pertanyaan untuk question sticker Instagram Story [BISNIS] yang menjual [PRODUK]. Konteks kampanye: [MOMEN]. Tujuan: [TUJUAN]. Untuk setiap pertanyaan berikan: teks pertayaannya, alasan mengapa itu mengundang jawaban, cara memanfaatkan jawaban yang masuk (share ke story, jadi konten baru, atau jadi leads), dan perkiraan tingkat respons (tinggi/sedang/rendah). Campur pertanyaan ringan yang mudah dijawab dengan pertanyaan dalam yang menghasilkan riset pasar.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk atau jasa utama; [MOMEN]: momen atau kampanye yang sedang berjalan; [TUJUAN]: tujuan sesi tanya jawab (riset/engagement/konversi)</t>
   </si>
   <si>
     <t>10 pertanyaan sticker siap pakai dengan rencana pemanfaatan jawaban</t>
@@ -2347,10 +2348,10 @@
     <t>Membuat kalimat rumpang yang mengundang komentar kreatif</t>
   </si>
   <si>
-    <t>Sebagai copywriter social media, buatkan [JUMLAH] ide konten "isi bagian kosong" untuk [BISNIS] dengan tone [TONE]. Target: [TARGET]. Setiap ide berupa satu kalimat rumpang yang mudah dilengkapi, misalnya "Aku gak bisa mulai pagi tanpa ___". Untuk setiap ide berikan: kalimat lengkapnya, contoh jawaban yang biasanya muncul, dan cara Anda membalas komentar terbaik agar jadi percakapan panjang. Hindari rumpang yang jawabannya sensitif atau memalukan.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [TARGET]: target audience; [JUMLAH]: berapa ide kalimat yang dibuat; [TONE]: tone brand (santai/profesional/lucu)</t>
+    <t>Sebagai copywriter media sosial, buatkan [JUMLAH] ide konten "isi bagian kosong" untuk [BISNIS] dengan tone [TONE]. Target: [AUDIENS]. Setiap ide berupa satu kalimat rumpang yang mudah dilengkapi, misalnya "Aku gak bisa mulai pagi tanpa ___". Untuk setiap ide berikan: kalimat lengkapnya, contoh jawaban yang biasanya muncul, dan cara Anda membalas komentar terbaik agar jadi percakapan panjang. Hindari rumpang yang jawabannya sensitif atau memalukan.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [AUDIENS]: pembeli atau pengikut yang dituju; [JUMLAH]: berapa ide kalimat yang dibuat; [TONE]: tone brand (santai/profesional/lucu)</t>
   </si>
   <si>
     <t>Daftar kalimat rumpang siap pakai dengan contoh jawaban dan strategi balasan</t>
@@ -2365,10 +2366,10 @@
     <t>Mengubah foto lucu produk jadi konten yang memancing komentar</t>
   </si>
   <si>
-    <t>Sebagai community manager, rancang konten "buatkan caption" untuk foto berikut: [FOTO]. Bisnis: [BISNIS]. Target: [TARGET]. Sertakan: hook pengumuman tantangan, aturan main dalam 3 poin, hadiah untuk caption terpilih: [HADIAH], batas waktu, dan 3 contoh caption milik Anda sendiri untuk memancing peserta pertama. Tulis juga kalimat pengumuman pemenang supaya momen penutupan jadi konten kedua.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [FOTO]: deskripsi foto yang akan dipakai; [TARGET]: target audience; [HADIAH]: hadiah kecil untuk komentar terbaik (opsional)</t>
+    <t>Sebagai community manager, rancang konten "buatkan caption" untuk foto berikut: [FOTO]. Bisnis: [BISNIS]. Target: [AUDIENS]. Sertakan: hook pengumuman tantangan, aturan main dalam 3 poin, hadiah untuk caption terpilih: [HADIAH], batas waktu, dan 3 contoh caption milik Anda sendiri untuk memancing peserta pertama. Tulis juga kalimat pengumuman pemenang supaya momen penutupan jadi konten kedua.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [FOTO]: deskripsi foto yang akan dipakai; [AUDIENS]: pembeli atau pengikut yang dituju; [HADIAH]: hadiah kecil untuk komentar terbaik (opsional)</t>
   </si>
   <si>
     <t>Paket lengkap tantangan caption dari pengumuman sampai penutupan</t>
@@ -2725,10 +2726,10 @@
     <t>Membuka konten dengan kalimat yang mengundang interaksi tanpa manipulasi</t>
   </si>
   <si>
-    <t>Sebagai engagement strategist, buatkan 15 hook pembuka konten yang memancing interaksi jujur untuk [BISNIS] dengan topik [TOPIK]. Target: [TARGET]. Produk: [PRODUK]. Kategori hook: pertanyaan personal, kesepakatan pendapat, kesalahan umum, pengakuan jujur, dan tantangan ringan. Untuk setiap hook tulis kalimatnya dan alasan mengapa orang terdorong merespons. Hindari hook yang meminta like atau follow secara langsung, hook yang mengancam, dan hook yang menipu isi konten. Tandai 3 hook terbaik untuk audiens pemula dan 3 untuk audiens ahli.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk atau jasa utama; [TOPIK]: topik konten yang akan diposting; [TARGET]: target audience</t>
+    <t>Sebagai engagement strategist, buatkan 15 hook pembuka konten yang memancing interaksi jujur untuk [BISNIS] dengan topik [TOPIK]. Target: [AUDIENS]. Produk: [PRODUK]. Kategori hook: pertanyaan personal, kesepakatan pendapat, kesalahan umum, pengakuan jujur, dan tantangan ringan. Untuk setiap hook tulis kalimatnya dan alasan mengapa orang terdorong merespons. Hindari hook yang meminta like atau follow secara langsung, hook yang mengancam, dan hook yang menipu isi konten. Tandai 3 hook terbaik untuk audiens pemula dan 3 untuk audiens ahli.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk atau jasa utama; [TOPIK]: topik konten yang akan diposting; [AUDIENS]: pembeli atau pengikut yang dituju</t>
   </si>
   <si>
     <t>15 hook interaksi terkategori dengan alasan psikologisnya</t>
@@ -2743,10 +2744,10 @@
     <t>Memakai fitur kolaborasi Instagram agar konten menjangkau audiens mitra</t>
   </si>
   <si>
-    <t>Sebagai partnership strategist, susun strategi Instagram Collab dengan [MITRA] untuk [BISNIS]. Topik konten: [TOPIK]. Tujuan: [GOAL]. Sertakan: 5 ide konten kolaborasi yang menguntungkan kedua belah pihak, template pesan pitching kepada mitra yang menjelaskan keuntungan mereka lebih dulu, pembagian tanggung jawab produksi, jadwal posting bersama, cara mengukur keberhasilan dari insight kolab, dan rencana tindak lanjut jika kolab pertama berhasil agar menjadi kerja sama rutin.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [MITRA]: mitra kolaborasi yang dituju; [TOPIK]: topik konten kolaborasi; [GOAL]: tujuan kolaborasi (reach/followers/penjualan)</t>
+    <t>Sebagai partnership strategist, susun strategi Instagram Collab dengan [MITRA] untuk [BISNIS]. Topik konten: [TOPIK]. Tujuan: [TUJUAN]. Sertakan: 5 ide konten kolaborasi yang menguntungkan kedua belah pihak, template pesan pitching kepada mitra yang menjelaskan keuntungan mereka lebih dulu, pembagian tanggung jawab produksi, jadwal posting bersama, cara mengukur keberhasilan dari insight kolab, dan rencana tindak lanjut jika kolab pertama berhasil agar menjadi kerja sama rutin.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [MITRA]: mitra kolaborasi yang dituju; [TOPIK]: topik konten kolaborasi; [TUJUAN]: tujuan kolaborasi (reach/followers/penjualan)</t>
   </si>
   <si>
     <t>Rencana kolaborasi lengkap dari pitching sampai kerja sama lanjutan</t>
@@ -2869,10 +2870,10 @@
     <t>Menaikkan engagement rate yang sedang stagnan dalam 30 hari</t>
   </si>
   <si>
-    <t>Sebagai social media growth specialist, buatkan rencana 30 hari menaikkan engagement [PLATFORM] dari [ENGAGEMENT_SEKARANG] ke [TARGET] untuk [BISNIS]. Sertakan: diagnosis 5 penyebab umum engagement rendah dan cara mengecek mana yang berlaku, perubahan konten minggu pertama sampai keempat, rutinitas interaksi harian 20 menit (komentar ke akun siapa, story apa, balasan apa), 5 ide konten yang berbasis percakapan, metrik yang dicatat tiap minggu, dan tanda rencana perlu diubah. Pastikan taktiknya sesuai algoritma terkini dan tidak melanggar pedoman platform.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang dianalisis; [ENGAGEMENT_SEKARANG]: engagement rate saat ini; [TARGET]: engagement rate yang diinginkan</t>
+    <t>Sebagai media sosial growth specialist, buatkan rencana 30 hari menaikkan engagement [PLATFORM] dari [ENGAGEMENT_SEKARANG] ke [AUDIENS] untuk [BISNIS]. Sertakan: diagnosis 5 penyebab umum engagement rendah dan cara mengecek mana yang berlaku, perubahan konten minggu pertama sampai keempat, rutinitas interaksi harian 20 menit (komentar ke akun siapa, story apa, balasan apa), 5 ide konten yang berbasis percakapan, metrik yang dicatat tiap minggu, dan tanda rencana perlu diubah. Pastikan taktiknya sesuai algoritma terkini dan tidak melanggar pedoman platform.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang dianalisis; [ENGAGEMENT_SEKARANG]: engagement rate saat ini; [AUDIENS]: engagement rate yang diinginkan</t>
   </si>
   <si>
     <t>Rencana 30 hari bertahap dengan rutinitas harian dan metrik mingguan</t>
@@ -2923,7 +2924,7 @@
     <t>Menangani situasi krisis atau komplain viral</t>
   </si>
   <si>
-    <t>Sebagai PR specialist, buatkan crisis communication plan untuk [SITUASI] dengan severity [SEVERITY] di [PLATFORM]. Stakeholder: [STAKEHOLDER]. Include: (1) holding statement (50 kata) untuk immediate response, (2) detailed apology letter (200 kata), (3) FAQ untuk anticipated questions (5-7 Q&amp;A), (4) internal memo untuk tim, (5) follow-up update template, (6) recovery content ideas. Tone harus empathetic, accountable, dan solution-oriented. Hindari defensive language.</t>
+    <t>Sebagai PR specialist, buatkan crisis communication plan untuk [SITUASI] dengan severity [SEVERITY] di [PLATFORM]. Stakeholder: [STAKEHOLDER]. Sertakan: (1) holding statement (50 kata) untuk immediate response, (2) detailed apology letter (200 kata), (3) FAQ untuk anticipated questions (5-7 Q&amp;A), (4) internal memo untuk tim, (5) follow-up update template, (6) recovery content ideas. Tone harus empathetic, accountable, dan solution-oriented. Hindari defensive language.</t>
   </si>
   <si>
     <t>[SITUASI]: jenis krisis (product issue/service failure/miscommunication/public complaint); [SEVERITY]: tingkat keparahan (minor/moderate/major); [PLATFORM]: platform dimana krisis terjadi; [STAKEHOLDER]: pihak yang terdampak</t>
@@ -2941,13 +2942,13 @@
     <t>Laporan Performa Bulanan</t>
   </si>
   <si>
-    <t>Membuat laporan performa social media bulanan</t>
-  </si>
-  <si>
-    <t>Sebagai analis media sosial, buatkan template laporan performa [PLATFORM] untuk periode [PERIODE]. Metrik: [METRICS]. Tujuan: [GOAL]. Sertakan: (1) ringkasan eksekutif (3-5 kalimat), (2) gambaran umum metrik utama dibanding bulan lalu, (3) analisis konten berperforma terbaik (5 posting teratas), (4) analisis konten berperforma terendah (3 posting terbawah), (5) wawasan tentang audiens, (6) perbandingan dengan kompetitor, (7) rekomendasi untuk bulan depan (5 tindakan), (8) target bulan berikutnya. Gunakan bahasa yang mudah dipahami orang non-teknis.</t>
-  </si>
-  <si>
-    <t>[PERIODE]: bulan yang dilaporkan; [PLATFORM]: platform yang dianalisis; [METRICS]: metrics yang di-track (followers/engagement/reach/conversions); [GOAL]: goal bulanan</t>
+    <t>Membuat laporan performa media sosial bulanan</t>
+  </si>
+  <si>
+    <t>Sebagai analis media sosial, buatkan template laporan performa [PLATFORM] untuk periode [PERIODE]. Metrik: [METRIK]. Tujuan: [TUJUAN]. Sertakan: (1) ringkasan eksekutif (3-5 kalimat), (2) gambaran umum metrik utama dibanding bulan lalu, (3) analisis konten berperforma terbaik (5 posting teratas), (4) analisis konten berperforma terendah (3 posting terbawah), (5) wawasan tentang audiens, (6) perbandingan dengan kompetitor, (7) rekomendasi untuk bulan depan (5 tindakan), (8) target bulan berikutnya. Gunakan bahasa yang mudah dipahami orang non-teknis.</t>
+  </si>
+  <si>
+    <t>[PERIODE]: bulan yang dilaporkan; [PLATFORM]: platform yang dianalisis; [METRIK]: metrik yang dicatat (followers/engagement/reach/konversi); [TUJUAN]: tujuan bulan ini</t>
   </si>
   <si>
     <t>Template laporan bulanan lengkap dengan analisis dan rekomendasi</t>
@@ -2962,7 +2963,7 @@
     <t>Merencanakan eksperimen untuk optimasi konten</t>
   </si>
   <si>
-    <t>Sebagai growth hacker, buatkan 5 A/B testing ideas untuk [ELEMENT] dengan hypothesis [HYPOTHESIS]. Success metric: [METRIC]. Durasi: [DURASI]. Untuk setiap test, berikan: (1) test name, (2) variable A description, (3) variable B description, (4) sample size needed, (5) success criteria, (6) implementation steps, (7) potential insights. Prioritaskan tests yang high-impact dan easy-to-implement.</t>
+    <t>Sebagai growth hacker, buatkan 5 A/B testing ideas untuk [ELEMENT] dengan hypothesis [HYPOTHESIS]. Success metric: [METRIC]. Durasi: [DURASI]. Untuk setiap test, berikan: (1) test name, (2) variable A denaskahion, (3) variable B denaskahion, (4) sample size needed, (5) success criteria, (6) implementation steps, (7) potential insights. Prioritaskan tests yang high-impact dan easy-to-implement.</t>
   </si>
   <si>
     <t>[ELEMENT]: element yang ingin di-test (caption/image/timing/hashtag/format); [HYPOTHESIS]: hipotesis yang ingin dibuktikan; [METRIC]: metric sukses (engagement rate/click-through/conversion); [DURASI]: lama test (1-4 minggu)</t>
@@ -2998,10 +2999,10 @@
     <t>Menganalisis kenapa konten tertentu perform baik/buruk</t>
   </si>
   <si>
-    <t>Sebagai perencana konten, analisis performa konten [PERIODE]. Konten terbaik: [TOP_CONTENT]. Konten terlemah: [BOTTOM_CONTENT]. Metrik: [METRICS]. Berikan: (1) analisis pola (apa persamaan konten terbaik), (2) analisis anti-pola (apa persamaan konten terlemah), (3) wawasan perilaku audiens, (4) preferensi format konten, (5) waktu posting paling optimal, (6) efektivitas hashtag, (7) korelasi panjang caption dengan hasil, (8) 5 rekomendasi yang bisa langsung diterapkan untuk konten ke depan. Gunakan pendekatan berbasis data.</t>
-  </si>
-  <si>
-    <t>[TOP_CONTENT]: 3-5 konten top performing; [BOTTOM_CONTENT]: 3-5 konten bottom performing; [METRICS]: metrics yang dianalisis (reach/engagement/saves/shares); [PERIODE]: periode analisis</t>
+    <t>Sebagai perencana konten, analisis performa konten [PERIODE]. Konten terbaik: [TOP_CONTENT]. Konten terlemah: [BOTTOM_CONTENT]. Metrik: [METRIK]. Berikan: (1) analisis pola (apa persamaan konten terbaik), (2) analisis anti-pola (apa persamaan konten terlemah), (3) wawasan perilaku audiens, (4) preferensi format konten, (5) waktu posting paling optimal, (6) efektivitas hashtag, (7) korelasi panjang caption dengan hasil, (8) 5 rekomendasi yang bisa langsung diterapkan untuk konten ke depan. Gunakan pendekatan berbasis data.</t>
+  </si>
+  <si>
+    <t>[TOP_CONTENT]: 3-5 konten top performing; [BOTTOM_CONTENT]: 3-5 konten bottom performing; [METRIK]: metrik yang dianalisis (reach/engagement/simpan/bagikan); [PERIODE]: periode analisis</t>
   </si>
   <si>
     <t>Analisis mendalam dengan wawasan yang bisa langsung ditindaklanjuti</t>
@@ -3013,7 +3014,7 @@
     <t>Templat Perhitungan ROI</t>
   </si>
   <si>
-    <t>Menghitung return on investment dari social media efforts</t>
+    <t>Menghitung return on investment dari media sosial efforts</t>
   </si>
   <si>
     <t>Sebagai analis pemasaran, buatkan perhitungan ROI untuk aktivitas media sosial [PERIODE]. Biaya: [COSTS]. Pendapatan: [REVENUE]. Target: [GOALS]. Sertakan: (1) perhitungan ROI langsung (pendapatan - biaya) / biaya x 100%, (2) biaya per pembelian (CPA), (3) nilai seumur hidup pelanggan (CLV) dari media sosial, (4) metrik nilai merek (jangkauan/tayangan/penyebutan), (5) perkiraan nilai interaksi, (6) perbandingan dengan tolok ukur industri, (7) rekomendasi mengoptimalkan ROI, (8) proyeksi periode berikutnya. Sajikan dalam format yang mudah dipahami pemangku kepentingan.</t>
@@ -3034,10 +3035,10 @@
     <t>Mencatat metrik mingguan agar tren terlihat sejak dini</t>
   </si>
   <si>
-    <t>Sebagai social media analyst, buatkan format tabel pencatatan metrik mingguan untuk [BISNIS] di [PLATFORM]. Metrik yang dipantau: [METRIK]. Target mingguan: [GOAL]. Tabel harus punya kolom: minggu ke, tanggal, nilai tiap metrik, perbandingan dengan minggu lalu, konten terbaik minggu itu, dan satu catatan penyebab naik atau turun. Tambahkan aturan kapan pencatatan dilakukan (hari apa, jam berapa), ambang batas perubahan yang dianggap normal, dan kondisi apa yang harus memicu analisis mendalam.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang dipantau; [METRIK]: metrik yang dicatat (followers/reach/engagement/klik/pesan masuk); [GOAL]: target mingguan</t>
+    <t>Sebagai media sosial analyst, buatkan format tabel pencatatan metrik mingguan untuk [BISNIS] di [PLATFORM]. Metrik yang dipantau: [METRIK]. Target mingguan: [TUJUAN]. Tabel harus punya kolom: minggu ke, tanggal, nilai tiap metrik, perbandingan dengan minggu lalu, konten terbaik minggu itu, dan satu catatan penyebab naik atau turun. Tambahkan aturan kapan pencatatan dilakukan (hari apa, jam berapa), ambang batas perubahan yang dianggap normal, dan kondisi apa yang harus memicu analisis mendalam.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang dipantau; [METRIK]: metrik yang dicatat (followers/reach/engagement/klik/pesan masuk); [TUJUAN]: target mingguan</t>
   </si>
   <si>
     <t>Format tabel pencatatan mingguan siap pakai dengan aturan pemicu analisis</t>
@@ -3052,10 +3053,10 @@
     <t>Menghitung engagement rate dengan benar agar tidak salah banding</t>
   </si>
   <si>
-    <t>Sebagai social media measurement specialist, jelaskan cara menghitung engagement rate untuk [PLATFORM] dengan data berikut: [DATA]. Bisnis: [BISNIS]. Benchmark industri: [BENCHMARK]. Sertakan: rumus engagement per follower, rumus engagement per reach, dan kapan memakai yang mana. Hitung keduanya dari data saya, bandingkan dengan benchmark, dan jelaskan apakah hasil saya sehat, biasa, atau perlu diperbaiki. Tutup dengan 3 faktor yang paling memengaruhi angka saya saat ini dan cara memperbaikinya tanpa konten bayar.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang dihitung; [DATA]: tempel data followers, likes, comments, shares, saves, reach; [BENCHMARK]: perkiraan engagement rata-rata industri Anda</t>
+    <t>Sebagai media sosial measurement specialist, jelaskan cara menghitung engagement rate untuk [PLATFORM] dengan data berikut: [DATA]. Bisnis: [BISNIS]. Benchmark industri: [BENCHMARK]. Sertakan: rumus engagement per follower, rumus engagement per reach, dan kapan memakai yang mana. Hitung keduanya dari data saya, bandingkan dengan benchmark, dan jelaskan apakah hasil saya sehat, biasa, atau perlu diperbaiki. Tutup dengan 3 faktor yang paling memengaruhi angka saya saat ini dan cara memperbaikinya tanpa konten bayar.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang dihitung; [DATA]: tempel data followers, like, komentar, bagikan, simpan, reach; [BENCHMARK]: perkiraan engagement rata-rata industri Anda</t>
   </si>
   <si>
     <t>Perhitungan engagement rate ganda dengan interpretasi dan rekomendasi</t>
@@ -3088,7 +3089,7 @@
     <t>Menemukan jam posting terbaik dari data sendiri, bukan asumsi umum</t>
   </si>
   <si>
-    <t>Sebagai social media analyst, bantu saya menemukan jam posting terbaik untuk [BISNIS] di [PLATFORM]. Profil audiens: [AUDIENS]. Data posting dan hasil yang saya catat: [DATA]. Sertakan: cara membaca data insight bawaan platform untuk jam aktif audiens, hipotesis jam terbaik berdasarkan kebiasaan audiens saya, rencana uji coba 2 minggu dengan pembagian jam yang terukur, tabel pencatatan hasil uji, dan keputusan akhir berdasarkan kriteria apa (reach tertinggi, engagement tertinggi, atau klik terbanyak) karena ketiganya bisa menghasilkan jam yang berbeda.</t>
+    <t>Sebagai media sosial analyst, bantu saya menemukan jam posting terbaik untuk [BISNIS] di [PLATFORM]. Profil audiens: [AUDIENS]. Data posting dan hasil yang saya catat: [DATA]. Sertakan: cara membaca data insight bawaan platform untuk jam aktif audiens, hipotesis jam terbaik berdasarkan kebiasaan audiens saya, rencana uji coba 2 minggu dengan pembagian jam yang terukur, tabel pencatatan hasil uji, dan keputusan akhir berdasarkan kriteria apa (reach tertinggi, engagement tertinggi, atau klik terbanyak) karena ketiganya bisa menghasilkan jam yang berbeda.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang dianalisis; [AUDIENS]: deskripsi kebiasaan audiens (pekerja/karyawan/ibu rumah tangga/pelajar); [DATA]: tempel data jam posting dan hasilnya jika ada</t>
@@ -3145,7 +3146,7 @@
     <t>Sebagai video performance analyst, bandingkan [JUMLAH_VIDEO] video teratas dengan video terbawah untuk [BISNIS] di [PLATFORM]. Data: [DATA]. Sertakan: tabel perbandingan metrik utama, pola yang berulang pada video berhasil (hook, durasi, jenis konten, momen pertama 3 detik), pola yang berulang pada video gagal, poin retention di mana penonton biasa pergi, dan 5 aturan produksi video berikutnya berdasarkan temuan ini. Aturan harus konkret dan bisa dipatuhu saat produksi, bukan saran umum.</t>
   </si>
   <si>
-    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform video yang dianalisis; [DATA]: tempel data video (views, watch time, retention, likes, shares, saves); [JUMLAH_VIDEO]: berapa video teratas dan terbawah yang dibandingkan</t>
+    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform video yang dianalisis; [DATA]: tempel data video (views, durasi tonton, retensi, like, bagikan, simpan); [JUMLAH_VIDEO]: berapa video teratas dan terbawah yang dibandingkan</t>
   </si>
   <si>
     <t>Perbandingan video berhasil dan gagal dengan 5 aturan produksi baru</t>
@@ -3232,7 +3233,7 @@
     <t>Memberi tanda pada setiap tautan agar tahu sumber trafik yang benar</t>
   </si>
   <si>
-    <t>Sebagai analytics specialist, ajari saya memakai parameter UTM untuk [BISNIS]. Tujuan tautan: [TUJUAN]. Kampanye yang perlu ditandai: [KAMPANYE]. Alat pembaca: [ALAT_ANALITIK]. Sertakan: penjelasan tiap parameter (source, medium, campaign, content) dengan contoh dari bisnis saya, daftar tautan lengkap untuk setiap kampanye yang sudah jadi, aturan penamaan konsisten agar data tidak pecah, kesalahan umum yang merusak data (huruf besar kecil beda, spasi, parameter ganda), dan cara membaca hasilnya di alat analitik yang saya pakai.</t>
+    <t>Sebagai analis data, ajari saya memakai parameter UTM untuk [BISNIS]. Tujuan tautan: [TUJUAN]. Kampanye yang perlu ditandai: [KAMPANYE]. Alat pembaca: [ALAT_ANALITIK]. Sertakan: penjelasan tiap parameter (source, medium, campaign, content) dengan contoh dari bisnis saya, daftar tautan lengkap untuk setiap kampanye yang sudah jadi, aturan penamaan konsisten agar data tidak pecah, kesalahan umum yang merusak data (huruf besar kecil beda, spasi, parameter ganda), dan cara membaca hasilnya di alat analitik yang saya pakai.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [KAMPANYE]: daftar kampanye atau kanal yang akan ditandai; [TUJUAN]: halaman yang menerima trafik; [ALAT_ANALITIK]: alat pembaca data (Google Analytics/log server)</t>
@@ -3286,10 +3287,10 @@
     <t>Membagi anggaran iklan ke kanal dan tujuan yang tepat</t>
   </si>
   <si>
-    <t>Sebagai media buyer, buatkan rencana alokasi anggaran iklan [ANGGARAN] per bulan untuk [BISNIS] dengan tujuan [GOAL]. Pilihan kanal: [KANAL]. Sertakan: prinsip pembagian anggaran untuk bisnis kecil (seberapa besar untuk penjualan langsung versus mengenalkan merek, berapa cadangan untuk uji coba), tabel alokasi per kanal dengan alasannya, struktur kampanye minimal di tiap kanal (jangan pecah terlalu kecil), aturan kapan anggaran dipindah antar kanal, metrik evaluasi mingguan, dan kesalahan pemborosan yang paling sering terjadi pada anggaran kecil.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [ANGGARAN]: total anggaran iklan per bulan; [KANAL]: pilihan kanal beriklan yang dipertimbangkan; [GOAL]: tujuan utama iklan (penjualan/daftar/kenal merek)</t>
+    <t>Sebagai media buyer, buatkan rencana alokasi anggaran iklan [ANGGARAN] per bulan untuk [BISNIS] dengan tujuan [TUJUAN]. Pilihan kanal: [KANAL]. Sertakan: prinsip pembagian anggaran untuk bisnis kecil (seberapa besar untuk penjualan langsung versus mengenalkan merek, berapa cadangan untuk uji coba), tabel alokasi per kanal dengan alasannya, struktur kampanye minimal di tiap kanal (jangan pecah terlalu kecil), aturan kapan anggaran dipindah antar kanal, metrik evaluasi mingguan, dan kesalahan pemborosan yang paling sering terjadi pada anggaran kecil.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [ANGGARAN]: total anggaran iklan per bulan; [KANAL]: pilihan kanal beriklan yang dipertimbangkan; [TUJUAN]: tujuan utama iklan (penjualan/daftar/kenal merek)</t>
   </si>
   <si>
     <t>Rencana alokasi anggaran per kanal dengan aturan evaluasi dan pemindahan</t>
@@ -3322,10 +3323,10 @@
     <t>Menyusun satu halaman pantauan berisi angka yang paling menentukan</t>
   </si>
   <si>
-    <t>Sebagai performance analyst, rancang dashboard KPI untuk [BISNIS] dengan goal utama [GOAL] menggunakan [ALAT]. Sumber data: [SUMBER_DATA]. Sertakan: pemilihan maksimal 7 KPI yang benar benar terhubung ke goal (tolak metrik yang cuma bagus dilihat), definisi tiap KPI agar semua orang mengerti sama, struktur layout dashboard dari kiri ke kanan (paling penting lebih dulu), frekuensi update tiap KPI, sumber pengambilan angkanya, dan aturan warna sederhana (hijau aman, kuning perlu perhatian, merah butuh tindakan). Dashboard harus bisa dibuat dalam satu hari.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [GOAL]: goal bisnis utama saat ini; [SUMBER_DATA]: tempat data berasal (platform/penjualan/iklan); [ALAT]: alat dashboard (spreadsheet/notion/berbayar)</t>
+    <t>Sebagai performance analyst, rancang dashboard KPI untuk [BISNIS] dengan goal utama [TUJUAN] menggunakan [ALAT]. Sumber data: [SUMBER_DATA]. Sertakan: pemilihan maksimal 7 KPI yang benar benar terhubung ke goal (tolak metrik yang cuma bagus dilihat), definisi tiap KPI agar semua orang mengerti sama, struktur layout dashboard dari kiri ke kanan (paling penting lebih dulu), frekuensi update tiap KPI, sumber pengambilan angkanya, dan aturan warna sederhana (hijau aman, kuning perlu perhatian, merah butuh tindakan). Dashboard harus bisa dibuat dalam satu hari.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [TUJUAN]: goal bisnis utama saat ini; [SUMBER_DATA]: tempat data berasal (platform/penjualan/iklan); [ALAT]: alat dashboard (spreadsheet/notion/berbayar)</t>
   </si>
   <si>
     <t>Rancangan dashboard KPI maksimal 7 metrik dengan layout dan aturan warna</t>
@@ -3376,10 +3377,10 @@
     <t>Menilai capaian tiga bulan dan menyusun arah kuartal berikutnya</t>
   </si>
   <si>
-    <t>Sebagai fasilitator telaah strategi, fasilitasi telaah kuartalan [KUARTAL] untuk [BISNIS]. Goal awal: [GOAL]. Capaian: [CAPAIAN]. Sertakan: skor capaian per goal dengan bukti angka, analisis kenapa tiap goal tercapai atau tidak (faktor internal dan eksternal), pembelajaran yang harus dibawa ke kuartal berikutnya, keputusan berhenti, lanjut, atau ubah untuk tiap inisiatif, draf 3 goal kuartal berikutnya dengan metrik pengukuran, dan daftar pertanyaan berat untuk evaluasi diri yang tidak membolehkan jawaban mengambang.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [KUARTAL]: kuartal yang direview; [CAPAIAN]: data pencapaian kuartal; [GOAL]: goal yang ditetapkan di awal kuartal</t>
+    <t>Sebagai fasilitator telaah strategi, fasilitasi telaah kuartalan [KUARTAL] untuk [BISNIS]. Goal awal: [TUJUAN]. Capaian: [CAPAIAN]. Sertakan: skor capaian per goal dengan bukti angka, analisis kenapa tiap goal tercapai atau tidak (faktor internal dan eksternal), pembelajaran yang harus dibawa ke kuartal berikutnya, keputusan berhenti, lanjut, atau ubah untuk tiap inisiatif, draf 3 goal kuartal berikutnya dengan metrik pengukuran, dan daftar pertanyaan berat untuk evaluasi diri yang tidak membolehkan jawaban mengambang.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [KUARTAL]: kuartal yang direview; [CAPAIAN]: data pencapaian kuartal; [TUJUAN]: goal yang ditetapkan di awal kuartal</t>
   </si>
   <si>
     <t>Kerangka telaah kuartalan dengan keputusan per inisiatif dan draf target baru</t>
@@ -3448,10 +3449,10 @@
     <t>Menetapkan angka dasar untuk mengukur kemajuan ke depan</t>
   </si>
   <si>
-    <t>Sebagai performance baseline analyst, susun angka dasar untuk [BISNIS] di [PLATFORM] dari data 90 hari berikut: [DATA_90_HARI]. Goal 6 bulan: [GOAL]. Sertakan: perhitungan baseline tiap metrik utama (rata rata, angka terbaik, angka terburuk, tren arah), keputusan metrik mana yang jadi acuan utama dan mana yang hanya dipantau, target pertumbuhan bulanan yang berbasis baseline bukan harapan, tabel sederhana untuk mencatat perkembangan bulanan terhadap baseline, dan aturan review kapan baseline dihitung ulang karena situasi berubah.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang diukur; [DATA_90_HARI]: data performa 90 hari terakhir; [GOAL]: goal 6 bulan ke depan</t>
+    <t>Sebagai performance baseline analyst, susun angka dasar untuk [BISNIS] di [PLATFORM] dari data 90 hari berikut: [DATA_90_HARI]. Goal 6 bulan: [TUJUAN]. Sertakan: perhitungan baseline tiap metrik utama (rata rata, angka terbaik, angka terburuk, tren arah), keputusan metrik mana yang jadi acuan utama dan mana yang hanya dipantau, target pertumbuhan bulanan yang berbasis baseline bukan harapan, tabel sederhana untuk mencatat perkembangan bulanan terhadap baseline, dan aturan review kapan baseline dihitung ulang karena situasi berubah.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang diukur; [DATA_90_HARI]: data performa 90 hari terakhir; [TUJUAN]: goal 6 bulan ke depan</t>
   </si>
   <si>
     <t>Baseline metrik dengan target pertumbuhan bertahap dan tabel pemantauan</t>
@@ -3574,10 +3575,10 @@
     <t>Mengubah data yang sudah dikumpulkan menjadi keputusan konkret</t>
   </si>
   <si>
-    <t>Sebagai data driven strategist, ubah temuan berikut menjadi tindakan untuk [BISNIS]. Goal saat ini: [GOAL]. Kendala: [KENDALA]. Temuan: [TEMUAN]. Sertakan: interpretasi tiap temuan dalam satu kalimat maknanya, tindakan yang disarankan per temuan dengan tingkat dampak dan biaya, peringatan untuk temuan yang menarik tetapi belum layak ditindak, urutan tiga tindakan pertama yang harus dimulai minggu ini dengan alasan urutannya, dan cara mengukur apakah tindakan itu benar benar menjawab temuan awal.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [TEMUAN]: daftar temuan data yang sudah Anda kumpulkan; [GOAL]: goal yang sedang dikejar; [KENDALA]: sumber daya yang tersedia (waktu/anggaran/tim)</t>
+    <t>Sebagai data driven strategist, ubah temuan berikut menjadi tindakan untuk [BISNIS]. Goal saat ini: [TUJUAN]. Kendala: [KENDALA]. Temuan: [TEMUAN]. Sertakan: interpretasi tiap temuan dalam satu kalimat maknanya, tindakan yang disarankan per temuan dengan tingkat dampak dan biaya, peringatan untuk temuan yang menarik tetapi belum layak ditindak, urutan tiga tindakan pertama yang harus dimulai minggu ini dengan alasan urutannya, dan cara mengukur apakah tindakan itu benar benar menjawab temuan awal.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [TEMUAN]: daftar temuan data yang sudah Anda kumpulkan; [TUJUAN]: goal yang sedang dikejar; [KENDALA]: sumber daya yang tersedia (waktu/anggaran/tim)</t>
   </si>
   <si>
     <t>Tabel terjemahan temuan ke tindakan dengan urutan minggu pertama</t>
@@ -3610,10 +3611,10 @@
     <t>Menyiapkan daftar data yang harus dicatat sejak sekarang agar analisis bisa jalan</t>
   </si>
   <si>
-    <t>Sebagai analytics setup specialist, susun daftar data yang harus mulai dicatat untuk [BISNIS] di [PLATFORM] agar goal [GOAL] terukur. Alat: [ALAT]. Sertakan: daftar data wajib per minggu dan per bulan dengan sumber pengambilannya di tiap platform, data penjualan yang harus dicatat manual karena tidak otomatis, struktur spreadsheet per lembar kerja, aturan konsistensi (hari pencatatan, satuan, penamaan), kesalahan pencatatan yang membuat data tidak bisa dibandingkan, dan checklist 10 menit akhir minggu agar pencatatan tidak terlewat.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang dijalankan; [GOAL]: goal yang ingin diukur; [ALAT]: alat pencatatan yang dipakai (spreadsheet/notion/manual)</t>
+    <t>Sebagai ahli penyiapan analitik, susun daftar data yang harus mulai dicatat untuk [BISNIS] di [PLATFORM] agar goal [TUJUAN] terukur. Alat: [ALAT]. Sertakan: daftar data wajib per minggu dan per bulan dengan sumber pengambilannya di tiap platform, data penjualan yang harus dicatat manual karena tidak otomatis, struktur spreadsheet per lembar kerja, aturan konsistensi (hari pencatatan, satuan, penamaan), kesalahan pencatatan yang membuat data tidak bisa dibandingkan, dan checklist 10 menit akhir minggu agar pencatatan tidak terlewat.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang dijalankan; [TUJUAN]: goal yang ingin diukur; [ALAT]: alat pencatatan yang dipakai (spreadsheet/notion/manual)</t>
   </si>
   <si>
     <t>Daftar data wajib dengan struktur spreadsheet dan checklist mingguan</t>
@@ -3643,7 +3644,7 @@
     <t>Annual Strategy Review</t>
   </si>
   <si>
-    <t>Melakukan review strategi tahunan dan planning tahun depan</t>
+    <t>Melakukan review strategi tahunan dan perencanaan tahun depan</t>
   </si>
   <si>
     <t>Sebagai direktur pemasaran, buatkan telaah strategi tahunan media sosial untuk [TAHUN_INI] dan perencanaan [TAHUN_DEPAN]. Pencapaian: [ACHIEVEMENTS]. Tantangan: [CHALLENGES]. Target: [GOALS_DEPAN]. Sertakan: (1) rekap setahun (metrik utama dan momen penting), (2) apa yang berhasil (5 faktor keberhasilan), (3) apa yang tidak berhasil (5 pelajaran), (4) perubahan lanskap kompetisi, (5) tren industri untuk tahun depan, (6) prioritas strategis (3-5 fokus utama), (7) target per kuartal dan inisiatifnya, (8) kebutuhan sumber daya (anggaran/tim/peralatan), (9) penilaian risiko dan cara menguranginya, (10) metrik keberhasilan dan rencana pemantauan. Buat lengkap tapi tetap bisa langsung dieksekusi.</t>
@@ -4235,6 +4236,324 @@
   </si>
   <si>
     <t>Tayang di slot yang direncanakan</t>
+  </si>
+  <si>
+    <t>Arti</t>
+  </si>
+  <si>
+    <t>Contoh</t>
+  </si>
+  <si>
+    <t>[BISNIS]</t>
+  </si>
+  <si>
+    <t>Jenis atau nama usaha yang dipromosikan</t>
+  </si>
+  <si>
+    <t>Produsen keripik singkong balado Bandung</t>
+  </si>
+  <si>
+    <t>[PRODUK]</t>
+  </si>
+  <si>
+    <t>Produk atau jasa yang dijual</t>
+  </si>
+  <si>
+    <t>Keripik singkong balado 250 gram</t>
+  </si>
+  <si>
+    <t>[PLATFORM]</t>
+  </si>
+  <si>
+    <t>Platform tempat konten ditayangkan</t>
+  </si>
+  <si>
+    <t>[TUJUAN]</t>
+  </si>
+  <si>
+    <t>Sasaran yang ingin dicapai dari posting atau kampanye</t>
+  </si>
+  <si>
+    <t>Menambah 30 chat masuk dalam satu bulan</t>
+  </si>
+  <si>
+    <t>[TOPIK]</t>
+  </si>
+  <si>
+    <t>Pokok bahasan konten</t>
+  </si>
+  <si>
+    <t>Cara menyimpan keripik agar tetap renyah</t>
+  </si>
+  <si>
+    <t>[DATA]</t>
+  </si>
+  <si>
+    <t>Ringkasan angka performa yang dilampirkan</t>
+  </si>
+  <si>
+    <t>Reach 12.000, 40 komentar, 9 chat masuk</t>
+  </si>
+  <si>
+    <t>[DURASI]</t>
+  </si>
+  <si>
+    <t>Panjang video yang diinginkan</t>
+  </si>
+  <si>
+    <t>30 detik</t>
+  </si>
+  <si>
+    <t>[AUDIENS]</t>
+  </si>
+  <si>
+    <t>Pembeli atau pengikut yang dituju</t>
+  </si>
+  <si>
+    <t>Ibu muda di Bandung yang belanja camilan online</t>
+  </si>
+  <si>
+    <t>[KANAL]</t>
+  </si>
+  <si>
+    <t>Jalur masuk pesanan atau percakapan</t>
+  </si>
+  <si>
+    <t>WhatsApp</t>
+  </si>
+  <si>
+    <t>[PERIODE]</t>
+  </si>
+  <si>
+    <t>Rentang waktu yang dianalisis atau dijadwalkan</t>
+  </si>
+  <si>
+    <t>Oktober 2026</t>
+  </si>
+  <si>
+    <t>[CTA]</t>
+  </si>
+  <si>
+    <t>Permintaan tindakan di akhir konten</t>
+  </si>
+  <si>
+    <t>Pesan sekarang lewat WhatsApp</t>
+  </si>
+  <si>
+    <t>[PENAWARAN]</t>
+  </si>
+  <si>
+    <t>Promosi atau penawaran khusus yang tersedia</t>
+  </si>
+  <si>
+    <t>Beli 2 gratis 1 mini pack</t>
+  </si>
+  <si>
+    <t>[SUMBER]</t>
+  </si>
+  <si>
+    <t>Asal data yang dipakai</t>
+  </si>
+  <si>
+    <t>Laporan Instagram minggu ketiga</t>
+  </si>
+  <si>
+    <t>[SITUASI]</t>
+  </si>
+  <si>
+    <t>Kejadian lucu yang dialami bisnis atau audiens</t>
+  </si>
+  <si>
+    <t>Kesalahan timbang bumbu saat produksi pertama</t>
+  </si>
+  <si>
+    <t>[FORMAT]</t>
+  </si>
+  <si>
+    <t>Bentuk penyajian konten</t>
+  </si>
+  <si>
+    <t>Daftar bernomor</t>
+  </si>
+  <si>
+    <t>[TONE]</t>
+  </si>
+  <si>
+    <t>Gaya bahasa yang diinginkan</t>
+  </si>
+  <si>
+    <t>Santai dan sedikit jenaka</t>
+  </si>
+  <si>
+    <t>[FREKUENSI]</t>
+  </si>
+  <si>
+    <t>Jumlah posting per periode</t>
+  </si>
+  <si>
+    <t>4 kali per minggu</t>
+  </si>
+  <si>
+    <t>[PILLAR]</t>
+  </si>
+  <si>
+    <t>Pilar konten bisnis</t>
+  </si>
+  <si>
+    <t>Edukasi, dapur, promo, pelanggan</t>
+  </si>
+  <si>
+    <t>[MOMEN]</t>
+  </si>
+  <si>
+    <t>Momen penting dalam bulan tersebut</t>
+  </si>
+  <si>
+    <t>Hari Pahlawan</t>
+  </si>
+  <si>
+    <t>[BATAS_WAKTU]</t>
+  </si>
+  <si>
+    <t>Tenggat yang ditetapkan</t>
+  </si>
+  <si>
+    <t>Jumat pukul 17.00</t>
+  </si>
+  <si>
+    <t>[INDUSTRI]</t>
+  </si>
+  <si>
+    <t>Bidang industri bisnis Anda</t>
+  </si>
+  <si>
+    <t>Makanan ringan</t>
+  </si>
+  <si>
+    <t>[PROSES]</t>
+  </si>
+  <si>
+    <t>Rangkaian pekerjaan yang diceritakan</t>
+  </si>
+  <si>
+    <t>Iris, bumbu, goreng, kemas</t>
+  </si>
+  <si>
+    <t>[PESAN]</t>
+  </si>
+  <si>
+    <t>Inti pesan yang ingin disampaikan</t>
+  </si>
+  <si>
+    <t>Keripik tanpa pengawet itu ada</t>
+  </si>
+  <si>
+    <t>[ALAT]</t>
+  </si>
+  <si>
+    <t>Alat atau bahan yang dibutuhkan</t>
+  </si>
+  <si>
+    <t>Wajan, timbangan digital, sealer</t>
+  </si>
+  <si>
+    <t>[LOKASI]</t>
+  </si>
+  <si>
+    <t>Area atau kota target</t>
+  </si>
+  <si>
+    <t>Bandung Raya</t>
+  </si>
+  <si>
+    <t>[EVENT]</t>
+  </si>
+  <si>
+    <t>Acara atau momen spesial yang terkait</t>
+  </si>
+  <si>
+    <t>Bazar UMKM Jakarta</t>
+  </si>
+  <si>
+    <t>[TIM]</t>
+  </si>
+  <si>
+    <t>Jumlah orang yang mengerjakan konten</t>
+  </si>
+  <si>
+    <t>2 orang</t>
+  </si>
+  <si>
+    <t>[HADIAH]</t>
+  </si>
+  <si>
+    <t>Hadiah untuk giveaway atau kontes</t>
+  </si>
+  <si>
+    <t>Satu toples keripik tiga rasa</t>
+  </si>
+  <si>
+    <t>[FAKTA]</t>
+  </si>
+  <si>
+    <t>Fakta atau angka benar yang dipakai</t>
+  </si>
+  <si>
+    <t>Lima ratus toples terjual bulan lalu</t>
+  </si>
+  <si>
+    <t>[JUMLAH]</t>
+  </si>
+  <si>
+    <t>Kapasitas atau kuantitas yang tersedia</t>
+  </si>
+  <si>
+    <t>200 toples per minggu</t>
+  </si>
+  <si>
+    <t>[CERITA]</t>
+  </si>
+  <si>
+    <t>Perjalanan pelanggan dari awal sampai hasil</t>
+  </si>
+  <si>
+    <t>Dari ragu-ragu sampai langganan enam bulan</t>
+  </si>
+  <si>
+    <t>[KRITERIA]</t>
+  </si>
+  <si>
+    <t>Poin perbandingan yang dipakai</t>
+  </si>
+  <si>
+    <t>Harga, rasa, ketahanan renyah</t>
+  </si>
+  <si>
+    <t>[BRAND]</t>
+  </si>
+  <si>
+    <t>Nama merek bisnis Anda</t>
+  </si>
+  <si>
+    <t>Keripik Bu Rina</t>
+  </si>
+  <si>
+    <t>[METRIK]</t>
+  </si>
+  <si>
+    <t>Metrik yang dicatat atau dianalisis</t>
+  </si>
+  <si>
+    <t>Reach, simpan, bagikan, chat masuk</t>
+  </si>
+  <si>
+    <t>[PERTANYAAN]</t>
+  </si>
+  <si>
+    <t>Daftar pertanyaan yang terkumpul</t>
+  </si>
+  <si>
+    <t>Berapa ongkir ke luar kota, ada varian pedas</t>
   </si>
 </sst>
 </file>
@@ -11535,4 +11854,414 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/products/200-template-sosmed-premium-premium.xlsx
+++ b/products/200-template-sosmed-premium-premium.xlsx
@@ -71,13 +71,13 @@
     <t>Menentukan 3-5 topik utama untuk konten Anda</t>
   </si>
   <si>
-    <t>Sebagai brand strategist, tentukan 5 content pillar untuk [BISNIS] yang menjual [PRODUK] kepada [AUDIENS]. Keahlian kami adalah [KEAHLIAN]. Setiap pillar harus: (1) relevan dengan audience, (2) menunjukkan expertise, (3) mendukung goal bisnis, (4) bisa diproduksi konsisten. Untuk setiap pillar, berikan: nama pillar, deskripsi, contoh 5 ide konten, dan persentase alokasi dari total konten bulanan.</t>
+    <t>Sebagai perancang strategi merek, tentukan 5 pilar konten untuk [BISNIS] yang menjual [PRODUK] kepada [AUDIENS]. Keahlian kami adalah [KEAHLIAN]. Setiap pillar harus: (1) relevan dengan audiens, (2) menunjukkan expertise, (3) mendukung tujuan bisnis, (4) bisa diproduksi konsisten. Untuk setiap pillar, berikan: nama pillar, deskripsi, contoh 5 ide konten, dan persentase alokasi dari total konten bulanan.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk/jasa yang dijual; [AUDIENS]: pembeli atau pengikut yang dituju; [KEAHLIAN]: keahlian atau unique selling point</t>
   </si>
   <si>
-    <t>5 content pillar lengkap dengan contoh ide dan alokasi persentase</t>
+    <t>5 pilar konten lengkap dengan contoh ide dan alokasi persentase</t>
   </si>
   <si>
     <t>T-003</t>
@@ -86,16 +86,16 @@
     <t>Ringkasan Riset Audiens</t>
   </si>
   <si>
-    <t>Memahami karakteristik dan kebutuhan audience Anda</t>
-  </si>
-  <si>
-    <t>Sebagai market researcher, buatkan profil audience untuk [BISNIS] yang menjual [PRODUK] kepada usia [USIA] di [LOKASI]. Sertakan: (1) demographic profile, (2) psychographic traits, (3) pain points dan challenges, (4) goals dan aspirations, (5) media sosial behavior (platform favorit, waktu aktif, jenis konten yang disukai), (6) buying triggers dan objections, (7) 5 persona berbeda dengan nama dan cerita singkat.</t>
+    <t>Memahami karakteristik dan kebutuhan audiens Anda</t>
+  </si>
+  <si>
+    <t>Sebagai peneliti pasar, buatkan profil audiens untuk [BISNIS] yang menjual [PRODUK] kepada usia [USIA] di [LOKASI]. Sertakan: (1) demographic profile, (2) psychographic traits, (3) pain points dan challenges, (4) goals dan aspirations, (5) media sosial behavior (platform favorit, waktu aktif, jenis konten yang disukai), (6) buying triggers dan objections, (7) 5 persona berbeda dengan nama dan cerita singkat.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk/jasa yang dijual; [USIA]: rentang usia audiens yang dituju; [LOKASI]: lokasi geografis target</t>
   </si>
   <si>
-    <t>Profil audience lengkap dengan 5 persona berbeda</t>
+    <t>Profil audiens lengkap dengan 5 persona berbeda</t>
   </si>
   <si>
     <t>T-004</t>
@@ -107,7 +107,7 @@
     <t>Menganalisis strategi media sosial kompetitor</t>
   </si>
   <si>
-    <t>Sebagai competitive intelligence analyst, analisis strategi media sosial [KOMPETITOR_1], [KOMPETITOR_2], dan [KOMPETITOR_3] di [PLATFORM] untuk bisnis [BISNIS]. Buat tabel perbandingan dengan kolom: Nama Kompetitor, Followers, Engagement Rate, Frekuensi Posting, Jenis Konten Dominan, Tone of Voice, Hashtag Strategy, Kekuatan, Kelemahan, dan Peluang untuk [BISNIS]. Berikan 5 rekomendasi strategi yang bisa kita adopsi atau diferensiasi.</t>
+    <t>Sebagai analis intelijen kompetitor, analisis strategi media sosial [KOMPETITOR_1], [KOMPETITOR_2], dan [KOMPETITOR_3] di [PLATFORM] untuk bisnis [BISNIS]. Buat tabel perbandingan dengan kolom: Nama Kompetitor, Followers, Engagement Rate, Frekuensi Posting, Jenis Konten Dominan, Tone of Voice, Hashtag Strategy, Kekuatan, Kelemahan, dan Peluang untuk [BISNIS]. Berikan 5 rekomendasi strategi yang bisa kita adopsi atau diferensiasi.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [KOMPETITOR_1]: nama kompetitor pertama; [KOMPETITOR_2]: nama kompetitor kedua; [KOMPETITOR_3]: nama kompetitor ketiga; [PLATFORM]: platform yang dianalisis</t>
@@ -125,10 +125,10 @@
     <t>Membuat 7 ide konten dalam sekali duduk</t>
   </si>
   <si>
-    <t>Sebagai content creator, buatkan 7 ide konten untuk [BISNIS] minggu ini. Content pillar: [PILLAR]. Goal: [TUJUAN]. Event: [EVENT]. Untuk setiap ide, berikan: (1) judul/hook, (2) format (image/video/carousel/story), (3) angle unik, (4) CTA yang sesuai, (5) estimasi waktu produksi. Variasikan antara konten edukatif, inspiratif, entertaining, dan promotif.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [PILLAR]: content pillar minggu ini; [TUJUAN]: tujuan minggu ini; [EVENT]: event atau momen spesial (jika ada)</t>
+    <t>Sebagai kreator konten, buatkan 7 ide konten untuk [BISNIS] minggu ini. Pilar konten: [PILLAR]. Tujuan: [TUJUAN]. Event: [EVENT]. Untuk setiap ide, berikan: (1) judul/hook, (2) format (image/video/carousel/story), (3) angle unik, (4) CTA yang sesuai, (5) estimasi waktu produksi. Variasikan antara konten edukatif, inspiratif, entertaining, dan promotif.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [PILLAR]: pilar konten minggu ini; [TUJUAN]: tujuan minggu ini; [EVENT]: event atau momen spesial (jika ada)</t>
   </si>
   <si>
     <t>7 ide konten lengkap dengan detail produksi</t>
@@ -143,7 +143,7 @@
     <t>Menentukan tema besar untuk konten satu bulan penuh</t>
   </si>
   <si>
-    <t>Sebagai media sosial strategist, tentukan tema konten untuk [BISNIS] sepanjang [BULAN]. Goal bulan ini: [TUJUAN]. Momen penting: [MOMEN]. Buat 4 tema mingguan yang saling terhubung, untuk setiap tema berikan: nama tema, alasan pemilihan, 5 ide konten, format yang disarankan, dan cara mengukur keberhasilannya. Pastikan tema minggu terakhir mengarah ke konversi penjualan.</t>
+    <t>Sebagai perancang strategi media sosial, tentukan tema konten untuk [BISNIS] sepanjang [BULAN]. Tujuan bulan ini: [TUJUAN]. Momen penting: [MOMEN]. Buat 4 tema mingguan yang saling terhubung, untuk setiap tema berikan: nama tema, alasan pemilihan, 5 ide konten, format yang disarankan, dan cara mengukur keberhasilannya. Pastikan tema minggu terakhir mengarah ke konversi penjualan.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [BULAN]: bulan yang direncanakan; [TUJUAN]: target bisnis bulan itu; [MOMEN]: momen penting dalam bulan tersebut</t>
@@ -161,10 +161,10 @@
     <t>Menentukan porsi konten edukasi, promosi, dan hiburan</t>
   </si>
   <si>
-    <t>Sebagai media sosial planner, hitung rasio konten ideal untuk [BISNIS] di [PLATFORM] dengan goal [TUJUAN]. Bagi konten menjadi 4 kategori: edukasi, inspirasi, hiburan, dan promosi. Berikan persentase ideal untuk setiap kategori beserta alasannya, contoh topik untuk masing-masing kategori, dan jadwal seminggu yang menerapkan rasio tersebut. Jelaskan juga tanda-tanda rasio perlu diubah.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform utama; [TUJUAN]: goal utama (awareness/sales/community)</t>
+    <t>Sebagai perencana media sosial, hitung rasio konten ideal untuk [BISNIS] di [PLATFORM] dengan tujuan [TUJUAN]. Bagi konten menjadi 4 kategori: edukasi, inspirasi, hiburan, dan promosi. Berikan persentase ideal untuk setiap kategori beserta alasannya, contoh topik untuk masing-masing kategori, dan jadwal seminggu yang menerapkan rasio tersebut. Jelaskan juga tanda-tanda rasio perlu diubah.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform utama; [TUJUAN]: tujuan utama (awareness/penjualan/komunitas)</t>
   </si>
   <si>
     <t>Rasio konten per kategori dengan jadwal contoh seminggu</t>
@@ -179,7 +179,7 @@
     <t>Membangun cadangan konten yang tidak kedaluwarsa</t>
   </si>
   <si>
-    <t>Sebagai content strategist, buatkan bank konten evergreen untuk [BISNIS] yang menjual [PRODUK]. Berdasarkan pertanyaan umum pelanggan: [PERTANYAAN_UMUM]. Buat 20 ide konten evergreen yang tetap relevan sepanjang tahun, untuk setiap ide berikan: judul, format konten, poin utama, dan tingkat kesulitan produksi (rendah/sedang/tinggi). Kelompokkan menjadi 4 kategori: edukasi produk, tips penggunaan, jawaban keberatan, dan cerita brand.</t>
+    <t>Sebagai perancang strategi konten, buatkan bank konten evergreen untuk [BISNIS] yang menjual [PRODUK]. Berdasarkan pertanyaan umum pelanggan: [PERTANYAAN_UMUM]. Buat 20 ide konten evergreen yang tetap relevan sepanjang tahun, untuk setiap ide berikan: judul, format konten, poin utama, dan tingkat kesulitan produksi (rendah/sedang/tinggi). Kelompokkan menjadi 4 kategori: edukasi produk, tips penggunaan, jawaban keberatan, dan cerita brand.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk atau jasa utama; [PERTANYAAN_UMUM]: pertanyaan yang sering ditanyakan pelanggan</t>
@@ -215,7 +215,7 @@
     <t>Merencanakan kampanye marketing dari awal sampai akhir</t>
   </si>
   <si>
-    <t>Sebagai campaign manager, buat kalender kampanye untuk [KAMPANYE] yang mempromosikan [PRODUK] dari [TANGGAL_MULAI] sampai [TANGGAL_SELESAI]. Budget: [BUDGET]. Struktur 3 fase: teasing (7 hari sebelum), launching (hari pertama sampai ketiga), sustaining (sisanya). Untuk setiap fase berikan: konten yang diposting, channel yang dipakai, anggaran alokasi, dan KPI yang dipantau. Tutup dengan checklist persiapan 2 minggu sebelum kampanye dimulai.</t>
+    <t>Sebagai manajer kampanye, buat kalender kampanye untuk [KAMPANYE] yang mempromosikan [PRODUK] dari [TANGGAL_MULAI] sampai [TANGGAL_SELESAI]. Budget: [BUDGET]. Struktur 3 fase: teasing (7 hari sebelum), launching (hari pertama sampai ketiga), sustaining (sisanya). Untuk setiap fase berikan: konten yang diposting, channel yang dipakai, anggaran alokasi, dan KPI yang dipantau. Tutup dengan checklist persiapan 2 minggu sebelum kampanye dimulai.</t>
   </si>
   <si>
     <t>[KAMPANYE]: nama kampanye; [PRODUK]: produk yang dipromosikan; [TANGGAL_MULAI]: tanggal mulai; [TANGGAL_SELESAI]: tanggal selesai; [BUDGET]: anggaran tersedia</t>
@@ -233,7 +233,7 @@
     <t>Merencanakan konten untuk peluncuran produk baru</t>
   </si>
   <si>
-    <t>Sebagai launch strategist, buat konten calendar peluncuran [PRODUK] pada [TANGGAL_LAUNCH]. Target: [AUDIENS], harga: [PRICE_POINT]. Susun konten dari H-14 sampai H+7: fase intrik (H-14 sampai H-8), fase mengungkap (H-7 sampai H-1), fase peluncuran (H-0 sampai H+3), fase testimoni (H+4 sampai H+7). Untuk setiap hari berikan: jenis konten, hook, channel, dan tujuan. Fokuskan konten H-7 ke atas untuk mengumpulkan waitlist.</t>
+    <t>Sebagai perancang strategi peluncuran, buat kalender konten peluncuran [PRODUK] pada [TANGGAL_LAUNCH]. Target: [AUDIENS], harga: [PRICE_POINT]. Susun konten dari H-14 sampai H+7: fase intrik (H-14 sampai H-8), fase mengungkap (H-7 sampai H-1), fase peluncuran (H-0 sampai H+3), fase testimoni (H+4 sampai H+7). Untuk setiap hari berikan: jenis konten, hook, kanal, dan tujuan. Fokuskan konten H-7 ke atas untuk mengumpulkan waitlist.</t>
   </si>
   <si>
     <t>[PRODUK]: produk baru yang akan diluncurkan; [TANGGAL_LAUNCH]: tanggal peluncuran; [AUDIENS]: pembeli atau pengikut yang dituju; [PRICE_POINT]: kisaran harga</t>
@@ -251,7 +251,7 @@
     <t>Menyiapkan konten untuk hari besar nasional dan internasional</t>
   </si>
   <si>
-    <t>Sebagai media sosial planner, susun konten untuk hari besar berikut: [HARI_BESAR] untuk bisnis [BISNIS]. Untuk setiap hari besar berikan: angle yang menghubungkan hari besar dengan produk (bukan sekadar ucapan), ide konten utama dan pendukung, timing posting, dan apakah perlu promo. Promo yang tersedia: [PROMO]. Hindari konten yang terlihat ikut-ikutan tanpa kaitan nyata dengan bisnis.</t>
+    <t>Sebagai perencana media sosial, susun konten untuk hari besar berikut: [HARI_BESAR] untuk bisnis [BISNIS]. Untuk setiap hari besar berikan: angle yang menghubungkan hari besar dengan produk (bukan sekadar ucapan), ide konten utama dan pendukung, timing posting, dan apakah perlu promo. Promo yang tersedia: [PROMO]. Hindari konten yang terlihat ikut-ikutan tanpa kaitan nyata dengan bisnis.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [HARI_BESAR]: daftar hari besar yang relevan; [PROMO]: jenis promo yang tersedia</t>
@@ -287,7 +287,7 @@
     <t>Menyusun alur persetujuan konten sebelum tayang</t>
   </si>
   <si>
-    <t>Sebagai workflow consultant, buat alur persetujuan konten untuk struktur tim berikut: [STRUKTUR_TIM]. Jenis konten: [JENIS_KONTEN]. Buat 2 alur: cepat (maksimal [BATAS_WAKTU]) untuk konten rutin, dan lengkap untuk konten sensitif seperti promo besar atau isu publik. Untuk setiap alur sebutkan: siapa menyetujui apa, kriteria yang diperiksa, dan cara menyampaikan revisi agar tidak berlarut-larut.</t>
+    <t>Sebagai konsultan alur kerja, buat alur persetujuan konten untuk struktur tim berikut: [STRUKTUR_TIM]. Jenis konten: [JENIS_KONTEN]. Buat 2 alur: cepat (maksimal [BATAS_WAKTU]) untuk konten rutin, dan lengkap untuk konten sensitif seperti promo besar atau isu publik. Untuk setiap alur sebutkan: siapa menyetujui apa, kriteria yang diperiksa, dan cara menyampaikan revisi agar tidak berlarut-larut.</t>
   </si>
   <si>
     <t>[STRUKTUR_TIM]: siapa terlibat (owner, marketing, cs); [JENIS_KONTEN]: jenis konten yang diproduksi; [BATAS_WAKTU]: batas waktu persetujuan</t>
@@ -305,7 +305,7 @@
     <t>Membuat brief yang jelas untuk konten kreatif</t>
   </si>
   <si>
-    <t>Sebagai creative director, buat template brief konten untuk proyek [PROYEK]. Tujuan: [OBJECTIVE]. Audiens: [AUDIENS]. Template harus mencakup: satu kalimat pesan inti, apa yang audiens harus lakukan setelah melihat konten, do dan don't, referensi visual, deadline, dan definisi berhasil. Buat versi satu halaman yang bisa diisi dalam 10 menit.</t>
+    <t>Sebagai direktur kreatif, buat template brief konten untuk proyek [PROYEK]. Tujuan: [OBJECTIVE]. Audiens: [AUDIENS]. Template harus mencakup: satu kalimat pesan inti, apa yang audiens harus lakukan setelah melihat konten, do dan don't, referensi visual, batas waktu, dan definisi berhasil. Buat versi satu halaman yang bisa diisi dalam 10 menit.</t>
   </si>
   <si>
     <t>[PROYEK]: nama proyek konten; [OBJECTIVE]: tujuan konten; [AUDIENS]: penerima pesan</t>
@@ -431,10 +431,10 @@
     <t>Menilai performa konten 3 bulan terakhir</t>
   </si>
   <si>
-    <t>Sebagai content auditor, analisis performa konten periode [PERIODE] dengan data berikut: [DATA]. Goal akun: [TUJUAN]. Kelompokkan konten menjadi 4 kuadran: performa tinggi dan mudah dibuat (perbanyak), performa tinggi tapi berat produksi (optimalkan proses), performa rendah tapi mudah (perbaiki angle), performa rendah dan berat (hentikan). Untuk setiap kuadran berikan contoh konten dari data dan rekomendasi tindakan spesifik.</t>
-  </si>
-  <si>
-    <t>[PERIODE]: periode audit; [DATA]: ringkasan data performa konten; [TUJUAN]: goal akun saat ini</t>
+    <t>Sebagai auditor konten, analisis performa konten periode [PERIODE] dengan data berikut: [DATA]. Tujuan akun: [TUJUAN]. Kelompokkan konten menjadi 4 kuadran: performa tinggi dan mudah dibuat (perbanyak), performa tinggi tapi berat produksi (optimalkan proses), performa rendah tapi mudah (perbaiki angle), performa rendah dan berat (hentikan). Untuk setiap kuadran berikan contoh konten dari data dan rekomendasi tindakan spesifik.</t>
+  </si>
+  <si>
+    <t>[PERIODE]: periode audit; [DATA]: ringkasan data performa konten; [TUJUAN]: tujuan akun saat ini</t>
   </si>
   <si>
     <t>Analisis 4 kuadran dengan rekomendasi tindakan</t>
@@ -485,7 +485,7 @@
     <t>Mengubah pertanyaan audiens menjadi ide konten</t>
   </si>
   <si>
-    <t>Sebagai content strategist, olah daftar pertanyaan audiens berikut: [PERTANYAAN_UMUM] dari sumber [SUMBER_PERTANYAAN]. Kelompokkan pertanyaan menjadi tema, untuk setiap tema hitung frekuensinya dan buat 3 ide konten yang menjawabnya dengan angle berbeda: jawaban langsung, miskonsepsi yang perlu diluruskan, dan studi kasus nyata. Sambungkan setiap ide dengan produk [PRODUK] secara natural tanpa memaksa jualan.</t>
+    <t>Sebagai perancang strategi konten, olah daftar pertanyaan audiens berikut: [PERTANYAAN_UMUM] dari sumber [SUMBER_PERTANYAAN]. Kelompokkan pertanyaan menjadi tema, untuk setiap tema hitung frekuensinya dan buat 3 ide konten yang menjawabnya dengan angle berbeda: jawaban langsung, miskonsepsi yang perlu diluruskan, dan studi kasus nyata. Sambungkan setiap ide dengan produk [PRODUK] secara natural tanpa memaksa jualan.</t>
   </si>
   <si>
     <t>[SUMBER_PERTANYAAN]: tempat pertanyaan muncul (DM, comment, grup WhatsApp); [PERTANYAAN]: daftar pertanyaan mentah yang terkumpul; [PRODUK]: produk atau jasa Anda</t>
@@ -557,7 +557,7 @@
     <t>Merencanakan konten untuk event online atau offline</t>
   </si>
   <si>
-    <t>Sebagai event content planner, susun konten untuk [EVENT] pada [TANGGAL] dengan tujuan [TUJUAN]. Buat konten 3 fase: sebelum (pembukaan pendaftaran, pengenalan pembicara, countdown), saat (live update, kutipan pembicara, interaksi peserta), dan sesudah (rekapan, materi gratis, testimonial peserta). Untuk setiap konten berikan format, timing, dan CTA. Sertakan rencana darurat jika pendaftaran lambat di tengah fase sebelum.</t>
+    <t>Sebagai perencana konten acara, susun konten untuk [EVENT] pada [TANGGAL] dengan tujuan [TUJUAN]. Buat konten 3 fase: sebelum (pembukaan pendaftaran, pengenalan pembicara, countdown), saat (live update, kutipan pembicara, interaksi peserta), dan sesudah (rekapan, materi gratis, testimonial peserta). Untuk setiap konten berikan format, timing, dan CTA. Sertakan rencana darurat jika pendaftaran lambat di tengah fase sebelum.</t>
   </si>
   <si>
     <t>[EVENT]: nama dan jenis event; [TANGGAL]: tanggal penyelenggaraan; [TUJUAN]: tujuan acara (calon pembeli, penjualan, mengenalkan merek)</t>
@@ -575,7 +575,7 @@
     <t>Merencanakan giveaway yang menghasilkan, bukan sekadar viral sesaat</t>
   </si>
   <si>
-    <t>Sebagai giveaway strategist, rancang kampanye giveaway dengan hadiah [HADIAH] untuk tujuan [TUJUAN]. Budget promosi: [BUDGET_PROMO]. Tentukan: syarat partisipasi yang sejalan dengan goal (jangan minta tag 10 teman jika goal-nya leads), durasi ideal, konten pengumuman dan pengingat, cara memilih pemenang yang transparan, dan konten pasca giveaway untuk mengonversi peserta baru menjadi pengikut yang benar-benar tertarik. Sertakan perhitungan biaya per hasil.</t>
+    <t>Sebagai perancang strategi giveaway, rancang kampanye giveaway dengan hadiah [HADIAH] untuk tujuan [TUJUAN]. Budget promosi: [BUDGET_PROMO]. Tentukan: syarat partisipasi yang sejalan dengan tujuan (jangan minta tag 10 teman jika tujuan-nya leads), durasi ideal, konten pengumuman dan pengingat, cara memilih pemenang yang transparan, dan konten pasca giveaway untuk mengonversi peserta baru menjadi pengikut yang benar-benar tertarik. Sertakan perhitungan biaya per hasil.</t>
   </si>
   <si>
     <t>[HADIAH]: hadiah yang tersedia; [TUJUAN]: tujuan giveaway (follower, leads, awareness); [BUDGET_PROMO]: anggaran promosi giveaway</t>
@@ -611,7 +611,7 @@
     <t>Menyiapkan konten darurat sebelum masalah terjadi</t>
   </si>
   <si>
-    <t>Sebagai crisis communication planner, siapkan rencana konten darurat untuk risiko berikut: [RISIKO]. Tim penanggung jawab: [TIM]. Channel resmi: [KANAL]. Buat untuk setiap risiko: template pernyataan awal (mengakui masalah tanpa menyalahkan pihak lain), template update kedua (langkah yang diambil), dan template penutup (pemulihan dan pencegahan). Sertakan aturan timing: seberapa cepat harus merespons dan kapan diam lebih baik.</t>
+    <t>Sebagai perencana komunikasi krisis, siapkan rencana konten darurat untuk risiko berikut: [RISIKO]. Tim penanggung jawab: [TIM]. Channel resmi: [KANAL]. Buat untuk setiap risiko: template pernyataan awal (mengakui masalah tanpa menyalahkan pihak lain), templat pembaruan kedua (langkah yang diambil), dan template penutup (pemulihan dan pencegahan). Sertakan aturan waktu: seberapa cepat harus merespons dan kapan diam lebih baik.</t>
   </si>
   <si>
     <t>[RISIKO]: risiko yang mungkin terjadi di bisnis Anda; [TIM]: siapa yang bertugas saat darurat; [KANAL]: channel resmi untuk komunikasi</t>
@@ -629,10 +629,10 @@
     <t>Menyusun cadangan ide konten untuk 3 bulan ke depan</t>
   </si>
   <si>
-    <t>Sebagai content strategist, bangun backlog ide untuk [BISNIS] dengan pillar [PILLAR] dan ritme [RITME] per minggu. Hasilkan 36 ide (cukup 3 bulan) yang terbagi merata antar pillar. Untuk setiap ide berikan: judul kerja, satu kalimat angle, format yang cocok, dan tingkat prioritas (tinggi untuk yang berpotensi konversi, sedang untuk engagement, rendah untuk pengisi jadwal). Pastikan minimal 8 ide bisa diproduksi dalam waktu di bawah 30 menit.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [PILLAR]: content pillar utama; [RITME]: frekuensi posting per minggu</t>
+    <t>Sebagai perancang strategi konten, bangun backlog ide untuk [BISNIS] dengan pillar [PILLAR] dan ritme [RITME] per minggu. Hasilkan 36 ide (cukup 3 bulan) yang terbagi merata antar pillar. Untuk setiap ide berikan: judul kerja, satu kalimat angle, format yang cocok, dan tingkat prioritas (tinggi untuk yang berpotensi konversi, sedang untuk engagement, rendah untuk pengisi jadwal). Pastikan minimal 8 ide bisa diproduksi dalam waktu di bawah 30 menit.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [PILLAR]: pilar konten utama; [RITME]: frekuensi posting per minggu</t>
   </si>
   <si>
     <t>Backlog 36 ide dengan prioritas dan estimasi waktu</t>
@@ -650,7 +650,7 @@
     <t>Sebagai ideation specialist, hasulkan 20 angle berbeda untuk pillar [PILLAR] yang ditujukan ke [AUDIENS] dan berkaitan dengan [PRODUK]. Variasikan angle ke dalam 5 jenis: kesalahan umum, rahasia praktisi, perbandingan pilihan, cerita nyata, dan jawaban skeptis. Untuk setiap angle tulis satu kalimat hook. Tandai 5 angle yang paling jarang dipakai kompetitor, itu yang berpotensi menonjol.</t>
   </si>
   <si>
-    <t>[PILLAR]: satu content pillar yang ingin diperdalam; [AUDIENS]: audiens pillar ini; [PRODUK]: produk yang berkaitan</t>
+    <t>[PILLAR]: satu pilar konten yang ingin diperdalam; [AUDIENS]: audiens pillar ini; [PRODUK]: produk yang berkaitan</t>
   </si>
   <si>
     <t>20 angle terklasifikasi dengan hook dan penanda peluang</t>
@@ -683,10 +683,10 @@
     <t>Evaluasi menyeluruh strategi konten bulanan</t>
   </si>
   <si>
-    <t>Sebagai media sosial strategist, evaluasi bulan ini dengan data [DATA_BULAN] terhadap goal [GOAL_BULAN]. Jawab: apakah goal tercapai dan seberapa jauh, kontribusi tiap jenis konten terhadap goal, keputusan bulan ini yang terbukti tepat dan yang keliru. Lalu tinjau draft rencana bulan depan: [RENCANA_BULAN_DEPAN]. Sarankan perubahan konkret berdasarkan temuan, jangan ubah yang sudah terbukti bekerja.</t>
-  </si>
-  <si>
-    <t>[DATA_BULAN]: data performa sebulan penuh; [GOAL_BULAN]: goal yang ditetapkan awal bulan; [RENCANA_BULAN_DEPAN]: draft rencana bulan depan</t>
+    <t>Sebagai perancang strategi media sosial, evaluasi bulan ini dengan data [DATA_BULAN] terhadap tujuan [GOAL_BULAN]. Jawab: apakah tujuan tercapai dan seberapa jauh, kontribusi tiap jenis konten terhadap tujuan, keputusan bulan ini yang terbukti tepat dan yang keliru. Lalu tinjau draft rencana bulan depan: [RENCANA_BULAN_DEPAN]. Sarankan perubahan konkret berdasarkan temuan, jangan ubah yang sudah terbukti bekerja.</t>
+  </si>
+  <si>
+    <t>[DATA_BULAN]: data performa sebulan penuh; [GOAL_BULAN]: tujuan yang ditetapkan awal bulan; [RENCANA_BULAN_DEPAN]: draft rencana bulan depan</t>
   </si>
   <si>
     <t>Evaluasi bulanan dengan perubahan rencana yang berbasis data</t>
@@ -701,10 +701,10 @@
     <t>Menyegarkan strategi konten setiap 3 bulan</t>
   </si>
   <si>
-    <t>Sebagai konsultan strategi, lakukan penyegaran strategi kuartalan. Hasil kuartal lalu: [HASIL_KUARTAL]. Perubahan pasar: [PERUBAHAN_PASAR]. Goal kuartal depan: [TUJUAN_KUARTAL_DEPAN]. Tentukan: apa yang dipertahankan (yang sudah terbukti), apa yang dihentikan (yang tidak menyumbang tujuan), dan apa yang dicoba baru (maksimal 2 eksperimen). Untuk setiap eksperimen tentukan ukuran keberhasilan dan tanggal evaluasi.</t>
-  </si>
-  <si>
-    <t>[HASIL_KUARTAL]: hasil 3 bulan terakhir; [PERUBAHAN_PASAR]: perubahan di pasar atau platform; [TUJUAN_KUARTAL_DEPAN]: goal 3 bulan ke depan</t>
+    <t>Sebagai konsultan strategi, lakukan penyegaran strategi kuartalan. Hasil kuartal lalu: [HASIL_KUARTAL]. Perubahan pasar: [PERUBAHAN_PASAR]. Tujuan kuartal depan: [TUJUAN_KUARTAL_DEPAN]. Tentukan: apa yang dipertahankan (yang sudah terbukti), apa yang dihentikan (yang tidak menyumbang tujuan), dan apa yang dicoba baru (maksimal 2 eksperimen). Untuk setiap eksperimen tentukan ukuran keberhasilan dan tanggal evaluasi.</t>
+  </si>
+  <si>
+    <t>[HASIL_KUARTAL]: hasil 3 bulan terakhir; [PERUBAHAN_PASAR]: perubahan di pasar atau platform; [TUJUAN_KUARTAL_DEPAN]: tujuan 3 bulan ke depan</t>
   </si>
   <si>
     <t>Keputusan pertahankan-hentikan-coba dengan kriteria evaluasi</t>
@@ -719,7 +719,7 @@
     <t>Menyusun peta jalan konten setahun penuh</t>
   </si>
   <si>
-    <t>Sebagai content strategist, susun roadmap konten setahun untuk [BISNIS] dengan target [GOAL_TAHUNAN]. Momen besar: [MOMEN_TAHUNAN]. Bagi tahun menjadi 4 kuartal dengan fokus berbeda: kuartal satu membangun fondasi audiens, kuartal dua memperdalam kepercayaan, kuartal tiga memaksimalkan musim ramai, kuartal empat memanen hasil dan mempertahankan pelanggan. Untuk setiap kuartal tentukan tema, jenis konten dominan, dan satu eksperimen besar.</t>
+    <t>Sebagai perancang strategi konten, susun peta jalan konten setahun untuk [BISNIS] dengan target [GOAL_TAHUNAN]. Momen besar: [MOMEN_TAHUNAN]. Bagi tahun menjadi 4 kuartal dengan fokus berbeda: kuartal satu membangun fondasi audiens, kuartal dua memperdalam kepercayaan, kuartal tiga memaksimalkan musim ramai, kuartal empat memanen hasil dan mempertahankan pelanggan. Untuk setiap kuartal tentukan tema, jenis konten dominan, dan satu eksperimen besar.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [GOAL_TAHUNAN]: target bisnis setahun; [MOMEN_TAHUNAN]: momen besar sepanjang tahun (launch, anniversary, musim ramai)</t>
@@ -761,7 +761,7 @@
     <t>[BISNIS]: jenis bisnis Anda; [INDUSTRI]: industri bisnis Anda; [TAHUN]: tahun yang direncanakan</t>
   </si>
   <si>
-    <t>Calendar lengkap dengan 50+ momen dan strategi konten</t>
+    <t>Kalender lengkap dengan 50+ momen dan strategi konten</t>
   </si>
   <si>
     <t>T-041</t>
@@ -797,7 +797,7 @@
     <t>Sebagai perencana konten Facebook, tulis post 200 kata tentang [TOPIK] dengan wawasan [INSIGHT] untuk [AUDIENS]. Tujuan: [TUJUAN]. Buat post yang: (1) terasa dekat dengan masalah pembaca, (2) memberikan manfaat nyata, (3) mudah dipahami, (4) mendorong pembaca membagikannya. Gunakan format: pertanyaan di awal, cerita atau contoh di tengah, kesimpulan yang bisa dibawa pulang di akhir. Tambahkan 1 CTA yang tidak memaksa jualan.</t>
   </si>
   <si>
-    <t>[TOPIK]: topik post; [INSIGHT]: insight atau tips yang dibagikan; [AUDIENS]: pembeli atau pengikut yang dituju; [TUJUAN]: goal post (awareness/engagement/traffic)</t>
+    <t>[TOPIK]: topik post; [INSIGHT]: insight atau tips yang dibagikan; [AUDIENS]: pembeli atau pengikut yang dituju; [TUJUAN]: tujuan posting (awareness/engagement/traffic)</t>
   </si>
   <si>
     <t>Post Facebook yang mengundang interaksi dan mudah dibagikan</t>
@@ -812,7 +812,7 @@
     <t>Membuat naskah TikTok yang berpotensi viral</t>
   </si>
   <si>
-    <t>Sebagai TikTok content creator, buatkan naskah video [DURASI] detik tentang [TOPIK] yang incorporate trend [TREND]. Jika ada produk [PRODUK], integrate secara natural. Struktur: (1) hook 3 detik pertama yang stop scroll, (2) setup 5 detik, (3) main content, (4) plot twist atau surprise, (5) CTA. Sertakan: text overlay untuk setiap scene, rekomendasi music/sound, camera angles, dan transition ideas.</t>
+    <t>Sebagai kreator konten TikTok, buatkan naskah video [DURASI] detik tentang [TOPIK] yang mengangkat tren [TREND]. Jika ada produk [PRODUK], integrate secara natural. Struktur: (1) hook 3 detik pertama yang stop scroll, (2) setup 5 detik, (3) main content, (4) plot twist atau surprise, (5) CTA. Sertakan: text overlay untuk setiap scene, rekomendasi music/sound, camera angles, dan transition ideas.</t>
   </si>
   <si>
     <t>[TOPIK]: topik video; [DURASI]: durasi video (15/30/60 detik); [TREND]: trend yang sedang viral; [PRODUK]: produk yang ingin dipromosikan (jika ada)</t>
@@ -938,7 +938,7 @@
     <t>Mengajarkan sesuatu yang berguna dalam satu caption</t>
   </si>
   <si>
-    <t>Sebagai educational content writer, tulis caption cara melakukan [TOPIK] untuk level [LEVEL]. Struktur: (1) hook yang menyebut hasil akhir yang bisa dicapai, (2) langkah-langkah dalam daftar bernomor dengan tiap langkah maksimal 2 kalimat, (3) kesalahan paling umum yang harus dihindari, (4) CTA menyimpan atau membagikan jika bermanfaat. Sebutkan [PRODUK] hanya di akhir jika memang relevan, jangan dipaksakan.</t>
+    <t>Sebagai penulis konten edukasi, tulis caption cara melakukan [TOPIK] untuk level [LEVEL]. Struktur: (1) hook yang menyebut hasil akhir yang bisa dicapai, (2) langkah-langkah dalam daftar bernomor dengan tiap langkah maksimal 2 kalimat, (3) kesalahan paling umum yang harus dihindari, (4) CTA menyimpan atau membagikan jika bermanfaat. Sebutkan [PRODUK] hanya di akhir jika memang relevan, jangan dipaksakan.</t>
   </si>
   <si>
     <t>[TOPIK]: keterampilan atau cara yang diajarkan; [LEVEL]: level audiens (pemula/menengah); [PRODUK]: produk terkait (opsional)</t>
@@ -1499,7 +1499,7 @@
     <t>Membuat struktur carousel yang mengundang interaksi</t>
   </si>
   <si>
-    <t>Sebagai visual content designer, buatkan struktur carousel Instagram [SLIDES] slide tentang [TOPIK]. Goal: [TUJUAN]. Akhiri dengan [CTA]. Untuk setiap slide, berikan: (1) headline/title, (2) 2-3 bullet points atau visual element, (3) design suggestion (warna, layout, imagery). Slide 1 harus hook yang stop scroll. Slide terakhir harus CTA yang clear. Buat flow yang logical dan visually appealing.</t>
+    <t>Sebagai desainer konten visual, buatkan struktur carousel Instagram [SLIDES] slide tentang [TOPIK]. Tujuan: [TUJUAN]. Akhiri dengan [CTA]. Untuk setiap slide, berikan: (1) headline/title, (2) 2-3 bullet points atau visual element, (3) design suggestion (warna, layout, imagery). Slide 1 harus hook yang stop scroll. Slide terakhir harus CTA yang clear. Buat flow yang logical dan visually appealing.</t>
   </si>
   <si>
     <t>[TOPIK]: topik carousel; [SLIDES]: jumlah slide (5-10); [TUJUAN]: tujuan (edukasi/hiburan/promosi); [CTA]: ajakan bertindak (CTA) di slide terakhir</t>
@@ -1517,7 +1517,7 @@
     <t>Membuat konsep Reels yang mengundang interaksi</t>
   </si>
   <si>
-    <t>Sebagai Reels creator, buatkan 5 konsep video [DURASI] detik tentang [TOPIK] dengan style [STYLE]. Jika ada produk [PRODUK], integrate secara natural. Untuk setiap konsep, berikan: (1) hook 3 detik pertama, (2) main content flow, (3) transition ideas, (4) music/sound recommendation, (5) text overlay suggestions, (6) CTA. Pastikan konsep sesuai dengan trend Reels saat ini.</t>
+    <t>Sebagai kreator Reels, buatkan 5 konsep video [DURASI] detik tentang [TOPIK] dengan style [STYLE]. Jika ada produk [PRODUK], integrate secara natural. Untuk setiap konsep, berikan: (1) hook 3 detik pertama, (2) main content flow, (3) transition ideas, (4) music/sound recommendation, (5) text overlay suggestions, (6) CTA. Pastikan konsep sesuai dengan trend Reels saat ini.</t>
   </si>
   <si>
     <t>[TOPIK]: topik Reels; [DURASI]: durasi (15/30/60 detik); [STYLE]: gaya (tutorial/entertaining/inspirational); [PRODUK]: produk yang ingin ditampilkan (opsional)</t>
@@ -1535,7 +1535,7 @@
     <t>Merencanakan series Instagram Stories</t>
   </si>
   <si>
-    <t>Sebagai Instagram strategist, buatkan [DURASI] hari Instagram Story series tentang [TOPIK]. Goal: [TUJUAN]. Include interactive elements: [INTERACTIVE]. Untuk setiap hari, berikan: (1) theme hari itu, (2) 3-5 story slides dengan konten, (3) interactive element (poll/quiz/question slider), (4) CTA untuk ke hari berikutnya atau ke link. Buat narrative arc yang membuat orang follow terus.</t>
+    <t>Sebagai perancang strategi Instagram, buatkan [DURASI] hari Instagram Story series tentang [TOPIK]. Tujuan: [TUJUAN]. Include interactive elements: [INTERACTIVE]. Untuk setiap hari, berikan: (1) theme hari itu, (2) 3-5 story slides dengan konten, (3) interactive element (poll/quiz/question slider), (4) CTA untuk ke hari berikutnya atau ke link. Buat narrative arc yang membuat orang follow terus.</t>
   </si>
   <si>
     <t>[TOPIK]: topik series; [DURASI]: berapa hari (3-7 hari); [TUJUAN]: tujuan (engagement/sales/awareness); [INTERACTIVE]: elemen interaktif yang ingin digunakan</t>
@@ -1574,7 +1574,7 @@
     <t>Sebagai meme creator, buatkan 5 konsep meme tentang [SITUASI] di industri [INDUSTRI]. Tone: [TONE]. Jika ada produk [PRODUK], integrate secara subtle tidak hard-sell. Untuk setiap konsep, berikan: (1) meme format (Drake/Distracted Boyfriend/Two Buttons/etc), (2) top text, (3) bottom text, (4) why it's relatable, (5) caption untuk post. Pastikan meme appropriate dan tidak offensive.</t>
   </si>
   <si>
-    <t>[SITUASI]: situasi atau masalah yang dihadapi audience; [INDUSTRI]: industri bisnis Anda; [TONE]: gaya humor (sarkastik/hangat/menggertak diri sendiri); [PRODUK]: produk yang ingin dipromosikan secara subtle</t>
+    <t>[SITUASI]: situasi atau masalah yang dihadapi audiens; [INDUSTRI]: industri bisnis Anda; [TONE]: gaya humor (sarkastik/hangat/menggertak diri sendiri); [PRODUK]: produk yang ingin dipromosikan secara subtle</t>
   </si>
   <si>
     <t>5 konsep meme lengkap dengan caption</t>
@@ -1589,7 +1589,7 @@
     <t>Merencanakan foto perbandingan sebelum dan sesudah yang jujur</t>
   </si>
   <si>
-    <t>Sebagai visual content planner, buat konsep foto sebelum-sesudah untuk [PRODUK] yang menunjukkan [PERUBAHAN]. Untuk menjaga kejujuran, tentukan syarat yang wajib sama di kedua foto: [SYARAT_FOTO] seperti pencahayaan, sudut, jarak, dan waktu. Rancang: komposisi kedua foto, properti pendukung, teks penjelas singkat di masing-masing foto, dan caption pendek. Tambahkan catatan tentang apa yang tidak boleh diedit agar hasil tetap bisa dipercaya.</t>
+    <t>Sebagai perencana konten visual, buat konsep foto sebelum-sesudah untuk [PRODUK] yang menunjukkan [PERUBAHAN]. Untuk menjaga kejujuran, tentukan syarat yang wajib sama di kedua foto: [SYARAT_FOTO] seperti pencahayaan, sudut, jarak, dan waktu. Rancang: komposisi kedua foto, properti pendukung, teks penjelas singkat di masing-masing foto, dan caption pendek. Tambahkan catatan tentang apa yang tidak boleh diedit agar hasil tetap bisa dipercaya.</t>
   </si>
   <si>
     <t>[PRODUK]: produk atau jasa yang menghasilkan perubahan; [PERUBAHAN]: perubahan yang ditunjukkan; [SYARAT_FOTO]: kondisi yang harus sama agar foto jujur</t>
@@ -1697,7 +1697,7 @@
     <t>Memperlihatkan kemasan produk sebagai bagian dari pengalaman</t>
   </si>
   <si>
-    <t>Sebagai packaging content planner, rancang konten yang memperlihatkan [KEMASAN] dengan sorotan pada [DETAIL]. Momen unboxing paling menarik: [UNBOXING_MOMENT]. Rencanakan: shot-by-shot urutan membuka kemasan, sudut kamera untuk tiap shot, teks yang muncul di tiap momen, dan musik atau suara yang mendukung. Sertakan satu shot close-up detail yang paling membedakan kemasan Anda dari pesaing.</t>
+    <t>Sebagai perencana konten kemasan, rancang konten yang memperlihatkan [KEMASAN] dengan sorotan pada [DETAIL]. Momen unboxing paling menarik: [UNBOXING_MOMENT]. Rencanakan: shot-by-shot urutan membuka kemasan, sudut kamera untuk tiap shot, teks yang muncul di tiap momen, dan musik atau suara yang mendukung. Sertakan satu shot close-up detail yang paling membedakan kemasan Anda dari pesaing.</t>
   </si>
   <si>
     <t>[KEMASAN]: kemasan produk Anda; [DETAIL]: detail kemasan yang ingin disorot; [UNBOXING_MOMENT]: momen paling menarik saat membuka</t>
@@ -1715,7 +1715,7 @@
     <t>Mendokumentasikan sehari dalam bisnis Anda</t>
   </si>
   <si>
-    <t>Sebagai documentary content planner, susun outline video sehari dalam bisnis [BISNIS]. Momen menarik: [MOMEN_MENARIK]. Pesan: [PESAN]. Struktur: pembukaan jam berapa dan apa yang sedang dilakukan, 4-6 momen puncak dengan satu kalimat konteks per momen, momen jujur yang tidak sempurna (ini yang membuat relatable), penutup dengan refleksi singkat. Tentukan durasi total, durasi tiap momen, dan cara merekam tanpa mengganggu pekerjaan.</t>
+    <t>Sebagai perencana konten dokumenter, susun outline video sehari dalam bisnis [BISNIS]. Momen menarik: [MOMEN_MENARIK]. Pesan: [PESAN]. Struktur: pembukaan jam berapa dan apa yang sedang dilakukan, 4-6 momen puncak dengan satu kalimat konteks per momen, momen jujur yang tidak sempurna (ini yang membuat relatable), penutup dengan refleksi singkat. Tentukan durasi total, durasi tiap momen, dan cara merekam tanpa mengganggu pekerjaan.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [MOMEN_MENARIK]: momen dalam sehari yang paling menarik; [PESAN]: pesan yang ingin tersampaikan</t>
@@ -1841,7 +1841,7 @@
     <t>Konten dengan suara yang memuaskan untuk produk tertentu</t>
   </si>
   <si>
-    <t>Sebagai ASMR content planner, rancang konten suara untuk [PRODUK] dengan suara kunci [SUARA_KUNCI] dari aksi [AKSI]. Tentukan: urutan aksi dari yang paling halus ke paling kuat, cara merekam suara bersih (jarak mikrofon, ruang yang minim gema), visual yang mendukung suara (close-up), dan durasi tiap aksi. Hindari suara latar lain. Suara harus menjadi bintang, visual pendukung.</t>
+    <t>Sebagai perencana konten ASMR, rancang konten suara untuk [PRODUK] dengan suara kunci [SUARA_KUNCI] dari aksi [AKSI]. Tentukan: urutan aksi dari yang paling halus ke paling kuat, cara merekam suara bersih (jarak mikrofon, ruang yang minim gema), visual yang mendukung suara (close-up), dan durasi tiap aksi. Hindari suara latar lain. Suara harus menjadi bintang, visual pendukung.</t>
   </si>
   <si>
     <t>[PRODUK]: produk yang dipakai; [SUARA_KUNCI]: suara yang paling memuaskan dari produk; [AKSI]: aksi yang menghasilkan suara</t>
@@ -1859,7 +1859,7 @@
     <t>Serial konten dari sudut pandang pelaksana (barista, kasir, kurir)</t>
   </si>
   <si>
-    <t>Sebagai series content planner, rancang serial dari sudut pandang [PERAN] dengan situasi harian [SITUASI] dan insight [PELAJARAN]. Rancang 5 episode: untuk tiap episode tentukan situasi spesifik, konflik atau tantangan kecil, cara penyelesaian, dan insight yang diambil pembaca. Episode pertama harus yang paling kuat untuk memancing orang mengikuti seri. Sertakan format konsisten (pembuka khas, durasi) agar seri terasa utuh.</t>
+    <t>Sebagai perencana konten serial, rancang serial dari sudut pandang [PERAN] dengan situasi harian [SITUASI] dan insight [PELAJARAN]. Rancang 5 episode: untuk tiap episode tentukan situasi spesifik, konflik atau tantangan kecil, cara penyelesaian, dan insight yang diambil pembaca. Episode pertama harus yang paling kuat untuk memancing orang mengikuti seri. Sertakan format konsisten (pembuka khas, durasi) agar seri terasa utuh.</t>
   </si>
   <si>
     <t>[PERAN]: peran yang difokuskan; [SITUASI]: situasi harian yang menarik; [PELAJARAN]: pelajaran atau insight dari posisi itu</t>
@@ -1913,7 +1913,7 @@
     <t>Menampilkan foto pelanggan dengan izin dan apresiasi</t>
   </si>
   <si>
-    <t>Sebagai community content planner, rancang konten fitur pelanggan [PELANGGAN] dengan foto [FOTO] dan status izin [IZIN]. Rencanakan: cara meminta izin yang hormat (template pesan), penyuntingan yang tetap jujur (jangan ubah wajah atau hasil), kredit yang jelas di visual dan caption, dan cara pelanggan lain bisa ikut berbagi (hashtag khusus atau tag). Jika izin belum ada, urutan pertama adalah meminta, bukan memposting.</t>
+    <t>Sebagai perencana konten komunitas, rancang konten fitur pelanggan [PELANGGAN] dengan foto [FOTO] dan status izin [IZIN]. Rencanakan: cara meminta izin yang hormat (template pesan), penyuntingan yang tetap jujur (jangan ubah wajah atau hasil), kredit yang jelas di visual dan caption, dan cara pelanggan lain bisa ikut berbagi (hashtag khusus atau tag). Jika izin belum ada, urutan pertama adalah meminta, bukan memposting.</t>
   </si>
   <si>
     <t>[PELANGGAN]: pelanggan yang ditampilkan; [FOTO]: foto yang akan di-repost; [IZIN]: status izin penggunaan</t>
@@ -2021,7 +2021,7 @@
     <t>Grafik kalender konten atau event untuk pembaca</t>
   </si>
   <si>
-    <t>Sebagai calendar designer, buat grafik kalender [BULAN] berisi [EVENTS] untuk tujuan [TUJUAN]. Tentukan: format grid kalender yang terbaca di ponsel, penanda event (ikon atau warna berbeda per jenis), teks ringkas per event maksimal 3 kata, dan area sorot untuk tanggal paling penting. Kalender harus tetap terbaca saat di-zoom dan cukup jelas saat di-save sebagai referensi.</t>
+    <t>Sebagai desainer kalender, buat grafik kalender [BULAN] berisi [EVENTS] untuk tujuan [TUJUAN]. Tentukan: format grid kalender yang terbaca di ponsel, penanda event (ikon atau warna berbeda per jenis), teks ringkas per event maksimal 3 kata, dan area sorot untuk tanggal paling penting. Kalender harus tetap terbaca saat di-zoom dan cukup jelas saat di-save sebagai referensi.</t>
   </si>
   <si>
     <t>[EVENTS]: daftar tanggal atau event penting; [BULAN]: bulan yang ditampilkan; [TUJUAN]: tujuan kalender (mengingatkan, membangun antisipasi)</t>
@@ -2078,7 +2078,7 @@
     <t>Sebagai feed designer, buat sistem desain sampul untuk pilar [PILAR] dengan warna [BRAND_COLOR]. Referensi tren: [TREN_SAAT_INI]. Tentukan: template dasar per pilar (pembeda visual antar pilar tapi satu keluarga desain), aturan teks sampul (maksimal kata, ukuran, posisi), dan grid feed (bagaimana sampul dilihat sebagai satu kesatuan). Sistem ini harus bisa dikerjakan orang non-desainer dalam 10 menit per sampul.</t>
   </si>
   <si>
-    <t>[PILAR]: daftar content pillar; [BRAND_COLOR]: warna brand; [TREN_SAAT_INI]: gaya sampul yang sedang populer di niche Anda</t>
+    <t>[PILAR]: daftar pilar konten; [BRAND_COLOR]: warna brand; [TREN_SAAT_INI]: gaya sampul yang sedang populer di niche Anda</t>
   </si>
   <si>
     <t>Sistem desain sampul per pilar yang mudah dikerjakan</t>
@@ -2147,7 +2147,7 @@
     <t>Menyiapkan pencahayaan dengan alat terbatas</t>
   </si>
   <si>
-    <t>Sebagai lighting consultant, buat panduan pencahayaan di [RUANG] dengan alat [ALAT_CAHA] untuk konten [JENIS_KONTEN]. Jelaskan: posisi sumber cahaya utama (menghadap wajah atau produk dari 45 derajat), cara memanfaatkan jendela alami beserta jam terbaiknya, cara mengatasi bayangan keras dengan alat murah (kertas putih, kain), dan kesalahan umum (cahaya dari belakang, campuran warna cahaya). Sertakan setup untuk 2 skenario: siang dan malam.</t>
+    <t>Sebagai konsultan pencahayaan, buat panduan pencahayaan di [RUANG] dengan alat [ALAT_CAHA] untuk konten [JENIS_KONTEN]. Jelaskan: posisi sumber cahaya utama (menghadap wajah atau produk dari 45 derajat), cara memanfaatkan jendela alami beserta jam terbaiknya, cara mengatasi bayangan keras dengan alat murah (kertas putih, kain), dan kesalahan umum (cahaya dari belakang, campuran warna cahaya). Sertakan setup untuk 2 skenario: siang dan malam.</t>
   </si>
   <si>
     <t>[RUANG]: ruangan yang dipakai; [ALAT_CAHA]: alat cahaya yang tersedia; [JENIS_KONTEN]: jenis konten yang direkam</t>
@@ -2201,13 +2201,13 @@
     <t>Merencanakan campaign yang mendorong UGC</t>
   </si>
   <si>
-    <t>Sebagai campaign strategist, buatkan UGC campaign untuk [BRAND] yang mempromosikan [PRODUK]. Goal: [TUJUAN]. Insentif: [INCENTIVE]. Sertakan: (1) nama campaign yang catchy, (2) hashtag campaign, (3) mekanisme partisipasi, (4) kriteria konten yang diharapkan, (5) timeline campaign (2-4 minggu), (6) cara seleksi pemenang, (7) strategi amplifikasi, (8) template announcement post. Pastikan campaign mudah diikuti dan motivating.</t>
+    <t>Sebagai perancang strategi kampanye, buatkan UGC campaign untuk [BRAND] yang mempromosikan [PRODUK]. Tujuan: [TUJUAN]. Insentif: [INCENTIVE]. Sertakan: (1) nama kampanye yang menarik, (2) hashtag kampanye, (3) mekanisme partisipasi, (4) kriteria konten yang diharapkan, (5) linimasa kampanye (2-4 minggu), (6) cara seleksi pemenang, (7) strategi amplifikasi, (8) template announcement post. Pastikan campaign mudah diikuti dan memotivasi.</t>
   </si>
   <si>
     <t>[BRAND]: nama brand Anda; [PRODUK]: produk yang ingin dipromosikan; [TUJUAN]: tujuan campaign (awareness/sales/engagement); [INCENTIVE]: insentif untuk partisipan</t>
   </si>
   <si>
-    <t>Plan UGC campaign lengkap dengan mekanisme dan timeline</t>
+    <t>Rencana kampanye UGC lengkap dengan mekanisme dan linimasa</t>
   </si>
   <si>
     <t>T-121</t>
@@ -2240,7 +2240,7 @@
     <t>Membalas direct message dengan professional</t>
   </si>
   <si>
-    <t>Sebagai customer service specialist, buatkan 3 template balasan DM [JENIS_DM] untuk [BRAND]. Goal: [TUJUAN]. Tone: [TONE]. Setiap template harus: (1) acknowledge pesan dengan nama customer, (2) jawab pertanyaan atau address concern, (3) berikan next step yang jelas, (4) akhiri dengan question atau CTA yang mendorong response. Include bagian yang bisa dipersonalisasi.</t>
+    <t>Sebagai spesialis layanan pelanggan, buatkan 3 template balasan DM [JENIS_DM] untuk [BRAND]. Tujuan: [TUJUAN]. Tone: [TONE]. Setiap template harus: (1) menanggapi pesan dengan menyebut nama pelanggan, (2) jawab pertanyaan atau tanggapi keluhan, (3) berikan langkah berikutnya yang jelas, (4) akhiri dengan pertanyaan atau CTA yang mendorong respons. Sertakan bagian yang bisa dipersonalisasi.</t>
   </si>
   <si>
     <t>[JENIS_DM]: jenis DM (inquiry/complaint/collaboration/general); [BRAND]: nama brand Anda; [TUJUAN]: tujuan balasan (convert/retain/inform); [TONE]: tone komunikasi (friendly/professional/casual)</t>
@@ -2255,13 +2255,13 @@
     <t>Ide Polling dan Pertanyaan</t>
   </si>
   <si>
-    <t>Membuat interactive content untuk Stories</t>
-  </si>
-  <si>
-    <t>Sebagai engagement strategist, buatkan 10 ide poll dan question untuk Stories tentang [TOPIK] untuk [AUDIENS]. Goal: [TUJUAN]. Funnel stage: [FUNNEL]. Untuk setiap ide, berikan: (1) type (poll/quiz/question slider/emoji slider), (2) question text, (3) options (untuk poll/quiz), (4) follow-up action berdasarkan jawaban. Variasikan antara fun, insightful, dan actionable questions.</t>
-  </si>
-  <si>
-    <t>[TOPIK]: topik yang ingin didiskusikan; [AUDIENS]: pembeli atau pengikut yang dituju; [TUJUAN]: tujuan (engagement/research/feedback); [FUNNEL]: tahap funnel (awareness/consideration/decision)</t>
+    <t>Membuat konten interaktif untuk Stories</t>
+  </si>
+  <si>
+    <t>Sebagai perancang strategi engagement, buatkan 10 ide polling dan pertanyaan untuk Stories tentang [TOPIK] untuk [AUDIENS]. Tujuan: [TUJUAN]. Funnel stage: [FUNNEL]. Untuk setiap ide, berikan: (1) jenis (poll/kuis/slider pertanyaan/slider emoji), (2) teks pertanyaan, (3) pilihan (untuk poll/kuis), (4) tindak lanjut berdasarkan jawaban. Variasikan antara pertanyaan yang seru, memberi wawasan, dan bisa ditindaklanjuti.</t>
+  </si>
+  <si>
+    <t>[TOPIK]: topik yang ingin didiskusikan; [AUDIENS]: pembeli atau pengikut yang dituju; [TUJUAN]: tujuan (engagement/riset/masukan); [FUNNEL]: tahap funnel (awareness/consideration/decision)</t>
   </si>
   <si>
     <t>10 ide konten interaktif yang mengundang interaksi</t>
@@ -2276,7 +2276,7 @@
     <t>Merencanakan contest atau giveaway</t>
   </si>
   <si>
-    <t>Sebagai campaign manager, buatkan mechanics untuk contest [PRIZE] dengan goal [TUJUAN]. Durasi: [DURASI]. Mechanics: [MECHANICS]. Sertakan: (1) nama contest yang catchy, (2) rules dan syarat partisipasi (5-7 poin), (3) step-by-step cara ikut, (4) kriteria pemenang, (5) timeline announcement, (6) disclaimer dan legal notes, (7) caption announcement post, (8) reminder posts (3 variasi), (9) winner announcement template. Pastikan mechanics mudah dipahami dan motivating.</t>
+    <t>Sebagai manajer kampanye, buatkan mekanisme lomba berhadiah [PRIZE] dengan tujuan [TUJUAN]. Durasi: [DURASI]. Mekanisme: [MECHANICS]. Sertakan: (1) nama lomba yang menarik, (2) aturan dan syarat partisipasi (5-7 poin), (3) langkah demi langkah cara ikut, (4) kriteria pemenang, (5) linimasa pengumuman, (6) disclaimer dan catatan legal, (7) caption posting pengumuman, (8) posting pengingat (3 variasi), (9) templat pengumuman pemenang. Pastikan mekanismenya mudah dipahami dan memotivasi.</t>
   </si>
   <si>
     <t>[PRIZE]: hadiah yang diberikan; [TUJUAN]: tujuan (followers/engagement/UGC/sales); [DURASI]: lama contest (3-14 hari); [MECHANICS]: mekanisme yang diinginkan (like+comment/share/UGC)</t>
@@ -2297,7 +2297,7 @@
     <t>Sebagai pembangun komunitas, buatkan strategi untuk membangun komunitas [BRAND] di bidang [NICHE] menggunakan [PLATFORM]. Tujuan: [TUJUAN]. Sertakan: (1) nama komunitas yang mudah diingat, (2) manfaat nyata untuk anggota, (3) proses penyambutan anggota baru, (4) kegiatan rutin mingguan dan tradisi komunitas, (5) pedoman moderasi, (6) pemicu interaksi antaranggota, (7) taktik pertumbuhan, (8) metrik untuk mengukur keberhasilan. Fokus pada koneksi yang tulus, bukan sekadar jumlah anggota.</t>
   </si>
   <si>
-    <t>[BRAND]: nama brand Anda; [NICHE]: niche atau industri; [PLATFORM]: platform utama (Instagram Group/Facebook Group/Discord/Telegram); [TUJUAN]: tujuan komunitas (support/feedback/advocacy)</t>
+    <t>[BRAND]: nama brand Anda; [NICHE]: niche atau industri; [PLATFORM]: platform utama (Instagram Group/Facebook Group/Discord/Telegram); [TUJUAN]: tujuan komunitas (dukungan/masukan/advokasi)</t>
   </si>
   <si>
     <t>Strategi komunitas lengkap dengan rencana implementasi</t>
@@ -2312,7 +2312,7 @@
     <t>Mengisi Instagram Story dengan pertanyaan interaktif yang mengundang jawaban</t>
   </si>
   <si>
-    <t>Sebagai media sosial strategist, buatkan 10 pertanyaan untuk question sticker Instagram Story [BISNIS] yang menjual [PRODUK]. Konteks kampanye: [MOMEN]. Tujuan: [TUJUAN]. Untuk setiap pertanyaan berikan: teks pertayaannya, alasan mengapa itu mengundang jawaban, cara memanfaatkan jawaban yang masuk (share ke story, jadi konten baru, atau jadi leads), dan perkiraan tingkat respons (tinggi/sedang/rendah). Campur pertanyaan ringan yang mudah dijawab dengan pertanyaan dalam yang menghasilkan riset pasar.</t>
+    <t>Sebagai perancang strategi media sosial, buatkan 10 pertanyaan untuk question sticker Instagram Story [BISNIS] yang menjual [PRODUK]. Konteks kampanye: [MOMEN]. Tujuan: [TUJUAN]. Untuk setiap pertanyaan berikan: teks pertayaannya, alasan mengapa itu mengundang jawaban, cara memanfaatkan jawaban yang masuk (share ke story, jadi konten baru, atau jadi leads), dan perkiraan tingkat respons (tinggi/sedang/rendah). Campur pertanyaan ringan yang mudah dijawab dengan pertanyaan dalam yang menghasilkan riset pasar.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk atau jasa utama; [MOMEN]: momen atau kampanye yang sedang berjalan; [TUJUAN]: tujuan sesi tanya jawab (riset/engagement/konversi)</t>
@@ -2330,7 +2330,7 @@
     <t>Membuat konten pilihan ganda yang gampang dijawab follower</t>
   </si>
   <si>
-    <t>Sebagai content creator, buatkan [JUMLAH] seri konten "This or That" untuk [BISNIS] di [PLATFORM]. Produk utama: [PRODUK]. Setiap seri berisi 8 pasangan pilihan yang relevan dengan produk atau gaya hidup target market, misalnya dua varian rasa, dua gaya tampilan, atau dua kebiasaan. Untuk setiap pasangan tulis: opsi A, opsi B, hook satu kalimat pembuka, dan kalimat penutup yang mengajak komentar memilih. Pastikan pilihan tidak ada yang benar atau salah agar semua orang nyaman menjawab.</t>
+    <t>Sebagai kreator konten, buatkan [JUMLAH] seri konten "This or That" untuk [BISNIS] di [PLATFORM]. Produk utama: [PRODUK]. Setiap seri berisi 8 pasangan pilihan yang relevan dengan produk atau gaya hidup target market, misalnya dua varian rasa, dua gaya tampilan, atau dua kebiasaan. Untuk setiap pasangan tulis: opsi A, opsi B, hook satu kalimat pembuka, dan kalimat penutup yang mengajak komentar memilih. Pastikan pilihan tidak ada yang benar atau salah agar semua orang nyaman menjawab.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk atau jasa utama; [JUMLAH]: berapa seri yang ingin dibuat; [PLATFORM]: platform yang digunakan</t>
@@ -2402,7 +2402,7 @@
     <t>Meluncurkan tantangan multi hari yang membuat audiens ikut berpartisipasi</t>
   </si>
   <si>
-    <t>Sebagai campaign strategist, rancang tantangan [DURASI] hari untuk [BISNIS] yang membantu peserta mencapai [HASIL]. Produk pendukung: [PRODUK]. Hashtag: [HASHTAG]. Sertakan: nama menarik untuk tantangan, janji hasil yang realistis, tugas harian yang ringan (maksimal 10 menit per hari), template caption harian untuk peserta, aturan partisipasi, cara memilih peserta unggulan tiap hari, dan rencana konten Anda sendiri selama tantangan berjalan. Akhiri dengan strategi konversi peserta menjadi pembeli setelah tantangan selesai.</t>
+    <t>Sebagai perancang strategi kampanye, rancang tantangan [DURASI] hari untuk [BISNIS] yang membantu peserta mencapai [HASIL]. Produk pendukung: [PRODUK]. Hashtag: [HASHTAG]. Sertakan: nama menarik untuk tantangan, janji hasil yang realistis, tugas harian yang ringan (maksimal 10 menit per hari), template caption harian untuk peserta, aturan partisipasi, cara memilih peserta unggulan tiap hari, dan rencana konten Anda sendiri selama tantangan berjalan. Akhiri dengan strategi konversi peserta menjadi pembeli setelah tantangan selesai.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk atau jasa utama; [DURASI]: lama tantangan (5/7/14/30 hari); [HASIL]: perubahan yang peserta ingin capai; [HASHTAG]: hashtag tantangan</t>
@@ -2444,7 +2444,7 @@
     <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: daftar produk yang akan dijual di live; [HARGA_SPECIAL]: harga khusus live; [STOK]: batas stok promo</t>
   </si>
   <si>
-    <t>Skrip live shopping lengkap per produk dengan closing dan follow up</t>
+    <t>Naskah live shopping lengkap per produk dengan penutup dan tindak lanjut</t>
   </si>
   <si>
     <t>T-134</t>
@@ -2456,13 +2456,13 @@
     <t>Meminta masukan pelanggan dengan cara yang menghasilkan jawaban jujur</t>
   </si>
   <si>
-    <t>Sebagai customer experience specialist, buatkan 3 versi pesan meminta feedback tentang [PRODUK] melalui [KANAL] untuk [BISNIS]. Kebijakan insentif: [INSENTIF]. Versi pertama singkat 3 kalimat, versi kedua santai dengan pertanyaan spesifik, versi ketiga formal dengan struktur pertanyaan 5 poin. Setiap versi harus menyebut waktunya (berapa hari setelah pembelian), memudahkan penerima menjawab tanpa mikir lama, dan menghindari kata yang memaksa atau memujuk berlebihan. Tambahkan kalimat respons untuk feedback positif dan kalimat respons untuk feedback negatif.</t>
+    <t>Sebagai spesialis pengalaman pelanggan, buatkan 3 versi pesan meminta masukan tentang [PRODUK] melalui [KANAL] untuk [BISNIS]. Kebijakan insentif: [INSENTIF]. Versi pertama singkat 3 kalimat, versi kedua santai dengan pertanyaan spesifik, versi ketiga formal dengan struktur pertanyaan 5 poin. Setiap versi harus menyebut waktunya (berapa hari setelah pembelian), memudahkan penerima menjawab tanpa mikir lama, dan menghindari kata yang memaksa atau memujuk berlebihan. Tambahkan kalimat respons untuk masukan positif dan kalimat respons untuk masukan negatif.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk yang baru dibeli atau dipakai pelanggan; [KANAL]: kanal permintaan (WA/email/DM/form); [INSENTIF]: keputusan apakah insentif diberikan (ya/tidak)</t>
   </si>
   <si>
-    <t>Tiga template pesan feedback siap pakai dengan rencana respons</t>
+    <t>Tiga templat pesan masukan siap pakai dengan rencana respons</t>
   </si>
   <si>
     <t>T-135</t>
@@ -2492,13 +2492,13 @@
     <t>Mengundang pelanggan setia mencoba produk baru sebelum diluncurkan</t>
   </si>
   <si>
-    <t>Sebagai product marketing specialist, buatkan undangan program beta tester untuk [PRODUK_BARU] dari [BISNIS]. Kuota: [JUMLAH_TESTER]. Kriteria: [KRITERIA]. Sertakan: hook pengumuman yang membuat orang merasa terpilih, manfaat yang didapat tester (akses awal, harga khusus, nama dicantumkan), kewajiban tester (pakai, beri masukan, tunggu waktu tertentu), cara mendaftar, timeline program dari seleksi sampai peluncuran, dan template pesan penerimaan serta penolakan yang tetap menjaga hubungan baik.</t>
+    <t>Sebagai spesialis pemasaran produk, buatkan undangan program beta tester untuk [PRODUK_BARU] dari [BISNIS]. Kuota: [JUMLAH_TESTER]. Kriteria: [KRITERIA]. Sertakan: hook pengumuman yang membuat orang merasa terpilih, manfaat yang didapat tester (akses awal, harga khusus, nama dicantumkan), kewajiban tester (pakai, beri masukan, tunggu waktu tertentu), cara mendaftar, linimasa program dari seleksi sampai peluncuran, dan template pesan penerimaan serta penolakan yang tetap menjaga hubungan baik.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PRODUK_BARU]: produk baru yang diuji; [JUMLAH_TESTER]: jumlah beta tester yang dicari; [KRITERIA]: kriteria tester ideal</t>
   </si>
   <si>
-    <t>Paket undangan beta lengkap dengan timeline dan template pesan</t>
+    <t>Paket undangan beta lengkap dengan linimasa dan template pesan</t>
   </si>
   <si>
     <t>T-137</t>
@@ -2564,7 +2564,7 @@
     <t>Menyapa pelanggan di hari spesial mereka agar merasa dikenal</t>
   </si>
   <si>
-    <t>Sebagai customer relationship specialist, buatkan sistem sapaan ulang tahun dan ulang tahun pembelian pertama untuk [BISNIS] melalui [KANAL]. Produk: [PRODUK]. Penawaran spesial: [PENAWARAN]. Sertakan: template sapaan tanpa penawaran yang tulus dan singkat, template sapaan dengan penawaran yang tidak terasa maksa, template untuk pelanggan yang sudah lama tidak belanja, jadwal pengiriman (tepat hari atau H minus), dan catatan privasi agar data tanggal lahir diminta dengan sopan. Tambahkan 2 contoh kalimat balasan jika pelanggan membalas.</t>
+    <t>Sebagai spesialis hubungan pelanggan, buatkan sistem sapaan ulang tahun dan ulang tahun pembelian pertama untuk [BISNIS] melalui [KANAL]. Produk: [PRODUK]. Penawaran spesial: [PENAWARAN]. Sertakan: template sapaan tanpa penawaran yang tulus dan singkat, template sapaan dengan penawaran yang tidak terasa maksa, template untuk pelanggan yang sudah lama tidak belanja, jadwal pengiriman (tepat hari atau H minus), dan catatan privasi agar data tanggal lahir diminta dengan sopan. Tambahkan 2 contoh kalimat balasan jika pelanggan membalas.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk atau jasa utama; [PENAWARAN]: penawaran spesial hari ulang tahun (opsional); [KANAL]: kanal pengiriman sapaan (WA/email/DM)</t>
@@ -2600,7 +2600,7 @@
     <t>Merespons komplain pelanggan dengan cepat dan menjaga reputasi</t>
   </si>
   <si>
-    <t>Sebagai customer service expert, buatkan framework balasan komplain untuk [BISNIS] dengan tone [TONE]. Kasus umum: [KASUS]. Kebijakan solusi: [KEBIJAKAN]. Sertakan: 4 langkah struktur balasan (akui, minta detail, solusi, tindak lanjut), template respons publik untuk komentar yang terlihat banyak orang, template respons privat untuk detail data, kalimat untuk komplain yang salah sasaran, dan batas waktu standar penanganan. Tambahkan 3 kesalahan balasan yang justru memperburuk situasi beserta contohnya.</t>
+    <t>Sebagai ahli layanan pelanggan, buatkan framework balasan komplain untuk [BISNIS] dengan tone [TONE]. Kasus umum: [KASUS]. Kebijakan solusi: [KEBIJAKAN]. Sertakan: 4 langkah struktur balasan (akui, minta detail, solusi, tindak lanjut), template respons publik untuk komentar yang terlihat banyak orang, template respons privat untuk detail data, kalimat untuk komplain yang salah sasaran, dan batas waktu standar penanganan. Tambahkan 3 kesalahan balasan yang justru memperburuk situasi beserta contohnya.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [KASUS]: jenis komplain yang sering terjadi; [KEBIJAKAN]: kebijakan solusi (refund/tukar/kompensasi); [TONE]: tone respons brand</t>
@@ -2654,7 +2654,7 @@
     <t>Menampilkan cerita pelanggan sebagai konten rutin yang membangun kepercayaan</t>
   </si>
   <si>
-    <t>Sebagai content producer, rancang seri "pelanggan sorotan" untuk [BISNIS] yang menjual [PRODUK]. Tayang [FREKUENSI] sebulan dengan format [FORMAT]. Sertakan: struktur konten (hook cerita, latar belakang pelanggan, masalah awal, pengalaman pakai produk, hasil yang didapat), daftar pertanyaan wawancara singkat untuk pelanggan, template izin penggunaan cerita dan foto, desain judul seri yang konsisten, dan cara mengakhiri konten dengan ajakan yang tidak menggurui. Beri 1 contoh naskah lengkap berdasarkan profil pelanggan fiktif.</t>
+    <t>Sebagai produser konten, rancang seri "pelanggan sorotan" untuk [BISNIS] yang menjual [PRODUK]. Tayang [FREKUENSI] sebulan dengan format [FORMAT]. Sertakan: struktur konten (hook cerita, latar belakang pelanggan, masalah awal, pengalaman pakai produk, hasil yang didapat), daftar pertanyaan wawancara singkat untuk pelanggan, template izin penggunaan cerita dan foto, desain judul seri yang konsisten, dan cara mengakhiri konten dengan ajakan yang tidak menggurui. Beri 1 contoh naskah lengkap berdasarkan profil pelanggan fiktif.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk atau jasa utama; [FREKUENSI]: berapa kali sebulan seri ini tayang; [FORMAT]: format konten (carousel/reel/story)</t>
@@ -2726,7 +2726,7 @@
     <t>Membuka konten dengan kalimat yang mengundang interaksi tanpa manipulasi</t>
   </si>
   <si>
-    <t>Sebagai engagement strategist, buatkan 15 hook pembuka konten yang memancing interaksi jujur untuk [BISNIS] dengan topik [TOPIK]. Target: [AUDIENS]. Produk: [PRODUK]. Kategori hook: pertanyaan personal, kesepakatan pendapat, kesalahan umum, pengakuan jujur, dan tantangan ringan. Untuk setiap hook tulis kalimatnya dan alasan mengapa orang terdorong merespons. Hindari hook yang meminta like atau follow secara langsung, hook yang mengancam, dan hook yang menipu isi konten. Tandai 3 hook terbaik untuk audiens pemula dan 3 untuk audiens ahli.</t>
+    <t>Sebagai perancang strategi engagement, buatkan 15 hook pembuka konten yang memancing interaksi jujur untuk [BISNIS] dengan topik [TOPIK]. Target: [AUDIENS]. Produk: [PRODUK]. Kategori hook: pertanyaan personal, kesepakatan pendapat, kesalahan umum, pengakuan jujur, dan tantangan ringan. Untuk setiap hook tulis kalimatnya dan alasan mengapa orang terdorong merespons. Hindari hook yang meminta like atau follow secara langsung, hook yang mengancam, dan hook yang menipu isi konten. Tandai 3 hook terbaik untuk audiens pemula dan 3 untuk audiens ahli.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk atau jasa utama; [TOPIK]: topik konten yang akan diposting; [AUDIENS]: pembeli atau pengikut yang dituju</t>
@@ -2780,7 +2780,7 @@
     <t>Menghubungi kreator konten untuk kerja sama promosi dengan cara yang dibalas</t>
   </si>
   <si>
-    <t>Sebagai influencer marketing specialist, buatkan 2 template pesan outreach kepada [KREATOR] untuk kerja sama dengan [BISNIS]. Produk: [PRODUK]. Bentuk kerja sama: [BENTUK_KERJA_SAMA]. Versi pertama pendek 5 kalimat untuk DM pertama yang menunjukkan Anda benar benar menonton kontennya dengan menyebut 1 karya spesifik. Versi kedua detail dengan rincian bentuk kerja sama, benefit mereka, dan langkah berikutnya. Tambahkan template follow up jika 5 hari tidak dibalas yang tetap sopan tanpa terasa menekan, dan template respons jika mereka meminta harga lebih tinggi dari anggaran.</t>
+    <t>Sebagai spesialis pemasaran influencer, buatkan 2 template pesan outreach kepada [KREATOR] untuk kerja sama dengan [BISNIS]. Produk: [PRODUK]. Bentuk kerja sama: [BENTUK_KERJA_SAMA]. Versi pertama pendek 5 kalimat untuk DM pertama yang menunjukkan Anda benar benar menonton kontennya dengan menyebut 1 karya spesifik. Versi kedua detail dengan rincian bentuk kerja sama, benefit mereka, dan langkah berikutnya. Tambahkan template follow up jika 5 hari tidak dibalas yang tetap sopan tanpa terasa menekan, dan template respons jika mereka meminta harga lebih tinggi dari anggaran.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [KREATOR]: profil kreator yang dituju (nama/niche/ukuran audiens); [PRODUK]: produk yang akan dipromosikan; [BENTUK_KERJA_SAMA]: bentuk kerja sama (barter/fee/afiliasi)</t>
@@ -2834,7 +2834,7 @@
     <t>Merancang konten yang memang sengaja disimpan atau dibagikan audiens</t>
   </si>
   <si>
-    <t>Sebagai content optimization specialist, buatkan 10 konsep konten yang dirancang agar disimpan atau dibagikan untuk [BISNIS] dengan keahlian [TOPIK_KEAHLIAN]. Produk: [PRODUK]. Format: [FORMAT]. Pisahkan dua jenis: konten simpan (checklist, panduan bertahap, daftar sumber, rumus hitung) dan konten bagikan (yang membuat orang menandai teman, konten relatable, kabar bermanfaat mendesak). Untuk setiap konsep tulis judul, isi poin utama, kalimat penutup yang menyebut manfaat disimpan, dan alasan mengapa audiens merasa perlu menyimpannya.</t>
+    <t>Sebagai spesialis optimasi konten, buatkan 10 konsep konten yang dirancang agar disimpan atau dibagikan untuk [BISNIS] dengan keahlian [TOPIK_KEAHLIAN]. Produk: [PRODUK]. Format: [FORMAT]. Pisahkan dua jenis: konten simpan (checklist, panduan bertahap, daftar sumber, rumus hitung) dan konten bagikan (yang membuat orang menandai teman, konten relatable, kabar bermanfaat mendesak). Untuk setiap konsep tulis judul, isi poin utama, kalimat penutup yang menyebut manfaat disimpan, dan alasan mengapa audiens merasa perlu menyimpannya.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk atau jasa utama; [TOPIK_KEAHLIAN]: topik yang Anda kuasai dan dicari audiens; [FORMAT]: format konten yang disukai audiens Anda</t>
@@ -2888,7 +2888,7 @@
     <t>Membangunkan follower yang tidak pernah berinteraksi sama sekali</t>
   </si>
   <si>
-    <t>Sebagai audience engagement specialist, rancang kampanye [DURASI] mengaktifkan kembali follower pasif [BISNIS] di [PLATFORM]. Produk: [PRODUK]. Sertakan: cara mengidentifikasi follower pasif tanpa aplikasi berbayar, 4 taktik berurutan (konten ajakan langsung, konten pengingat nilai, sesi tanya jawab live, penawaran khusus follower), naskah untuk tiap taktik, ekspektasi hasil yang jujur karena tidak semua follower akan aktif, dan keputusan akhir jika kampanye gagal yaitu fokus ke audiens baru atau konten yang berbeda.</t>
+    <t>Sebagai spesialis engagement audiens, rancang kampanye [DURASI] mengaktifkan kembali follower pasif [BISNIS] di [PLATFORM]. Produk: [PRODUK]. Sertakan: cara mengidentifikasi follower pasif tanpa aplikasi berbayar, 4 taktik berurutan (konten ajakan langsung, konten pengingat nilai, sesi tanya jawab live, penawaran khusus follower), naskah untuk tiap taktik, ekspektasi hasil yang jujur karena tidak semua follower akan aktif, dan keputusan akhir jika kampanye gagal yaitu fokus ke audiens baru atau konten yang berbeda.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang dianalisis; [PRODUK]: produk atau jasa utama; [DURASI]: lama kampanye reaktivasi</t>
@@ -2906,7 +2906,7 @@
     <t>Menjaga hubungan dengan pembeli setelah transaksi agar repeat order</t>
   </si>
   <si>
-    <t>Sebagai customer success specialist, buatkan rangkaian tindak lanjut pasca pembelian untuk [PRODUK] melalui [KANAL] dengan jeda [INTERVAL]. Pesan 1: ucapan terima kasih dan panduan pakai singkat. Pesan 2: pertanyaan pengalaman pakai dan penawaran bantuan. Pesan 3: permintaan ulasan atau testimoni. Pesan 4: rekomendasi produk pendamping yang melengkapi pembelian pertama. Pesan 5: sapaan rutin tanpa jualan untuk menjaga hubungan. Setiap pesan maksimal 60 kata, hangat, tidak berbau transaksi kecuali yang memang bertujuan menjual.</t>
+    <t>Sebagai spesialis keberhasilan pelanggan, buatkan rangkaian tindak lanjut pasca pembelian untuk [PRODUK] melalui [KANAL] dengan jeda [INTERVAL]. Pesan 1: ucapan terima kasih dan panduan pakai singkat. Pesan 2: pertanyaan pengalaman pakai dan penawaran bantuan. Pesan 3: permintaan ulasan atau testimoni. Pesan 4: rekomendasi produk pendamping yang melengkapi pembelian pertama. Pesan 5: sapaan rutin tanpa jualan untuk menjaga hubungan. Setiap pesan maksimal 60 kata, hangat, tidak berbau transaksi kecuali yang memang bertujuan menjual.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk yang baru dibeli; [KANAL]: kanal tindak lanjut (WA/DM/email); [INTERVAL]: jeda antar pesan yang diinginkan</t>
@@ -2924,7 +2924,7 @@
     <t>Menangani situasi krisis atau komplain viral</t>
   </si>
   <si>
-    <t>Sebagai PR specialist, buatkan crisis communication plan untuk [SITUASI] dengan severity [SEVERITY] di [PLATFORM]. Stakeholder: [STAKEHOLDER]. Sertakan: (1) holding statement (50 kata) untuk immediate response, (2) detailed apology letter (200 kata), (3) FAQ untuk anticipated questions (5-7 Q&amp;A), (4) internal memo untuk tim, (5) follow-up update template, (6) recovery content ideas. Tone harus empathetic, accountable, dan solution-oriented. Hindari defensive language.</t>
+    <t>Sebagai PR specialist, buatkan rencana komunikasi krisis untuk [SITUASI] dengan tingkat keparahan [SEVERITY] di [PLATFORM]. Pemangku kepentingan: [STAKEHOLDER]. Sertakan: (1) pernyataan awal (50 kata) untuk respons pertama, (2) surat permintaan maaf terperinci (200 kata), (3) FAQ untuk pertanyaan yang mungkin muncul (5-7 tanya jawab), (4) memo internal untuk tim, (5) templat pembaruan tindak lanjut, (6) ide konten pemulihan. Nada harus empatik, bertanggung jawab, dan berorientasi solusi. Hindari bahasa defensif.</t>
   </si>
   <si>
     <t>[SITUASI]: jenis krisis (product issue/service failure/miscommunication/public complaint); [SEVERITY]: tingkat keparahan (minor/moderate/major); [PLATFORM]: platform dimana krisis terjadi; [STAKEHOLDER]: pihak yang terdampak</t>
@@ -3020,7 +3020,7 @@
     <t>Sebagai analis pemasaran, buatkan perhitungan ROI untuk aktivitas media sosial [PERIODE]. Biaya: [COSTS]. Pendapatan: [REVENUE]. Target: [GOALS]. Sertakan: (1) perhitungan ROI langsung (pendapatan - biaya) / biaya x 100%, (2) biaya per pembelian (CPA), (3) nilai seumur hidup pelanggan (CLV) dari media sosial, (4) metrik nilai merek (jangkauan/tayangan/penyebutan), (5) perkiraan nilai interaksi, (6) perbandingan dengan tolok ukur industri, (7) rekomendasi mengoptimalkan ROI, (8) proyeksi periode berikutnya. Sajikan dalam format yang mudah dipahami pemangku kepentingan.</t>
   </si>
   <si>
-    <t>[PERIODE]: periode perhitungan (bulanan/kuartalan/tahunan); [COSTS]: biaya yang dikeluarkan (ads/tools/time); [REVENUE]: revenue yang di-generate (sales/leads/valuasi brand); [GOALS]: goal bisnis utama</t>
+    <t>[PERIODE]: periode perhitungan (bulanan/kuartalan/tahunan); [COSTS]: biaya yang dikeluarkan (ads/tools/time); [REVENUE]: revenue yang di-generate (sales/leads/valuasi brand); [GOALS]: tujuan bisnis utama</t>
   </si>
   <si>
     <t>Laporan ROI lengkap dengan metrik keuangan dan rekomendasi</t>
@@ -3251,7 +3251,7 @@
     <t>Menghitung biaya mendapatkan satu pembeli agar tidak jual rugi</t>
   </si>
   <si>
-    <t>Sebagai unit economics analyst, hitung customer acquisition cost untuk [BISNIS]. Biaya: [BIAYA]. Pembeli baru: [PEMBELI_BARU]. Harga produk: [HARGA_PRODUK]. Sertakan: perhitungan CAC total dan CAC per kanal jika data memungkinkan, perbandingan CAC dengan margin per unit agar terlihat untung atau rugi per pembeli baru, aturan berapa kali CAC dibanding margin yang masih sehat untuk bisnis kecil, biaya tersembunyi yang sering lupa dihitung, dan 3 cara menurunkan CAC tanpa menurunkan kualitas pembeli. Sajikan rumus yang bisa dipakai ulang tiap bulan.</t>
+    <t>Sebagai analis ekonomi unit, hitung customer acquisition cost untuk [BISNIS]. Biaya: [BIAYA]. Pembeli baru: [PEMBELI_BARU]. Harga produk: [HARGA_PRODUK]. Sertakan: perhitungan CAC total dan CAC per kanal jika data memungkinkan, perbandingan CAC dengan margin per unit agar terlihat untung atau rugi per pembeli baru, aturan berapa kali CAC dibanding margin yang masih sehat untuk bisnis kecil, biaya tersembunyi yang sering lupa dihitung, dan 3 cara menurunkan CAC tanpa menurunkan kualitas pembeli. Sajikan rumus yang bisa dipakai ulang tiap bulan.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [BIAYA]: rincian biaya (iklan/alat/gaji/produksi konten); [PEMBELI_BARU]: jumlah pembeli baru dalam periode; [HARGA_PRODUK]: harga produk dan margin per unit</t>
@@ -3269,7 +3269,7 @@
     <t>Mengestimasi nilai jangka panjang satu pelanggan untuk keputusan promosi</t>
   </si>
   <si>
-    <t>Sebagai retention analyst, estimasikan customer lifetime value untuk [BISNIS]. Produk dan harga: [PRODUK]. Data perilaku beli: [DATA]. Margin: [MARGIN]. Sertakan: cara menghitung CLV sederhana untuk bisnis kecil dengan data terbatas, perhitungan dari data saya, interpretasi berapa yang layak dibelanjakan untuk mendapatkan dan mempertahankan satu pelanggan, cara menaikkan CLV tanpa produk baru (repeat order, upsell, program langganan), dan bandingkan nilai pelanggan baru dengan pelanggan lama untuk memutuskan prioritas promosi.</t>
+    <t>Sebagai analis retensi, estimasikan customer lifetime value untuk [BISNIS]. Produk dan harga: [PRODUK]. Data perilaku beli: [DATA]. Margin: [MARGIN]. Sertakan: cara menghitung CLV sederhana untuk bisnis kecil dengan data terbatas, perhitungan dari data saya, interpretasi berapa yang layak dibelanjakan untuk mendapatkan dan mempertahankan satu pelanggan, cara menaikkan CLV tanpa produk baru (repeat order, upsell, program langganan), dan bandingkan nilai pelanggan baru dengan pelanggan lama untuk memutuskan prioritas promosi.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: daftar produk dan harganya; [DATA]: data frekuensi beli dan jangka waktu pelanggan bertahan; [MARGIN]: margin rata rata per transaksi</t>
@@ -3287,7 +3287,7 @@
     <t>Membagi anggaran iklan ke kanal dan tujuan yang tepat</t>
   </si>
   <si>
-    <t>Sebagai media buyer, buatkan rencana alokasi anggaran iklan [ANGGARAN] per bulan untuk [BISNIS] dengan tujuan [TUJUAN]. Pilihan kanal: [KANAL]. Sertakan: prinsip pembagian anggaran untuk bisnis kecil (seberapa besar untuk penjualan langsung versus mengenalkan merek, berapa cadangan untuk uji coba), tabel alokasi per kanal dengan alasannya, struktur kampanye minimal di tiap kanal (jangan pecah terlalu kecil), aturan kapan anggaran dipindah antar kanal, metrik evaluasi mingguan, dan kesalahan pemborosan yang paling sering terjadi pada anggaran kecil.</t>
+    <t>Sebagai pembeli media, buatkan rencana alokasi anggaran iklan [ANGGARAN] per bulan untuk [BISNIS] dengan tujuan [TUJUAN]. Pilihan kanal: [KANAL]. Sertakan: prinsip pembagian anggaran untuk bisnis kecil (seberapa besar untuk penjualan langsung versus mengenalkan merek, berapa cadangan untuk uji coba), tabel alokasi per kanal dengan alasannya, struktur kampanye minimal di tiap kanal (jangan pecah terlalu kecil), aturan kapan anggaran dipindah antar kanal, metrik evaluasi mingguan, dan kesalahan pemborosan yang paling sering terjadi pada anggaran kecil.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [ANGGARAN]: total anggaran iklan per bulan; [KANAL]: pilihan kanal beriklan yang dipertimbangkan; [TUJUAN]: tujuan utama iklan (penjualan/daftar/kenal merek)</t>
@@ -3323,10 +3323,10 @@
     <t>Menyusun satu halaman pantauan berisi angka yang paling menentukan</t>
   </si>
   <si>
-    <t>Sebagai performance analyst, rancang dashboard KPI untuk [BISNIS] dengan goal utama [TUJUAN] menggunakan [ALAT]. Sumber data: [SUMBER_DATA]. Sertakan: pemilihan maksimal 7 KPI yang benar benar terhubung ke goal (tolak metrik yang cuma bagus dilihat), definisi tiap KPI agar semua orang mengerti sama, struktur layout dashboard dari kiri ke kanan (paling penting lebih dulu), frekuensi update tiap KPI, sumber pengambilan angkanya, dan aturan warna sederhana (hijau aman, kuning perlu perhatian, merah butuh tindakan). Dashboard harus bisa dibuat dalam satu hari.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [TUJUAN]: goal bisnis utama saat ini; [SUMBER_DATA]: tempat data berasal (platform/penjualan/iklan); [ALAT]: alat dashboard (spreadsheet/notion/berbayar)</t>
+    <t>Sebagai analis performa, rancang dashboard KPI untuk [BISNIS] dengan tujuan utama [TUJUAN] menggunakan [ALAT]. Sumber data: [SUMBER_DATA]. Sertakan: pemilihan maksimal 7 KPI yang benar benar terhubung ke tujuan (tolak metrik yang cuma bagus dilihat), definisi tiap KPI agar semua orang mengerti sama, struktur layout dashboard dari kiri ke kanan (paling penting lebih dulu), frekuensi update tiap KPI, sumber pengambilan angkanya, dan aturan warna sederhana (hijau aman, kuning perlu perhatian, merah butuh tindakan). Dashboard harus bisa dibuat dalam satu hari.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [TUJUAN]: tujuan bisnis utama saat ini; [SUMBER_DATA]: tempat data berasal (platform/penjualan/iklan); [ALAT]: alat dashboard (spreadsheet/notion/berbayar)</t>
   </si>
   <si>
     <t>Rancangan dashboard KPI maksimal 7 metrik dengan layout dan aturan warna</t>
@@ -3377,10 +3377,10 @@
     <t>Menilai capaian tiga bulan dan menyusun arah kuartal berikutnya</t>
   </si>
   <si>
-    <t>Sebagai fasilitator telaah strategi, fasilitasi telaah kuartalan [KUARTAL] untuk [BISNIS]. Goal awal: [TUJUAN]. Capaian: [CAPAIAN]. Sertakan: skor capaian per goal dengan bukti angka, analisis kenapa tiap goal tercapai atau tidak (faktor internal dan eksternal), pembelajaran yang harus dibawa ke kuartal berikutnya, keputusan berhenti, lanjut, atau ubah untuk tiap inisiatif, draf 3 goal kuartal berikutnya dengan metrik pengukuran, dan daftar pertanyaan berat untuk evaluasi diri yang tidak membolehkan jawaban mengambang.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [KUARTAL]: kuartal yang direview; [CAPAIAN]: data pencapaian kuartal; [TUJUAN]: goal yang ditetapkan di awal kuartal</t>
+    <t>Sebagai fasilitator telaah strategi, fasilitasi telaah kuartalan [KUARTAL] untuk [BISNIS]. Tujuan awal: [TUJUAN]. Capaian: [CAPAIAN]. Sertakan: skor capaian per tujuan dengan bukti angka, analisis kenapa tiap tujuan tercapai atau tidak (faktor internal dan eksternal), pembelajaran yang harus dibawa ke kuartal berikutnya, keputusan berhenti, lanjut, atau ubah untuk tiap inisiatif, draf 3 tujuan kuartal berikutnya dengan metrik pengukuran, dan daftar pertanyaan berat untuk evaluasi diri yang tidak membolehkan jawaban mengambang.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [KUARTAL]: kuartal yang direview; [CAPAIAN]: data pencapaian kuartal; [TUJUAN]: tujuan yang ditetapkan di awal kuartal</t>
   </si>
   <si>
     <t>Kerangka telaah kuartalan dengan keputusan per inisiatif dan draf target baru</t>
@@ -3395,7 +3395,7 @@
     <t>Menemukan topik yang dicari audiens tetapi belum Anda buat</t>
   </si>
   <si>
-    <t>Sebagai content strategist, analisis celah konten untuk [BISNIS] yang menjual [PRODUK]. Topik yang sudah dibuat: [KONTEN_ADA]. Pertanyaan audiens yang sering muncul: [PERTANYAAN_AUDIENS]. Sertakan: pemetaan topik yang sudah tercakup versus yang belum, kategori pertanyaan audiens yang belum terjawab oleh konten mana pun, 15 ide konten penutup celah diprioritaskan dari yang paling mendesak, format terbaik untuk tiap ide, dan jadwal masuk ke kalender 4 minggu tanpa menindih konten rutin yang sudah berjalan.</t>
+    <t>Sebagai perancang strategi konten, analisis celah konten untuk [BISNIS] yang menjual [PRODUK]. Topik yang sudah dibuat: [KONTEN_ADA]. Pertanyaan audiens yang sering muncul: [PERTANYAAN_AUDIENS]. Sertakan: pemetaan topik yang sudah tercakup versus yang belum, kategori pertanyaan audiens yang belum terjawab oleh konten mana pun, 15 ide konten penutup celah diprioritaskan dari yang paling mendesak, format terbaik untuk tiap ide, dan jadwal masuk ke kalender 4 minggu tanpa menindih konten rutin yang sudah berjalan.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk atau jasa utama; [KONTEN_ADA]: ringkasan topik yang sudah pernah dibuat; [PERTANYAAN_AUDIENS]: pertanyaan audiens yang sering muncul</t>
@@ -3413,7 +3413,7 @@
     <t>Memahami siapa yang benar benar mengikuti dan membeli dari Anda</t>
   </si>
   <si>
-    <t>Sebagai audience researcher, bedah data audiens berikut: [DATA] untuk [BISNIS] di [PLATFORM]. Data pembeli aktual: [PEMBELI]. Sertakan: profil follower dari data platform, perbandingan dengan profil pembeli sebenarnya karena follower bukan selalu pembeli, kesenjangan terbesar di antara keduanya dan artinya bagi strategi konten, segmen audiens yang paling berharga untuk difokuskan, konten yang cocok untuk segmen itu, dan 3 pertanyaan riset lanjutan yang perlu dijawab dari percakapan langsung bukan dari data.</t>
+    <t>Sebagai peneliti audiens, bedah data audiens berikut: [DATA] untuk [BISNIS] di [PLATFORM]. Data pembeli aktual: [PEMBELI]. Sertakan: profil follower dari data platform, perbandingan dengan profil pembeli sebenarnya karena follower bukan selalu pembeli, kesenjangan terbesar di antara keduanya dan artinya bagi strategi konten, segmen audiens yang paling berharga untuk difokuskan, konten yang cocok untuk segmen itu, dan 3 pertanyaan riset lanjutan yang perlu dijawab dari percakapan langsung bukan dari data.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang dianalisis; [DATA]: tempel data insight audiens (usia, lokasi, gender, jam aktif); [PEMBELI]: data pembeli aktual yang Anda kenal</t>
@@ -3449,10 +3449,10 @@
     <t>Menetapkan angka dasar untuk mengukur kemajuan ke depan</t>
   </si>
   <si>
-    <t>Sebagai performance baseline analyst, susun angka dasar untuk [BISNIS] di [PLATFORM] dari data 90 hari berikut: [DATA_90_HARI]. Goal 6 bulan: [TUJUAN]. Sertakan: perhitungan baseline tiap metrik utama (rata rata, angka terbaik, angka terburuk, tren arah), keputusan metrik mana yang jadi acuan utama dan mana yang hanya dipantau, target pertumbuhan bulanan yang berbasis baseline bukan harapan, tabel sederhana untuk mencatat perkembangan bulanan terhadap baseline, dan aturan review kapan baseline dihitung ulang karena situasi berubah.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang diukur; [DATA_90_HARI]: data performa 90 hari terakhir; [TUJUAN]: goal 6 bulan ke depan</t>
+    <t>Sebagai analis dasar performa, susun angka dasar untuk [BISNIS] di [PLATFORM] dari data 90 hari berikut: [DATA_90_HARI]. Tujuan 6 bulan: [TUJUAN]. Sertakan: perhitungan baseline tiap metrik utama (rata rata, angka terbaik, angka terburuk, tren arah), keputusan metrik mana yang jadi acuan utama dan mana yang hanya dipantau, target pertumbuhan bulanan yang berbasis baseline bukan harapan, tabel sederhana untuk mencatat perkembangan bulanan terhadap baseline, dan aturan review kapan baseline dihitung ulang karena situasi berubah.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang diukur; [DATA_90_HARI]: data performa 90 hari terakhir; [TUJUAN]: tujuan 6 bulan ke depan</t>
   </si>
   <si>
     <t>Baseline metrik dengan target pertumbuhan bertahap dan tabel pemantauan</t>
@@ -3485,7 +3485,7 @@
     <t>Mengelompokkan pelanggan per bulan masuk untuk melihat siapa yang bertahan</t>
   </si>
   <si>
-    <t>Sebagai retention analyst, ajari saya analisis kohort sederhana untuk [BISNIS] yang menjual [PRODUK]. Metrik yang dilihat: [METRIK]. Data yang saya punya: [DATA]. Sertakan: penjelasan analisis kohort dengan bahasa pemilik bisnis kecil, struktur tabel kohort (baris bulan masuk, kolom bulan ke 1 sampai 6, isi persentase pelanggan yang masih beli), cara mengisi tabel dari data saya, cara membaca pola bulan di mana pelanggan biasa hilang, penyebab umum kehilangan di titik itu, dan tindakan retensi yang disisipkan tepat sebelum titik hilang itu.</t>
+    <t>Sebagai analis retensi, ajari saya analisis kohort sederhana untuk [BISNIS] yang menjual [PRODUK]. Metrik yang dilihat: [METRIK]. Data yang saya punya: [DATA]. Sertakan: penjelasan analisis kohort dengan bahasa pemilik bisnis kecil, struktur tabel kohort (baris bulan masuk, kolom bulan ke 1 sampai 6, isi persentase pelanggan yang masih beli), cara mengisi tabel dari data saya, cara membaca pola bulan di mana pelanggan biasa hilang, penyebab umum kehilangan di titik itu, dan tindakan retensi yang disisipkan tepat sebelum titik hilang itu.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PRODUK]: produk atau jasa utama; [DATA]: data tanggal pembelian pertama dan pembelian lanjutan pelanggan; [METRIK]: metrik yang dilihat (repeat order/nilai beli/retensi)</t>
@@ -3539,7 +3539,7 @@
     <t>Mengurutkan konten dari yang paling menghasilkan agar bisa direplikasi</t>
   </si>
   <si>
-    <t>Sebagai content performance analyst, urutkan konten [PLATFORM] periode [PERIODE] berdasarkan hasil nyata untuk [BISNIS]. Data: [DATA]. Sertakan: metode penilaian yang menggabungkan jangkauan dan konversi bukan reach saja, tabel peringkat 10 konten teratas dengan skor, kategori konten yang mendominasi papan atas, kategori yang sering diposting tetapi tidak berkontribusi, biaya waktu per jenis konten versus hasilnya untuk menilai efisiensi, dan rekomendasi komposisi konten 30 hari ke depan berdasarkan peringkat ini.</t>
+    <t>Sebagai analis performa konten, urutkan konten [PLATFORM] periode [PERIODE] berdasarkan hasil nyata untuk [BISNIS]. Data: [DATA]. Sertakan: metode penilaian yang menggabungkan jangkauan dan konversi bukan reach saja, tabel peringkat 10 konten teratas dengan skor, kategori konten yang mendominasi papan atas, kategori yang sering diposting tetapi tidak berkontribusi, biaya waktu per jenis konten versus hasilnya untuk menilai efisiensi, dan rekomendasi komposisi konten 30 hari ke depan berdasarkan peringkat ini.</t>
   </si>
   <si>
     <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang dievaluasi; [DATA]: data konten (reach, engagement, klik, penjualan per konten); [PERIODE]: periode evaluasi</t>
@@ -3575,10 +3575,10 @@
     <t>Mengubah data yang sudah dikumpulkan menjadi keputusan konkret</t>
   </si>
   <si>
-    <t>Sebagai data driven strategist, ubah temuan berikut menjadi tindakan untuk [BISNIS]. Goal saat ini: [TUJUAN]. Kendala: [KENDALA]. Temuan: [TEMUAN]. Sertakan: interpretasi tiap temuan dalam satu kalimat maknanya, tindakan yang disarankan per temuan dengan tingkat dampak dan biaya, peringatan untuk temuan yang menarik tetapi belum layak ditindak, urutan tiga tindakan pertama yang harus dimulai minggu ini dengan alasan urutannya, dan cara mengukur apakah tindakan itu benar benar menjawab temuan awal.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [TEMUAN]: daftar temuan data yang sudah Anda kumpulkan; [TUJUAN]: goal yang sedang dikejar; [KENDALA]: sumber daya yang tersedia (waktu/anggaran/tim)</t>
+    <t>Sebagai perancang strategi berbasis data, ubah temuan berikut menjadi tindakan untuk [BISNIS]. Tujuan saat ini: [TUJUAN]. Kendala: [KENDALA]. Temuan: [TEMUAN]. Sertakan: interpretasi tiap temuan dalam satu kalimat maknanya, tindakan yang disarankan per temuan dengan tingkat dampak dan biaya, peringatan untuk temuan yang menarik tetapi belum layak ditindak, urutan tiga tindakan pertama yang harus dimulai minggu ini dengan alasan urutannya, dan cara mengukur apakah tindakan itu benar benar menjawab temuan awal.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [TEMUAN]: daftar temuan data yang sudah Anda kumpulkan; [TUJUAN]: tujuan yang sedang dikejar; [KENDALA]: sumber daya yang tersedia (waktu/anggaran/tim)</t>
   </si>
   <si>
     <t>Tabel terjemahan temuan ke tindakan dengan urutan minggu pertama</t>
@@ -3611,10 +3611,10 @@
     <t>Menyiapkan daftar data yang harus dicatat sejak sekarang agar analisis bisa jalan</t>
   </si>
   <si>
-    <t>Sebagai ahli penyiapan analitik, susun daftar data yang harus mulai dicatat untuk [BISNIS] di [PLATFORM] agar goal [TUJUAN] terukur. Alat: [ALAT]. Sertakan: daftar data wajib per minggu dan per bulan dengan sumber pengambilannya di tiap platform, data penjualan yang harus dicatat manual karena tidak otomatis, struktur spreadsheet per lembar kerja, aturan konsistensi (hari pencatatan, satuan, penamaan), kesalahan pencatatan yang membuat data tidak bisa dibandingkan, dan checklist 10 menit akhir minggu agar pencatatan tidak terlewat.</t>
-  </si>
-  <si>
-    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang dijalankan; [TUJUAN]: goal yang ingin diukur; [ALAT]: alat pencatatan yang dipakai (spreadsheet/notion/manual)</t>
+    <t>Sebagai ahli penyiapan analitik, susun daftar data yang harus mulai dicatat untuk [BISNIS] di [PLATFORM] agar tujuan [TUJUAN] terukur. Alat: [ALAT]. Sertakan: daftar data wajib per minggu dan per bulan dengan sumber pengambilannya di tiap platform, data penjualan yang harus dicatat manual karena tidak otomatis, struktur spreadsheet per lembar kerja, aturan konsistensi (hari pencatatan, satuan, penamaan), kesalahan pencatatan yang membuat data tidak bisa dibandingkan, dan checklist 10 menit akhir minggu agar pencatatan tidak terlewat.</t>
+  </si>
+  <si>
+    <t>[BISNIS]: jenis bisnis Anda; [PLATFORM]: platform yang dijalankan; [TUJUAN]: tujuan yang ingin diukur; [ALAT]: alat pencatatan yang dipakai (spreadsheet/notion/manual)</t>
   </si>
   <si>
     <t>Daftar data wajib dengan struktur spreadsheet dan checklist mingguan</t>
@@ -3641,7 +3641,7 @@
     <t>T-200</t>
   </si>
   <si>
-    <t>Annual Strategy Review</t>
+    <t>Telaah Strategi Tahunan</t>
   </si>
   <si>
     <t>Melakukan review strategi tahunan dan perencanaan tahun depan</t>
@@ -3650,7 +3650,7 @@
     <t>Sebagai direktur pemasaran, buatkan telaah strategi tahunan media sosial untuk [TAHUN_INI] dan perencanaan [TAHUN_DEPAN]. Pencapaian: [ACHIEVEMENTS]. Tantangan: [CHALLENGES]. Target: [GOALS_DEPAN]. Sertakan: (1) rekap setahun (metrik utama dan momen penting), (2) apa yang berhasil (5 faktor keberhasilan), (3) apa yang tidak berhasil (5 pelajaran), (4) perubahan lanskap kompetisi, (5) tren industri untuk tahun depan, (6) prioritas strategis (3-5 fokus utama), (7) target per kuartal dan inisiatifnya, (8) kebutuhan sumber daya (anggaran/tim/peralatan), (9) penilaian risiko dan cara menguranginya, (10) metrik keberhasilan dan rencana pemantauan. Buat lengkap tapi tetap bisa langsung dieksekusi.</t>
   </si>
   <si>
-    <t>[TAHUN_INI]: tahun yang di-review; [TAHUN_DEPAN]: tahun yang direncanakan; [ACHIEVEMENTS]: pencapaian tahun ini; [CHALLENGES]: tantangan yang dihadapi; [GOALS_DEPAN]: goal tahun depan</t>
+    <t>[TAHUN_INI]: tahun yang di-review; [TAHUN_DEPAN]: tahun yang direncanakan; [ACHIEVEMENTS]: pencapaian tahun ini; [CHALLENGES]: tantangan yang dihadapi; [GOALS_DEPAN]: tujuan tahun depan</t>
   </si>
   <si>
     <t>Telaah tahunan dan rencana strategis lengkap</t>
